--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,29 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +84,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,11 +98,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -92,6 +133,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2727,4 +2780,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول شارژر (Charger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Charger_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2077,76 @@
       <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CH-035</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>valid=false را از task_control به Charger_Evaluate بده؛ 5s مشاهده</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>safe-idle</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>duty=0 بدون overcurrent کاذب</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2136,15 +2136,226 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CH-036</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>استراحت حرارتی 1h-&gt;10min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>دو کانال BULK جریان ماکس 650mA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>یک ساعت مداوم &gt;=600mA شارژ کن</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>i&gt;=600 BULK 1h</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>70min</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>بعد 1h هر کانال 10min PWM=0 THERMAL_REST سپس ادامه</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PASS: PWM صفر در استراحت + رله بسته. FAIL: عدم استراحت</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CH-037</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ورودی خارج بازه 22-30V</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vin متغیر</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vin=20V سپس 31V بده</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vin 20V و 31V</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>در هر دو PWM=0 و INPUT_WAIT، فقط 22-30V شارژ</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PASS: عدم شارژ خارج بازه. FAIL: شارژ خارج بازه</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CH-038</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>حفظ THERMAL_REST در SafeIdle</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>کانال در استراحت حرارتی</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر بده حین rest</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>valid=false حین rest</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>THERMAL_REST حفظ نه OFF</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>کد بازبینی</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2203,14 +2203,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -2273,14 +2270,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -2343,7 +2337,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -2354,10 +2347,81 @@
           <t>thermal</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CH-039</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>شارژ فعال (BULK)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>حین شارژ صبر کن تا یک ذخیرهٔ فلش رخ دهد (ذخیرهٔ NVM یا CalLut از پنل، یا ذخیرهٔ دوره‌ای Diag حدود هر ۶۰ ثانیه) و گیت‌های PWM هر دو کانال را با اسکوپ ببین</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>شارژ فعال + ذخیرهٔ فلش</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2da0ed1</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -754,7 +754,10 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>شماتیک و board_pins.h با کد تطبیق داده شود</t>
+          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
+گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
+گام ۳: بررسی کن رله وقتی سیم‌پیچش خاموش است وصل باشد (NC).
+گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -825,7 +828,10 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>بوت برد؛ پالس PWM و state هر دو کانال در پنل دیده شود</t>
+          <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
+گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
+گام ۳: از پنل، پالس PWM و وضعیت (state) هر دو کانال را نگاه کن و زمان را از لحظهٔ بوت بگیر.
+گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -896,7 +902,10 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>با اسکوپ پله‌های duty بعد از گیت ثبات</t>
+          <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
+گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
+گام ۳: بعد از تمام شدن گیت 15 ثانیه‌ای ثبات، پله‌های duty را 20 ثانیه ضبط کن.
+گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -967,7 +976,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>جریان تخمینی خروجی (Iest) در پنل پایش شود</t>
+          <t>گام ۱: شارژ را در حالت BULK راه بینداز (باتری نیمه‌شارژ وصل باشد).
+گام ۲: در پنل، جریان تخمینی خروجی (Iest) همان کانال را باز کن.
+گام ۳: 60 ثانیه مقدار Iest را نگاه کن.
+گام ۴: باید در باند 630 تا 650 میلی‌آمپر تثبیت شود و همان‌جا پایدار بماند.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1038,7 +1050,10 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ورود 14.3V؛ رفتار پله 0.1٪ و فرار 14.6V</t>
+          <t>گام ۱: شارژ را ادامه بده تا ولتاژ کانال به حدود 14.3 ولت برسد.
+گام ۲: ولتاژ باتری را از 14300 به‌آرامی تا 14600 میلی‌ولت بالا ببر (با منبع یا بار قابل تنظیم).
+گام ۳: 120 ثانیه رفتار را نگاه کن: نزدیک 14.4 ولت باید با پله‌های ریز 0.1 درصدی تثبیت شود.
+گام ۴: وقتی از 14.6 ولت رد شد باید یک پلهٔ نزولی 0.5 درصدی ببینی؛ بازهٔ پایدار قابل قبول 14.35 تا 14.45 ولت است.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1109,7 +1124,10 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ادامه شارژ؛ شمارندهٔ شستشو (کل مدت ۱۰ دقیقه) + تیپر &lt;50mA/60s + سقف 1h</t>
+          <t>گام ۱: شارژ را در حالت ABSORB نگه دار.
+گام ۲: این سه شرط را زیر نظر بگیر: شستشوی کامل 10 دقیقه‌ای تمام شود، تیپر جریان زیر 50 میلی‌آمپر به مدت 60 ثانیه بماند، و سقف کلی 1 ساعت رد نشود.
+گام ۳: وضعیت کانال را در پنل نگاه کن (حداکثر تا 3600 ثانیه).
+گام ۴: بعد از کامل شدن شستشو باید وضعیت FLOAT شود (state=3).</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1180,7 +1198,10 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>duty پارک صفر؛ افت باتری زیر 12.8V</t>
+          <t>گام ۱: شارژ را در حالت FLOAT نگه دار؛ duty باید پارک و صفر باشد.
+گام ۲: ولتاژ باتری را به زیر 12.8 ولت (12800 میلی‌ولت) بیاور.
+گام ۳: 30 ثانیه وضعیت را نگاه کن.
+گام ۴: فقط وقتی زیر 12.8 ولت رفت باید برگردد به BULK (state=1) و آن هم با رمپ نرم از duty کم.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1251,7 +1272,10 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>بار طوری که جریان بدون فیلتر &gt;950mA شود</t>
+          <t>گام ۱: شارژ را در حالت BULK راه بینداز.
+گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
+گام ۳: همان لحظه گیت کانال را با اسکوپ یا پنل نگاه کن (در حد 1 ثانیه).
+گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1322,7 +1346,10 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>عبور آستانهٔ LM393 (اضافه‌جریان واقعی)؛ رفتار retry</t>
+          <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
+گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
+گام ۳: 10 ثانیه رفتار را نگاه کن: PWM همان کانال باید صفر شود.
+گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1393,7 +1420,10 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>تریپ مجدد در ریتری</t>
+          <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
+گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
+گام ۳: 10 ثانیه duty را نگاه کن.
+گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1464,7 +1494,10 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>تریپ سوم همان کانال</t>
+          <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
+گام ۲: JIT را برای بار سوم تریپ کن.
+گام ۳: وضعیت و رله را چک کن: باید FINAL_FAULT باشد (state=7)، هر دو PWM صفر و رله باز.
+گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1535,7 +1568,10 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ولتاژ sense کانال را زیر 2000mV یا بالای 15000mV ببر</t>
+          <t>گام ۱: شارژ فعال باشد.
+گام ۲: ولتاژ sense کانال را از بازه بیرون ببر: یک بار زیر 2000 میلی‌ولت و یک بار بالای 15000 میلی‌ولت.
+گام ۳: در هر دو حالت (در حد 1 ثانیه) گیت را نگاه کن: PWM همان کانال باید صفر شود.
+گام ۴: ولتاژ را به بازهٔ 2000 تا 15000 برگردان؛ PWM باید بعد از رفع خطا برگردد.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1606,7 +1642,10 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>پارامتر ۱۹=۱ با تأیید؛ duty های 16/18 مقدار بده</t>
+          <t>گام ۱: پنل ESP را وصل کن و ورودی 24 ولت بده.
+گام ۲: پارامتر 19 را روی 1 بگذار و تأیید کن تا مود دستی فعال شود (با دیالوگ تأیید).
+گام ۳: برای پارامترهای 16 و 18 مقدار 200 پرمیل duty بده.
+گام ۴: در 5 ثانیه اول چک کن: وضعیت هر دو کانال 9 (state=9) شود و duty مستقیم و بدون رمپ روی 200 پرمیل بنشیند؛ در این مود توقف 14.4 ولت و BAT_LOST غیرفعال‌اند.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1677,7 +1716,10 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>لینک ESP را قطع کن (هیچ فریمی نرسد)</t>
+          <t>گام ۱: شارژر را در مود دستی با duty فعال نگه دار (CH-013).
+گام ۲: لینک ESP را کامل قطع کن تا هیچ فریمی به برد نرسد.
+گام ۳: از زمان قطع لینک، حداکثر 4 ثانیه duty هر دو کانال را نگاه کن.
+گام ۴: حداکثر تا 3000 میلی‌ثانیه باید هر دو duty خودکار صفر شوند و شارژر به حالت خودکار برگردد.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1748,7 +1790,10 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>تریپ JIT → پارک؛ سپس ارسال مجدد همان duty از پنل</t>
+          <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
+گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
+گام ۳: از پنل همان duty را دوباره برای کانال بفرست؛ کانال باید دوباره مسلح شود و درایو برگردد.
+گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1819,7 +1864,10 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ولتاژ کانال بالای 15.0V</t>
+          <t>گام ۱: در مود دستی، یک electronic load با clamp وصل کن.
+گام ۲: ولتاژ کانال را به 15.0 ولت (15000 میلی‌ولت) و بالاتر برسان.
+گام ۳: 5 ثانیه نگاه کن: بالای 15 ولت duty باید صفر باشد.
+گام ۴: ولتاژ را زیر 15 ولت بیاور؛ شارژ باید خودکار ادامه پیدا کند.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1890,7 +1938,10 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>پارامتر 11=0 (قطع کانال ۱)</t>
+          <t>گام ۱: در مود دستی با هر دو کانال فعال باش (CH-013).
+گام ۲: پارامتر 11 را روی 0 بگذار (قطع کانال ۱).
+گام ۳: 2 ثانیه نگاه کن: duty کانال ۱ باید صفر شود ولی وضعیت همچنان 9 (state=9) بماند.
+گام ۴: کانال ۲ نباید تغییری کرده باشد.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1961,7 +2012,10 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>پارامتر ۱۹=۰ از پنل</t>
+          <t>گام ۱: در مود دستی باش (CH-013).
+گام ۲: پارامتر 19 را از پنل روی 0 بگذار تا مود دستی خاموش شود.
+گام ۳: 20 ثانیه نگاه کن: هر دو duty صفر شوند و وضعیت از 9 خارج شود (state≠9).
+گام ۴: شارژر خودکار باید از OFF شروع کند، گیت 15 ثانیه‌ای ثبات را بگذراند و بعد وارد BULK شود.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2032,7 +2086,10 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>پارامتر 13/14=200؛ سپس duty فیکس/دستی/رمپ</t>
+          <t>گام ۱: پارامترهای 13 و 14 (سقف duty دو کانال) را روی 200 پرمیل بگذار.
+گام ۲: یکی‌یکی این مسیرها را امتحان کن: duty ثابت خودکار، duty دستی از پنل، و رمپ نرم شروع شارژ.
+گام ۳: در هر مسیر 10 ثانیه duty واقعی گیت را با اسکوپ یا پنل بخوان.
+گام ۴: در هیچ مسیری duty نباید از 200 پرمیل بالاتر برود.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2103,7 +2160,10 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>valid=false را از task_control به Charger_Evaluate بده؛ 5s مشاهده</t>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
+گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
+گام ۳: duty هر دو کانال را نگاه کن: باید صفر بماند و شارژر safe-idle باشد.
+گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2170,7 +2230,10 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>یک ساعت مداوم &gt;=600mA شارژ کن</t>
+          <t>گام ۱: هر دو کانال را در BULK با جریان نزدیک سقف (دست‌کم 600 میلی‌آمپر) راه بینداز.
+گام ۲: یک ساعت (70 دقیقه با حاشیه) بی‌وقفه شارژ کن و PWM هر دو کانال را زیر نظر بگیر.
+گام ۳: بعد از 1 ساعت شارژ سنگین، هر کانال باید 10 دقیقه استراحت حرارتی برود: PWM صفر ولی رله بسته می‌ماند.
+گام ۴: بعد از 10 دقیقه استراحت، شارژ باید خودش ادامه پیدا کند. اگر استراحت نیامد، تست رد است.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2237,7 +2300,10 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vin=20V سپس 31V بده</t>
+          <t>گام ۱: منبع ورودی متغیر وصل کن و شارژ را در 24 ولت راه بینداز.
+گام ۲: ولتاژ ورودی را روی 20 ولت بگذار و 5 ثانیه نگاه کن: PWM باید صفر و وضعیت INPUT_WAIT باشد.
+گام ۳: ولتاژ را روی 31 ولت بگذار و 5 ثانیه نگاه کن: باز هم PWM صفر و INPUT_WAIT.
+گام ۴: به 24 ولت برگردان؛ شارژ باید برگردد. نتیجه: فقط در بازهٔ 22 تا 30 ولت شارژ مجاز است.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2304,7 +2370,10 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>snapshot نامعتبر بده حین rest</t>
+          <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
+گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
+گام ۳: 2 ثانیه وضعیت را نگاه کن: باید THERMAL_REST حفظ شود، نه اینکه به OFF برود.
+گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2376,7 +2445,10 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>حین شارژ صبر کن تا یک ذخیرهٔ فلش رخ دهد (ذخیرهٔ NVM یا CalLut از پنل، یا ذخیرهٔ دوره‌ای Diag حدود هر ۶۰ ثانیه) و گیت‌های PWM هر دو کانال را با اسکوپ ببین</t>
+          <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
+گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
+گام ۳: لحظهٔ پاک/نوشتن فلش را روی اسکوپ ببین: هر دو گیت PWM باید متوقف و خروجی صفر باشد.
+گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +71,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +153,33 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,11 +201,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +291,94 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -517,21 +753,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Charger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Charger | دو شارژر مستقل ۱۲V؛ Ch1→باتری بالا (VHIGH)، Ch2→باتری پایین (VLOW)؛ پارامترهای زندهٔ ESP + مود تست دستی v1.2</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -541,21 +777,21 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>سناریوها حول رفتار قابل مشاهدهٔ هر کانال: state (تله‌متری ESP)، duty (اسکوپ PA0/PA6)، رلهٔ NC و پنل ESP نوشته شده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>ثابت‌های مرجع در charger.h: باند تنظیم 630..650mA تخمینی، خطای سخت 950mA، ابزورب 14.3/14.4/14.6V، فلوت 13.5V، reentry 12.8V، سقف duty 500‰، ددمن مود دستی 3000ms.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>تست مود دستی فقط با بار مقاومتی یا electronic load با voltage clamp؛ مقاومت آزاد شبیه‌ساز باتری نیست و منبع ورودی باید محدودشده باشد.</t>
         </is>
@@ -565,14 +801,14 @@
       <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>هشدار: تست مود دستی بدون باتری فقط با electronic load دارای voltage clamp؛ هرگز با مقاومت آزاد.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>هشدار: منبع ورودی در تست‌های اول محدودشده باشد؛ current-limit ورودی جای حفاظت خروجی firmware نیست.</t>
         </is>
@@ -591,6 +827,9 @@
     <mergeCell ref="A5"/>
     <mergeCell ref="A1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -598,161 +837,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Charger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>CH-001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>نگاشت سخت‌افزار</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
@@ -760,73 +1000,73 @@
 گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>PA0=TIM2_CH1، PA6=TIM3_CH1، PA1/PA7 سنس، PB2/PB6 JIT، رله NC</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>نگاشت مطابق شماتیک؛ رله با coil خاموش وصل (NC)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>نگاشت ثابت</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>PASS: تطابق کامل</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr"/>
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CH-002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>پیش‌فرض امن بوت</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>باتری و ورودی ۲۴V وصل، بوت تازه</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
 گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
@@ -834,73 +1074,73 @@
 گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>v_in=24V، هر دو v_bat≥12V</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>هر دو PWM صفر تا پایان گیت ۱۵ ثانیهٔ ثبات اتصال</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>حفظ تا شروع BULK</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>PWM=0 تا 15000±2000ms</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CH-003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>شروع BULK با رمپ</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>CH-002 پاس</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
 گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
@@ -908,73 +1148,73 @@
 گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>همان CH-002</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>پله‌های duty از 10‰ صعودی</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CH-004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>تنظیم BULK</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>در BULK</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز (باتری نیمه‌شارژ وصل باشد).
 گام ۲: در پنل، جریان تخمینی خروجی (Iest) همان کانال را باز کن.
@@ -982,73 +1222,73 @@
 گام ۴: باید در باند 630 تا 650 میلی‌آمپر تثبیت شود و همان‌جا پایدار بماند.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>باتری نیمه‌شارژ</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>Iest در باند 630..650mA تثبیت</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>نگه‌داشت باند</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>630≤Iest≤650 پایدار</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>ولتاژ کانال به 14.3V می‌رسد</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده تا ولتاژ کانال به حدود 14.3 ولت برسد.
 گام ۲: ولتاژ باتری را از 14300 به‌آرامی تا 14600 میلی‌ولت بالا ببر (با منبع یا بار قابل تنظیم).
@@ -1056,73 +1296,73 @@
 گام ۴: وقتی از 14.6 ولت رد شد باید یک پلهٔ نزولی 0.5 درصدی ببینی؛ بازهٔ پایدار قابل قبول 14.35 تا 14.45 ولت است.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>v_bat≈14300→14600mV</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>120s</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>تثبیت حدود 14.4V با پله ریز؛ عبور 14.6V پله نزولی 0.5٪</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>14.35..14.45V پایدار</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CH-006</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>شستشوی ABSORB</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>در ABSORB</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت ABSORB نگه دار.
 گام ۲: این سه شرط را زیر نظر بگیر: شستشوی کامل 10 دقیقه‌ای تمام شود، تیپر جریان زیر 50 میلی‌آمپر به مدت 60 ثانیه بماند، و سقف کلی 1 ساعت رد نشود.
@@ -1130,73 +1370,73 @@
 گام ۴: بعد از کامل شدن شستشو باید وضعیت FLOAT شود (state=3).</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>تا 3600s</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>ورود FLOAT بعد از شستشوی کامل</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>یک‌بار</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>state=3 بعد از شرط شستشو</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>CH-007</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FLOAT و reentry</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>در FLOAT</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت FLOAT نگه دار؛ duty باید پارک و صفر باشد.
 گام ۲: ولتاژ باتری را به زیر 12.8 ولت (12800 میلی‌ولت) بیاور.
@@ -1204,73 +1444,73 @@
 گام ۴: فقط وقتی زیر 12.8 ولت رفت باید برگردد به BULK (state=1) و آن هم با رمپ نرم از duty کم.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>v_bat&lt;12800mV</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>پارک روی duty صفر؛ reentry به BULK فقط زیر 12.8V</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>state=1 با رمپ نرم</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>CH-008</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>خطای سخت جریان</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>در BULK</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز.
 گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
@@ -1278,73 +1518,73 @@
 گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>I_unfilt&gt;950mA</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>ریست کانال (PWM صفر فوری و شروع دوباره)</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>لحظه‌ای</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>PWM=0 فوری</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr"/>
+      <c r="N12" s="22" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>CH-009</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>تریپ JIT اول</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
 گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
@@ -1352,73 +1592,73 @@
 گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>JIT falling (PB2/PB6)</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>retry خودکار</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>state=5 → ریتری 50٪ duty قبل</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>CH-010</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>تریپ دوم همان کانال</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
 گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
@@ -1426,73 +1666,73 @@
 گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم حداکثر 10٪ (100‰)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>duty≤100‰</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="22" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr"/>
+      <c r="Q14" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>CH-011</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>تریپ سوم FINAL</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>دو تریپ ثبت‌شده</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
 گام ۲: JIT را برای بار سوم تریپ کن.
@@ -1500,73 +1740,73 @@
 گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>latch دائمی تا ریبوت</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: ولتاژ sense کانال را از بازه بیرون ببر: یک بار زیر 2000 میلی‌ولت و یک بار بالای 15000 میلی‌ولت.
@@ -1574,73 +1814,73 @@
 گام ۴: ولتاژ را به بازهٔ 2000 تا 15000 برگردان؛ PWM باید بعد از رفع خطا برگردد.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>v_bat خارج 2000..15000mV</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر تا رفع</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>تا رفع شرط</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>PWM=0</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr"/>
+      <c r="N16" s="22" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>پنل ESP وصل، ورودی ۲۴V</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل ESP را وصل کن و ورودی 24 ولت بده.
 گام ۲: پارامتر 19 را روی 1 بگذار و تأیید کن تا مود دستی فعال شود (با دیالوگ تأیید).
@@ -1648,73 +1888,73 @@
 گام ۴: در 5 ثانیه اول چک کن: وضعیت هر دو کانال 9 (state=9) شود و duty مستقیم و بدون رمپ روی 200 پرمیل بنشیند؛ در این مود توقف 14.4 ولت و BAT_LOST غیرفعال‌اند.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>ID19=1، ID16/18=200‰</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>state=9 هر دو کانال؛ duty مستقیم بدون رمپ؛ توقف 14.4V و BAT_LOST غیرفعال</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>duty فوری=200‰ هر دو</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr"/>
+      <c r="N17" s="17" t="inlineStr"/>
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="P17" s="19" t="inlineStr"/>
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>CH-014</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>مود دستی: ددمن لینک</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>گام ۱: شارژر را در مود دستی با duty فعال نگه دار (CH-013).
 گام ۲: لینک ESP را کامل قطع کن تا هیچ فریمی به برد نرسد.
@@ -1722,73 +1962,73 @@
 گام ۴: حداکثر تا 3000 میلی‌ثانیه باید هر دو duty خودکار صفر شوند و شارژر به حالت خودکار برگردد.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>سکوت لینک</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>4s</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>خروج خودکار: هر دو duty صفر + بازگشت شارژر خودکار</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>duty=0 در ≤3000ms</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr"/>
+      <c r="N18" s="22" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="P18" s="24" t="inlineStr"/>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>CH-015</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>مود دستی: JIT و re-arm</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
 گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
@@ -1796,73 +2036,73 @@
 گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>JIT trip در مود دستی</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>پارک تا re-arm انسانی</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr"/>
+      <c r="N19" s="17" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="P19" s="19" t="inlineStr"/>
+      <c r="Q19" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>CH-016</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>مود دستی: قطع 15V</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>در مود دستی، electronic load با clamp</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی، یک electronic load با clamp وصل کن.
 گام ۲: ولتاژ کانال را به 15.0 ولت (15000 میلی‌ولت) و بالاتر برسان.
@@ -1870,73 +2110,73 @@
 گام ۴: ولتاژ را زیر 15 ولت بیاور؛ شارژ باید خودکار ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>v_bat≥15000mV</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>duty صفر؛ با افت زیر 15V ادامهٔ خودکار</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>خودکار</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>PWM=0 بالای 15V و برگشت زیرش</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr"/>
+      <c r="N20" s="22" t="inlineStr"/>
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="P20" s="24" t="inlineStr"/>
+      <c r="Q20" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>CH-017</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>مود دستی: قطع کانال</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی با هر دو کانال فعال باش (CH-013).
 گام ۲: پارامتر 11 را روی 0 بگذار (قطع کانال ۱).
@@ -1944,73 +2184,73 @@
 گام ۴: کانال ۲ نباید تغییری کرده باشد.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>ID11=0</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>duty کانال ۱ صفر؛ state همچنان 9</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>PWM1=0، state=9</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="M21" s="17" t="inlineStr"/>
+      <c r="N21" s="17" t="inlineStr"/>
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="P21" s="19" t="inlineStr"/>
+      <c r="Q21" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>CH-018</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی باش (CH-013).
 گام ۲: پارامتر 19 را از پنل روی 0 بگذار تا مود دستی خاموش شود.
@@ -2018,73 +2258,73 @@
 گام ۴: شارژر خودکار باید از OFF شروع کند، گیت 15 ثانیه‌ای ثبات را بگذراند و بعد وارد BULK شود.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>ID19=0</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>هر دو duty صفر؛ شارژر خودکار از OFF با گیت ۱۵s دوباره</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>state≠9؛ settle→BULK</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr"/>
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr"/>
+      <c r="N22" s="22" t="inlineStr"/>
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="P22" s="24" t="inlineStr"/>
+      <c r="Q22" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>CH-019</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>سقف duty زنده</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پارامترهای 13 و 14 (سقف duty دو کانال) را روی 200 پرمیل بگذار.
 گام ۲: یکی‌یکی این مسیرها را امتحان کن: duty ثابت خودکار، duty دستی از پنل، و رمپ نرم شروع شارژ.
@@ -2092,73 +2332,73 @@
 گام ۴: در هیچ مسیری duty نباید از 200 پرمیل بالاتر برود.</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>ID13=200</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>همهٔ مسیرهای duty به سقف زمان-اجرا گیره می‌خورند</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>duty≤200‰ در همهٔ حالت‌ها</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr"/>
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="M23" s="17" t="inlineStr"/>
+      <c r="N23" s="17" t="inlineStr"/>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="P23" s="19" t="inlineStr"/>
+      <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>CH-035</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
 گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
@@ -2166,69 +2406,73 @@
 گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>safe-idle</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>duty=0 بدون overcurrent کاذب</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>CH-036</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>استراحت حرارتی 1h-&gt;10min</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>دو کانال BULK جریان ماکس 650mA</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در BULK با جریان نزدیک سقف (دست‌کم 600 میلی‌آمپر) راه بینداز.
 گام ۲: یک ساعت (70 دقیقه با حاشیه) بی‌وقفه شارژ کن و PWM هر دو کانال را زیر نظر بگیر.
@@ -2236,69 +2480,73 @@
 گام ۴: بعد از 10 دقیقه استراحت، شارژ باید خودش ادامه پیدا کند. اگر استراحت نیامد، تست رد است.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>i&gt;=600 BULK 1h</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>70min</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>بعد 1h هر کانال 10min PWM=0 THERMAL_REST سپس ادامه</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>PASS: PWM صفر در استراحت + رله بسته. FAIL: عدم استراحت</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="M25" s="17" t="n"/>
+      <c r="N25" s="17" t="n"/>
+      <c r="O25" s="19" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>CH-037</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>ورودی خارج بازه 22-30V</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Vin متغیر</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>گام ۱: منبع ورودی متغیر وصل کن و شارژ را در 24 ولت راه بینداز.
 گام ۲: ولتاژ ورودی را روی 20 ولت بگذار و 5 ثانیه نگاه کن: PWM باید صفر و وضعیت INPUT_WAIT باشد.
@@ -2306,69 +2554,73 @@
 گام ۴: به 24 ولت برگردان؛ شارژ باید برگردد. نتیجه: فقط در بازهٔ 22 تا 30 ولت شارژ مجاز است.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>Vin 20V و 31V</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>در هر دو PWM=0 و INPUT_WAIT، فقط 22-30V شارژ</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>PASS: عدم شارژ خارج بازه. FAIL: شارژ خارج بازه</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="24" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="P26" s="24" t="n"/>
+      <c r="Q26" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>CH-038</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>حفظ THERMAL_REST در SafeIdle</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>کانال در استراحت حرارتی</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
 گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
@@ -2376,74 +2628,77 @@
 گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>valid=false حین rest</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>THERMAL_REST حفظ نه OFF</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="17" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>CH-039</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال (BULK)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
@@ -2451,73 +2706,332 @@
 گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>شارژ فعال + ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="24" t="inlineStr">
         <is>
           <t>2da0ed1</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="P28" s="24" t="n"/>
+      <c r="Q28" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="Q29" s="31">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="31">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="31">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="31">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="31">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="31">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="31">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="31">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="31">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="31">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="31">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="31">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="31">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="31">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="31">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="31">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="31">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="31">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="31">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="31">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="31">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="31">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="31">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="31">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="31">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="31">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="31">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="31">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="31">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="31">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="31">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="31">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="31">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="31">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Q63" s="31">
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Q64" s="31">
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="Q65" s="31">
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="Q66" s="31">
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="Q67" s="31">
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="Q68" s="31">
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q28"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2531,197 +3045,202 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Charger</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="43" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>گیت ثبات اتصال</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>۱۵s دیدن ولتاژ باتری</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>OFF→BULK فقط بعد از ثبات</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>charger.h (2026-09-19)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>JIT-ریتری و reentry معاف</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>باند تنظیم BULK</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>630..650mA Iest</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>پله‌های duty برای نگه‌داشت باند</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>CHG_REGULATE_LOW_MA / CHG_BULK_CURRENT_MAX_MA</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>تصمیم روی جریان تخمینی خروجی</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>خطای سخت جریان</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>&gt;950mA</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>ریست کانال</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>CHG_CURRENT_HARD_FAULT_MA</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>حداکثر ~10ms تأخیر با فیلترها</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>ورود 14.3 / نگه‌داشت 14.4 / فرار 14.6V</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>پله 0.1٪ / نزول 0.5٪</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>CHG_ABSORB_*</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>شستشوی ۱۰ دقیقه کل مدت</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>JIT</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>lockout 3s، ریتری ۵۰٪، دوم ≤۱۰٪، سوم FINAL</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>ریتری تک‌تک از صف</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>CHG_JIT_LOCKOUT_MS / CHG_DUTY_RETRY_SECOND_MAX</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>در مود دستی: بدون ریتری، فقط re-arm</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>مود دستی v1.2</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>ID19، ددمن 3s، قطع 15V، سقف، قطع کانال</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>duty مستقیم از 16/18</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>CHG_MANUAL_WATCHDOG_MS و §5.2 سند ESP</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>فریز Fault_Evaluate حین مود</t>
         </is>
@@ -2731,6 +3250,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2738,6 +3260,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2760,81 +3283,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Charger</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="42" t="n"/>
+      <c r="C2" s="42" t="n"/>
+      <c r="D2" s="42" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="42" t="n"/>
+      <c r="G2" s="42" t="n"/>
+      <c r="H2" s="42" t="n"/>
+      <c r="I2" s="42" t="n"/>
+      <c r="J2" s="42" t="n"/>
+      <c r="K2" s="42" t="n"/>
+      <c r="L2" s="42" t="n"/>
+      <c r="M2" s="43" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="32" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="32" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="32" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2852,6 +3387,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2864,203 +3400,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Charger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Charger — دو کانال ۱۲V مستقل</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — پوشش v1.2 مود دستی)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>پنل ESP + اسکوپ + مولتی‌متر + منبع محدودشده</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="35">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="35">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="35">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="35">
         <f>IF(19=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/19)</f>
         <v/>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -3079,6 +3617,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3090,105 +3629,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -3202,7 +3749,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3214,55 +3761,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول شارژر (Charger)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Charger_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -3275,6 +3823,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,13 @@
       <name val="Tahoma"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -263,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -379,6 +389,13 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -974,99 +991,25 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>CH-001</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>نگاشت سخت‌افزار</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+          <t>CH-002</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>پیش‌فرض امن بوت</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>برد خاموش</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
-گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
-گام ۳: بررسی کن رله وقتی سیم‌پیچش خاموش است وصل باشد (NC).
-گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>PA0=TIM2_CH1، PA6=TIM3_CH1، PA1/PA7 سنس، PB2/PB6 JIT، رله NC</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>نگاشت مطابق شماتیک؛ رله با coil خاموش وصل (NC)</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>نگاشت ثابت</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>PASS: تطابق کامل</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr"/>
-      <c r="O5" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="19" t="inlineStr"/>
-      <c r="Q5" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>CH-002</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>پیش‌فرض امن بوت</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>باتری و ورودی ۲۴V وصل، بوت تازه</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
 گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
@@ -1074,73 +1017,73 @@
 گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>v_in=24V، هر دو v_bat≥12V</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>هر دو PWM صفر تا پایان گیت ۱۵ ثانیهٔ ثبات اتصال</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>حفظ تا شروع BULK</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>PWM=0 تا 15000±2000ms</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr"/>
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CH-003</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>شروع BULK با رمپ</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>CH-002 پاس</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
 گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
@@ -1148,73 +1091,73 @@
 گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>همان CH-002</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>پله‌های duty از 10‰ صعودی</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr"/>
+      <c r="O6" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="P6" s="19" t="inlineStr"/>
+      <c r="Q6" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CH-004</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>تنظیم BULK</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>در BULK</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز (باتری نیمه‌شارژ وصل باشد).
 گام ۲: در پنل، جریان تخمینی خروجی (Iest) همان کانال را باز کن.
@@ -1222,73 +1165,73 @@
 گام ۴: باید در باند 630 تا 650 میلی‌آمپر تثبیت شود و همان‌جا پایدار بماند.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>باتری نیمه‌شارژ</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>Iest در باند 630..650mA تثبیت</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>نگه‌داشت باند</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>630≤Iest≤650 پایدار</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr"/>
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>ولتاژ کانال به 14.3V می‌رسد</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده تا ولتاژ کانال به حدود 14.3 ولت برسد.
 گام ۲: ولتاژ باتری را از 14300 به‌آرامی تا 14600 میلی‌ولت بالا ببر (با منبع یا بار قابل تنظیم).
@@ -1296,73 +1239,73 @@
 گام ۴: وقتی از 14.6 ولت رد شد باید یک پلهٔ نزولی 0.5 درصدی ببینی؛ بازهٔ پایدار قابل قبول 14.35 تا 14.45 ولت است.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>v_bat≈14300→14600mV</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>120s</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>تثبیت حدود 14.4V با پله ریز؛ عبور 14.6V پله نزولی 0.5٪</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>14.35..14.45V پایدار</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr"/>
+      <c r="N8" s="17" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>CH-006</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>شستشوی ABSORB</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>در ABSORB</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت ABSORB نگه دار.
 گام ۲: این سه شرط را زیر نظر بگیر: شستشوی کامل 10 دقیقه‌ای تمام شود، تیپر جریان زیر 50 میلی‌آمپر به مدت 60 ثانیه بماند، و سقف کلی 1 ساعت رد نشود.
@@ -1370,73 +1313,73 @@
 گام ۴: بعد از کامل شدن شستشو باید وضعیت FLOAT شود (state=3).</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>تا 3600s</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>ورود FLOAT بعد از شستشوی کامل</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>یک‌بار</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>state=3 بعد از شرط شستشو</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr"/>
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr"/>
+      <c r="Q9" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CH-007</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>FLOAT و reentry</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>در FLOAT</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت FLOAT نگه دار؛ duty باید پارک و صفر باشد.
 گام ۲: ولتاژ باتری را به زیر 12.8 ولت (12800 میلی‌ولت) بیاور.
@@ -1444,73 +1387,73 @@
 گام ۴: فقط وقتی زیر 12.8 ولت رفت باید برگردد به BULK (state=1) و آن هم با رمپ نرم از duty کم.</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>v_bat&lt;12800mV</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>پارک روی duty صفر؛ reentry به BULK فقط زیر 12.8V</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>state=1 با رمپ نرم</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>CH-008</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>خطای سخت جریان</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>در BULK</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز.
 گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
@@ -1518,73 +1461,73 @@
 گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>I_unfilt&gt;950mA</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>ریست کانال (PWM صفر فوری و شروع دوباره)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>لحظه‌ای</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>PWM=0 فوری</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr"/>
+      <c r="N11" s="22" t="inlineStr"/>
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="P11" s="24" t="inlineStr"/>
+      <c r="Q11" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>CH-009</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>تریپ JIT اول</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
 گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
@@ -1592,73 +1535,73 @@
 گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>JIT falling (PB2/PB6)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>retry خودکار</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>state=5 → ریتری 50٪ duty قبل</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr"/>
+      <c r="N12" s="17" t="inlineStr"/>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="19" t="inlineStr"/>
-      <c r="Q13" s="21" t="inlineStr">
+      <c r="P12" s="19" t="inlineStr"/>
+      <c r="Q12" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>CH-010</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>تریپ دوم همان کانال</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
 گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
@@ -1666,73 +1609,73 @@
 گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم حداکثر 10٪ (100‰)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>duty≤100‰</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr"/>
+      <c r="N13" s="22" t="inlineStr"/>
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr"/>
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>CH-011</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>تریپ سوم FINAL</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>دو تریپ ثبت‌شده</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
 گام ۲: JIT را برای بار سوم تریپ کن.
@@ -1740,73 +1683,73 @@
 گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>latch دائمی تا ریبوت</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr"/>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="19" t="inlineStr"/>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="P14" s="19" t="inlineStr"/>
+      <c r="Q14" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: ولتاژ sense کانال را از بازه بیرون ببر: یک بار زیر 2000 میلی‌ولت و یک بار بالای 15000 میلی‌ولت.
@@ -1814,73 +1757,73 @@
 گام ۴: ولتاژ را به بازهٔ 2000 تا 15000 برگردان؛ PWM باید بعد از رفع خطا برگردد.</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>v_bat خارج 2000..15000mV</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر تا رفع</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>تا رفع شرط</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>PWM=0</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr"/>
-      <c r="N16" s="22" t="inlineStr"/>
-      <c r="O16" s="24" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr"/>
+      <c r="N15" s="22" t="inlineStr"/>
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr"/>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="P15" s="24" t="inlineStr"/>
+      <c r="Q15" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>پنل ESP وصل، ورودی ۲۴V</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل ESP را وصل کن و ورودی 24 ولت بده.
 گام ۲: پارامتر 19 را روی 1 بگذار و تأیید کن تا مود دستی فعال شود (با دیالوگ تأیید).
@@ -1888,73 +1831,73 @@
 گام ۴: در 5 ثانیه اول چک کن: وضعیت هر دو کانال 9 (state=9) شود و duty مستقیم و بدون رمپ روی 200 پرمیل بنشیند؛ در این مود توقف 14.4 ولت و BAT_LOST غیرفعال‌اند.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>ID19=1، ID16/18=200‰</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>state=9 هر دو کانال؛ duty مستقیم بدون رمپ؛ توقف 14.4V و BAT_LOST غیرفعال</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>duty فوری=200‰ هر دو</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr"/>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr"/>
-      <c r="N17" s="17" t="inlineStr"/>
-      <c r="O17" s="19" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr"/>
+      <c r="N16" s="17" t="inlineStr"/>
+      <c r="O16" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P17" s="19" t="inlineStr"/>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="P16" s="19" t="inlineStr"/>
+      <c r="Q16" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>CH-014</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>مود دستی: ددمن لینک</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>گام ۱: شارژر را در مود دستی با duty فعال نگه دار (CH-013).
 گام ۲: لینک ESP را کامل قطع کن تا هیچ فریمی به برد نرسد.
@@ -1962,73 +1905,73 @@
 گام ۴: حداکثر تا 3000 میلی‌ثانیه باید هر دو duty خودکار صفر شوند و شارژر به حالت خودکار برگردد.</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>سکوت لینک</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>4s</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>خروج خودکار: هر دو duty صفر + بازگشت شارژر خودکار</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>duty=0 در ≤3000ms</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr"/>
-      <c r="N18" s="22" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr"/>
+      <c r="N17" s="22" t="inlineStr"/>
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr"/>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="P17" s="24" t="inlineStr"/>
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>CH-015</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>مود دستی: JIT و re-arm</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
 گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
@@ -2036,73 +1979,73 @@
 گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>JIT trip در مود دستی</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>پارک تا re-arm انسانی</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr"/>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr"/>
-      <c r="N19" s="17" t="inlineStr"/>
-      <c r="O19" s="19" t="inlineStr">
+      <c r="M18" s="17" t="inlineStr"/>
+      <c r="N18" s="17" t="inlineStr"/>
+      <c r="O18" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P19" s="19" t="inlineStr"/>
-      <c r="Q19" s="21" t="inlineStr">
+      <c r="P18" s="19" t="inlineStr"/>
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>CH-016</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>مود دستی: قطع 15V</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>در مود دستی، electronic load با clamp</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی، یک electronic load با clamp وصل کن.
 گام ۲: ولتاژ کانال را به 15.0 ولت (15000 میلی‌ولت) و بالاتر برسان.
@@ -2110,73 +2053,73 @@
 گام ۴: ولتاژ را زیر 15 ولت بیاور؛ شارژ باید خودکار ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>v_bat≥15000mV</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>duty صفر؛ با افت زیر 15V ادامهٔ خودکار</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>خودکار</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>PWM=0 بالای 15V و برگشت زیرش</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr"/>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="22" t="inlineStr"/>
-      <c r="N20" s="22" t="inlineStr"/>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr"/>
+      <c r="N19" s="22" t="inlineStr"/>
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr"/>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="P19" s="24" t="inlineStr"/>
+      <c r="Q19" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>CH-017</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>مود دستی: قطع کانال</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی با هر دو کانال فعال باش (CH-013).
 گام ۲: پارامتر 11 را روی 0 بگذار (قطع کانال ۱).
@@ -2184,73 +2127,73 @@
 گام ۴: کانال ۲ نباید تغییری کرده باشد.</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>ID11=0</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>duty کانال ۱ صفر؛ state همچنان 9</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>PWM1=0، state=9</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr"/>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr"/>
-      <c r="N21" s="17" t="inlineStr"/>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="M20" s="17" t="inlineStr"/>
+      <c r="N20" s="17" t="inlineStr"/>
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P21" s="19" t="inlineStr"/>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="P20" s="19" t="inlineStr"/>
+      <c r="Q20" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>CH-018</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی باش (CH-013).
 گام ۲: پارامتر 19 را از پنل روی 0 بگذار تا مود دستی خاموش شود.
@@ -2258,73 +2201,73 @@
 گام ۴: شارژر خودکار باید از OFF شروع کند، گیت 15 ثانیه‌ای ثبات را بگذراند و بعد وارد BULK شود.</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>ID19=0</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>هر دو duty صفر؛ شارژر خودکار از OFF با گیت ۱۵s دوباره</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>state≠9؛ settle→BULK</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr"/>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr"/>
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="22" t="inlineStr"/>
-      <c r="N22" s="22" t="inlineStr"/>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr"/>
+      <c r="N21" s="22" t="inlineStr"/>
+      <c r="O21" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr"/>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="P21" s="24" t="inlineStr"/>
+      <c r="Q21" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>CH-019</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>سقف duty زنده</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پارامترهای 13 و 14 (سقف duty دو کانال) را روی 200 پرمیل بگذار.
 گام ۲: یکی‌یکی این مسیرها را امتحان کن: duty ثابت خودکار، duty دستی از پنل، و رمپ نرم شروع شارژ.
@@ -2332,147 +2275,73 @@
 گام ۴: در هیچ مسیری duty نباید از 200 پرمیل بالاتر برود.</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>ID13=200</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>همهٔ مسیرهای duty به سقف زمان-اجرا گیره می‌خورند</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>duty≤200‰ در همهٔ حالت‌ها</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr"/>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr"/>
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr"/>
-      <c r="N23" s="17" t="inlineStr"/>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="M22" s="17" t="inlineStr"/>
+      <c r="N22" s="17" t="inlineStr"/>
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P23" s="19" t="inlineStr"/>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="P22" s="19" t="inlineStr"/>
+      <c r="Q22" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>CH-035</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>snapshot zeroing</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>CH-036</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>استراحت حرارتی 1h-&gt;10min</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>snapshot نامعتبر</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
-گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
-گام ۳: duty هر دو کانال را نگاه کن: باید صفر بماند و شارژر safe-idle باشد.
-گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>safe-idle</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>duty=0 بدون overcurrent کاذب</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="29" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="24" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="25" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>CH-036</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>استراحت حرارتی 1h-&gt;10min</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>دو کانال BULK جریان ماکس 650mA</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در BULK با جریان نزدیک سقف (دست‌کم 600 میلی‌آمپر) راه بینداز.
 گام ۲: یک ساعت (70 دقیقه با حاشیه) بی‌وقفه شارژ کن و PWM هر دو کانال را زیر نظر بگیر.
@@ -2480,73 +2349,73 @@
 گام ۴: بعد از 10 دقیقه استراحت، شارژ باید خودش ادامه پیدا کند. اگر استراحت نیامد، تست رد است.</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>i&gt;=600 BULK 1h</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>70min</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>بعد 1h هر کانال 10min PWM=0 THERMAL_REST سپس ادامه</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>PASS: PWM صفر در استراحت + رله بسته. FAIL: عدم استراحت</t>
         </is>
       </c>
-      <c r="K25" s="17" t="n"/>
-      <c r="L25" s="29" t="inlineStr">
+      <c r="K23" s="17" t="n"/>
+      <c r="L23" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M25" s="17" t="n"/>
-      <c r="N25" s="17" t="n"/>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P25" s="19" t="n"/>
-      <c r="Q25" s="21" t="inlineStr">
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>CH-037</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>ورودی خارج بازه 22-30V</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>Vin متغیر</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>گام ۱: منبع ورودی متغیر وصل کن و شارژ را در 24 ولت راه بینداز.
 گام ۲: ولتاژ ورودی را روی 20 ولت بگذار و 5 ثانیه نگاه کن: PWM باید صفر و وضعیت INPUT_WAIT باشد.
@@ -2554,151 +2423,73 @@
 گام ۴: به 24 ولت برگردان؛ شارژ باید برگردد. نتیجه: فقط در بازهٔ 22 تا 30 ولت شارژ مجاز است.</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>Vin 20V و 31V</t>
         </is>
       </c>
-      <c r="G26" s="24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>در هر دو PWM=0 و INPUT_WAIT، فقط 22-30V شارژ</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>PASS: عدم شارژ خارج بازه. FAIL: شارژ خارج بازه</t>
         </is>
       </c>
-      <c r="K26" s="22" t="n"/>
-      <c r="L26" s="29" t="inlineStr">
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M26" s="22" t="n"/>
-      <c r="N26" s="22" t="n"/>
-      <c r="O26" s="24" t="inlineStr">
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P26" s="24" t="n"/>
-      <c r="Q26" s="25" t="inlineStr">
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>CH-038</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>حفظ THERMAL_REST در SafeIdle</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>کانال در استراحت حرارتی</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
-گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
-گام ۳: 2 ثانیه وضعیت را نگاه کن: باید THERMAL_REST حفظ شود، نه اینکه به OFF برود.
-گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>valid=false حین rest</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>THERMAL_REST حفظ نه OFF</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="30" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="n"/>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>کد بازبینی</t>
-        </is>
-      </c>
-      <c r="O27" s="19" t="inlineStr">
-        <is>
-          <t>thermal</t>
-        </is>
-      </c>
-      <c r="P27" s="19" t="n"/>
-      <c r="Q27" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>CH-039</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال (BULK)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
@@ -2706,297 +2497,297 @@
 گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>شارژ فعال + ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
         </is>
       </c>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M28" s="22" t="n"/>
-      <c r="N28" s="22" t="n"/>
-      <c r="O28" s="24" t="inlineStr">
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="24" t="inlineStr">
         <is>
           <t>2da0ed1</t>
         </is>
       </c>
-      <c r="P28" s="24" t="n"/>
-      <c r="Q28" s="25" t="inlineStr">
+      <c r="P25" s="24" t="n"/>
+      <c r="Q25" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="Q26" s="31">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="Q27" s="31">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="Q28" s="31">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="31">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="31">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="31">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="31">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="31">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="31">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="31">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="31">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="31">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="31">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="31">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="31">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="31">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="31">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="31">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="31">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="31">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="31">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="31">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="31">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="31">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="31">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="31">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="31">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="31">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="31">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="31">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="31">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="31">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="31">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="31">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="31">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="31">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="31">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="Q63" s="31">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="Q64" s="31">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="Q65" s="31">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="Q66" s="31">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="Q67" s="31">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="Q68" s="31">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q28"/>
+  <autoFilter ref="A4:Q65"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -3011,17 +2802,15 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId11"/>
+    <hyperlink ref="D6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E13" location="'برنامه تست'!A12"/>
+    <hyperlink ref="E14" location="'برنامه تست'!A12"/>
+    <hyperlink ref="E17" location="'برنامه تست'!A16"/>
+    <hyperlink ref="E18" location="'برنامه تست'!A16"/>
+    <hyperlink ref="E20" location="'برنامه تست'!A16"/>
+    <hyperlink ref="E21" location="'برنامه تست'!A16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3029,6 +2818,498 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="47" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>CH-001</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>نگاشت سخت‌افزار</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>برد خاموش</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
+گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
+گام ۳: بررسی کن رله وقتی سیم‌پیچش خاموش است وصل باشد (NC).
+گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>PA0=TIM2_CH1، PA6=TIM3_CH1، PA1/PA7 سنس، PB2/PB6 JIT، رله NC</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>نگاشت مطابق شماتیک؛ رله با coil خاموش وصل (NC)</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>نگاشت ثابت</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>PASS: تطابق کامل</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>CH-035</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
+گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
+گام ۳: duty هر دو کانال را نگاه کن: باید صفر بماند و شارژر safe-idle باشد.
+گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>safe-idle</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>duty=0 بدون overcurrent کاذب</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P6" s="24" t="n"/>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>CH-038</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>حفظ THERMAL_REST در SafeIdle</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>کانال در استراحت حرارتی</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
+گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
+گام ۳: 2 ثانیه وضعیت را نگاه کن: باید THERMAL_REST حفظ شود، نه اینکه به OFF برود.
+گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>valid=false حین rest</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>THERMAL_REST حفظ نه OFF</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t>کد بازبینی</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P7" s="19" t="n"/>
+      <c r="Q7" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="31">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="31">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="31">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="31">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="31">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="31">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="31">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="31">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="31">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="31">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="31">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="31">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="31">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="31">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="31">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="31">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="31">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="31">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="31">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="31">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q7"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E7" location="'برنامه تست'!A23"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3257,7 +3538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3384,7 +3665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3614,7 +3895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3746,7 +4027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -858,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -991,12 +994,12 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>CH-002</t>
+          <t>CH-004</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>پیش‌فرض امن بوت</t>
+          <t>تنظیم BULK</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -1006,158 +1009,10 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>باتری و ورودی ۲۴V وصل، بوت تازه</t>
+          <t>در BULK</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
-گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
-گام ۳: از پنل، پالس PWM و وضعیت (state) هر دو کانال را نگاه کن و زمان را از لحظهٔ بوت بگیر.
-گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>v_in=24V، هر دو v_bat≥12V</t>
-        </is>
-      </c>
-      <c r="G5" s="24" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>هر دو PWM صفر تا پایان گیت ۱۵ ثانیهٔ ثبات اتصال</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>حفظ تا شروع BULK</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>PWM=0 تا 15000±2000ms</t>
-        </is>
-      </c>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
-      <c r="O5" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="24" t="inlineStr"/>
-      <c r="Q5" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>CH-003</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>شروع BULK با رمپ</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>CH-002 پاس</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
-گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
-گام ۳: بعد از تمام شدن گیت 15 ثانیه‌ای ثبات، پله‌های duty را 20 ثانیه ضبط کن.
-گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>همان CH-002</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>20s</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>پله‌های duty از 10‰ صعودی</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-      <c r="O6" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P6" s="19" t="inlineStr"/>
-      <c r="Q6" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>CH-004</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>تنظیم BULK</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>در BULK</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز (باتری نیمه‌شارژ وصل باشد).
 گام ۲: در پنل، جریان تخمینی خروجی (Iest) همان کانال را باز کن.
@@ -1165,73 +1020,73 @@
 گام ۴: باید در باند 630 تا 650 میلی‌آمپر تثبیت شود و همان‌جا پایدار بماند.</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>باتری نیمه‌شارژ</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>Iest در باند 630..650mA تثبیت</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>نگه‌داشت باند</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>630≤Iest≤650 پایدار</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr"/>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr"/>
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>ولتاژ کانال به 14.3V می‌رسد</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده تا ولتاژ کانال به حدود 14.3 ولت برسد.
 گام ۲: ولتاژ باتری را از 14300 به‌آرامی تا 14600 میلی‌ولت بالا ببر (با منبع یا بار قابل تنظیم).
@@ -1239,73 +1094,73 @@
 گام ۴: وقتی از 14.6 ولت رد شد باید یک پلهٔ نزولی 0.5 درصدی ببینی؛ بازهٔ پایدار قابل قبول 14.35 تا 14.45 ولت است.</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>v_bat≈14300→14600mV</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>120s</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>تثبیت حدود 14.4V با پله ریز؛ عبور 14.6V پله نزولی 0.5٪</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>14.35..14.45V پایدار</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr"/>
-      <c r="N8" s="17" t="inlineStr"/>
-      <c r="O8" s="19" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr"/>
+      <c r="O6" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="19" t="inlineStr"/>
-      <c r="Q8" s="21" t="inlineStr">
+      <c r="P6" s="19" t="inlineStr"/>
+      <c r="Q6" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CH-006</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>شستشوی ABSORB</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>در ABSORB</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت ABSORB نگه دار.
 گام ۲: این سه شرط را زیر نظر بگیر: شستشوی کامل 10 دقیقه‌ای تمام شود، تیپر جریان زیر 50 میلی‌آمپر به مدت 60 ثانیه بماند، و سقف کلی 1 ساعت رد نشود.
@@ -1313,73 +1168,73 @@
 گام ۴: بعد از کامل شدن شستشو باید وضعیت FLOAT شود (state=3).</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>تا 3600s</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>ورود FLOAT بعد از شستشوی کامل</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>یک‌بار</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>state=3 بعد از شرط شستشو</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr"/>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr"/>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr"/>
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CH-007</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>FLOAT و reentry</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>در FLOAT</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت FLOAT نگه دار؛ duty باید پارک و صفر باشد.
 گام ۲: ولتاژ باتری را به زیر 12.8 ولت (12800 میلی‌ولت) بیاور.
@@ -1387,147 +1242,73 @@
 گام ۴: فقط وقتی زیر 12.8 ولت رفت باید برگردد به BULK (state=1) و آن هم با رمپ نرم از duty کم.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>v_bat&lt;12800mV</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>پارک روی duty صفر؛ reentry به BULK فقط زیر 12.8V</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>state=1 با رمپ نرم</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr"/>
+      <c r="N8" s="17" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="19" t="inlineStr"/>
-      <c r="Q10" s="21" t="inlineStr">
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>CH-008</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>خطای سخت جریان</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>CH-009</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>تریپ JIT اول</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>در BULK</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژ را در حالت BULK راه بینداز.
-گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
-گام ۳: همان لحظه گیت کانال را با اسکوپ یا پنل نگاه کن (در حد 1 ثانیه).
-گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>I_unfilt&gt;950mA</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>1s</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>ریست کانال (PWM صفر فوری و شروع دوباره)</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>لحظه‌ای</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="inlineStr">
-        <is>
-          <t>PWM=0 فوری</t>
-        </is>
-      </c>
-      <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="22" t="inlineStr"/>
-      <c r="N11" s="22" t="inlineStr"/>
-      <c r="O11" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="24" t="inlineStr"/>
-      <c r="Q11" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>CH-009</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>تریپ JIT اول</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
 گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
@@ -1535,73 +1316,73 @@
 گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>JIT falling (PB2/PB6)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>retry خودکار</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>state=5 → ریتری 50٪ duty قبل</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr"/>
-      <c r="N12" s="17" t="inlineStr"/>
-      <c r="O12" s="19" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="19" t="inlineStr"/>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CH-010</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>تریپ دوم همان کانال</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
 گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
@@ -1609,73 +1390,73 @@
 گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>ریتری دوم حداکثر 10٪ (100‰)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>duty≤100‰</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr"/>
-      <c r="N13" s="22" t="inlineStr"/>
-      <c r="O13" s="24" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr"/>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>CH-011</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>تریپ سوم FINAL</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>دو تریپ ثبت‌شده</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
 گام ۲: JIT را برای بار سوم تریپ کن.
@@ -1683,73 +1464,73 @@
 گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>latch دائمی تا ریبوت</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr"/>
-      <c r="N14" s="17" t="inlineStr"/>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="19" t="inlineStr"/>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: ولتاژ sense کانال را از بازه بیرون ببر: یک بار زیر 2000 میلی‌ولت و یک بار بالای 15000 میلی‌ولت.
@@ -1757,73 +1538,73 @@
 گام ۴: ولتاژ را به بازهٔ 2000 تا 15000 برگردان؛ PWM باید بعد از رفع خطا برگردد.</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>v_bat خارج 2000..15000mV</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر تا رفع</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>تا رفع شرط</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>PWM=0</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr"/>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr"/>
-      <c r="N15" s="22" t="inlineStr"/>
-      <c r="O15" s="24" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr"/>
+      <c r="N12" s="22" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr"/>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>پنل ESP وصل، ورودی ۲۴V</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پنل ESP را وصل کن و ورودی 24 ولت بده.
 گام ۲: پارامتر 19 را روی 1 بگذار و تأیید کن تا مود دستی فعال شود (با دیالوگ تأیید).
@@ -1831,73 +1612,73 @@
 گام ۴: در 5 ثانیه اول چک کن: وضعیت هر دو کانال 9 (state=9) شود و duty مستقیم و بدون رمپ روی 200 پرمیل بنشیند؛ در این مود توقف 14.4 ولت و BAT_LOST غیرفعال‌اند.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>ID19=1، ID16/18=200‰</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>state=9 هر دو کانال؛ duty مستقیم بدون رمپ؛ توقف 14.4V و BAT_LOST غیرفعال</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>duty فوری=200‰ هر دو</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr"/>
-      <c r="N16" s="17" t="inlineStr"/>
-      <c r="O16" s="19" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P16" s="19" t="inlineStr"/>
-      <c r="Q16" s="21" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>CH-014</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>مود دستی: ددمن لینک</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>گام ۱: شارژر را در مود دستی با duty فعال نگه دار (CH-013).
 گام ۲: لینک ESP را کامل قطع کن تا هیچ فریمی به برد نرسد.
@@ -1905,73 +1686,73 @@
 گام ۴: حداکثر تا 3000 میلی‌ثانیه باید هر دو duty خودکار صفر شوند و شارژر به حالت خودکار برگردد.</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>سکوت لینک</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>4s</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>خروج خودکار: هر دو duty صفر + بازگشت شارژر خودکار</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>duty=0 در ≤3000ms</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr"/>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="22" t="inlineStr"/>
-      <c r="N17" s="22" t="inlineStr"/>
-      <c r="O17" s="24" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="22" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr"/>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr"/>
+      <c r="Q14" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>CH-015</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>مود دستی: JIT و re-arm</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
 گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
@@ -1979,73 +1760,73 @@
 گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>JIT trip در مود دستی</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>پارک تا re-arm انسانی</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr"/>
-      <c r="N18" s="17" t="inlineStr"/>
-      <c r="O18" s="19" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P18" s="19" t="inlineStr"/>
-      <c r="Q18" s="21" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>CH-016</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>مود دستی: قطع 15V</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>در مود دستی، electronic load با clamp</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی، یک electronic load با clamp وصل کن.
 گام ۲: ولتاژ کانال را به 15.0 ولت (15000 میلی‌ولت) و بالاتر برسان.
@@ -2053,73 +1834,73 @@
 گام ۴: ولتاژ را زیر 15 ولت بیاور؛ شارژ باید خودکار ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>v_bat≥15000mV</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>duty صفر؛ با افت زیر 15V ادامهٔ خودکار</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>خودکار</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>PWM=0 بالای 15V و برگشت زیرش</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr"/>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr"/>
-      <c r="N19" s="22" t="inlineStr"/>
-      <c r="O19" s="24" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr"/>
+      <c r="N16" s="22" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P19" s="24" t="inlineStr"/>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>CH-017</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>مود دستی: قطع کانال</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی با هر دو کانال فعال باش (CH-013).
 گام ۲: پارامتر 11 را روی 0 بگذار (قطع کانال ۱).
@@ -2127,73 +1908,73 @@
 گام ۴: کانال ۲ نباید تغییری کرده باشد.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>ID11=0</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>duty کانال ۱ صفر؛ state همچنان 9</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>PWM1=0، state=9</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr"/>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr"/>
-      <c r="N20" s="17" t="inlineStr"/>
-      <c r="O20" s="19" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr"/>
+      <c r="N17" s="17" t="inlineStr"/>
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P20" s="19" t="inlineStr"/>
-      <c r="Q20" s="21" t="inlineStr">
+      <c r="P17" s="19" t="inlineStr"/>
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>CH-018</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی باش (CH-013).
 گام ۲: پارامتر 19 را از پنل روی 0 بگذار تا مود دستی خاموش شود.
@@ -2201,73 +1982,73 @@
 گام ۴: شارژر خودکار باید از OFF شروع کند، گیت 15 ثانیه‌ای ثبات را بگذراند و بعد وارد BULK شود.</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>ID19=0</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>هر دو duty صفر؛ شارژر خودکار از OFF با گیت ۱۵s دوباره</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>state≠9؛ settle→BULK</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr"/>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="22" t="inlineStr"/>
-      <c r="N21" s="22" t="inlineStr"/>
-      <c r="O21" s="24" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr"/>
+      <c r="N18" s="22" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P21" s="24" t="inlineStr"/>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="P18" s="24" t="inlineStr"/>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>CH-019</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>سقف duty زنده</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>گام ۱: پارامترهای 13 و 14 (سقف duty دو کانال) را روی 200 پرمیل بگذار.
 گام ۲: یکی‌یکی این مسیرها را امتحان کن: duty ثابت خودکار، duty دستی از پنل، و رمپ نرم شروع شارژ.
@@ -2275,73 +2056,73 @@
 گام ۴: در هیچ مسیری duty نباید از 200 پرمیل بالاتر برود.</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>ID13=200</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>همهٔ مسیرهای duty به سقف زمان-اجرا گیره می‌خورند</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>duty≤200‰ در همهٔ حالت‌ها</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr"/>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr"/>
-      <c r="N22" s="17" t="inlineStr"/>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr"/>
+      <c r="N19" s="17" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P22" s="19" t="inlineStr"/>
-      <c r="Q22" s="21" t="inlineStr">
+      <c r="P19" s="19" t="inlineStr"/>
+      <c r="Q19" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>CH-036</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>استراحت حرارتی 1h-&gt;10min</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>دو کانال BULK جریان ماکس 650mA</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در BULK با جریان نزدیک سقف (دست‌کم 600 میلی‌آمپر) راه بینداز.
 گام ۲: یک ساعت (70 دقیقه با حاشیه) بی‌وقفه شارژ کن و PWM هر دو کانال را زیر نظر بگیر.
@@ -2349,73 +2130,73 @@
 گام ۴: بعد از 10 دقیقه استراحت، شارژ باید خودش ادامه پیدا کند. اگر استراحت نیامد، تست رد است.</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>i&gt;=600 BULK 1h</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>70min</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>بعد 1h هر کانال 10min PWM=0 THERMAL_REST سپس ادامه</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>PASS: PWM صفر در استراحت + رله بسته. FAIL: عدم استراحت</t>
         </is>
       </c>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="29" t="inlineStr">
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M23" s="17" t="n"/>
-      <c r="N23" s="17" t="n"/>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P23" s="19" t="n"/>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="P20" s="19" t="n"/>
+      <c r="Q20" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>CH-037</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>ورودی خارج بازه 22-30V</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>Vin متغیر</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>گام ۱: منبع ورودی متغیر وصل کن و شارژ را در 24 ولت راه بینداز.
 گام ۲: ولتاژ ورودی را روی 20 ولت بگذار و 5 ثانیه نگاه کن: PWM باید صفر و وضعیت INPUT_WAIT باشد.
@@ -2423,371 +2204,293 @@
 گام ۴: به 24 ولت برگردان؛ شارژ باید برگردد. نتیجه: فقط در بازهٔ 22 تا 30 ولت شارژ مجاز است.</t>
         </is>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>Vin 20V و 31V</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>در هر دو PWM=0 و INPUT_WAIT، فقط 22-30V شارژ</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>PASS: عدم شارژ خارج بازه. FAIL: شارژ خارج بازه</t>
         </is>
       </c>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="29" t="inlineStr">
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="29" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="24" t="inlineStr">
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="24" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="25" t="inlineStr">
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="Q22" s="31">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="Q23" s="31">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="Q24" s="31">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>CH-039</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>شارژ فعال (BULK)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
-گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
-گام ۳: لحظهٔ پاک/نوشتن فلش را روی اسکوپ ببین: هر دو گیت PWM باید متوقف و خروجی صفر باشد.
-گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>شارژ فعال + ذخیرهٔ فلش</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
-        <is>
-          <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
-        <is>
-          <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="n"/>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="24" t="inlineStr">
-        <is>
-          <t>2da0ed1</t>
-        </is>
-      </c>
-      <c r="P25" s="24" t="n"/>
-      <c r="Q25" s="25" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="Q25" s="31">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="Q26" s="31">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="Q27" s="31">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="Q28" s="31">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="31">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="31">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="31">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="31">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="31">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="31">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="31">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="31">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="31">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="31">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="31">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="31">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="31">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="31">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="31">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="31">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="31">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="31">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="31">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="31">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="31">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="31">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="31">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="31">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="31">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="31">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="31">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="31">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="31">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="31">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="31">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="31">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="31">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="Q62" s="31">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="Q63" s="31">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="Q64" s="31">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="Q65" s="31">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q65"/>
+  <autoFilter ref="A4:Q61"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -2802,15 +2505,12 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E13" location="'برنامه تست'!A12"/>
-    <hyperlink ref="E14" location="'برنامه تست'!A12"/>
-    <hyperlink ref="E17" location="'برنامه تست'!A16"/>
-    <hyperlink ref="E18" location="'برنامه تست'!A16"/>
-    <hyperlink ref="E20" location="'برنامه تست'!A16"/>
-    <hyperlink ref="E21" location="'برنامه تست'!A16"/>
+    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
+    <hyperlink ref="E11" location="'برنامه تست'!A9"/>
+    <hyperlink ref="E14" location="'برنامه تست'!A13"/>
+    <hyperlink ref="E15" location="'برنامه تست'!A13"/>
+    <hyperlink ref="E17" location="'برنامه تست'!A13"/>
+    <hyperlink ref="E18" location="'برنامه تست'!A13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2818,6 +2518,574 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="47" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>CH-002</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>پیش‌فرض امن بوت</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>باتری و ورودی ۲۴V وصل، بوت تازه</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
+گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
+گام ۳: از پنل، پالس PWM و وضعیت (state) هر دو کانال را نگاه کن و زمان را از لحظهٔ بوت بگیر.
+گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>v_in=24V، هر دو v_bat≥12V</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>هر دو PWM صفر تا پایان گیت ۱۵ ثانیهٔ ثبات اتصال</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>حفظ تا شروع BULK</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>PWM=0 تا 15000±2000ms</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="n"/>
+      <c r="Q5" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>CH-003</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>شروع BULK با رمپ</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>CH-002 پاس</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
+گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
+گام ۳: بعد از تمام شدن گیت 15 ثانیه‌ای ثبات، پله‌های duty را 20 ثانیه ضبط کن.
+گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>همان CH-002</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>پله‌های duty از 10‰ صعودی</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="19" t="n"/>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>CH-008</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>خطای سخت جریان</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>در BULK</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ را در حالت BULK راه بینداز.
+گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
+گام ۳: همان لحظه گیت کانال را با اسکوپ یا پنل نگاه کن (در حد 1 ثانیه).
+گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>I_unfilt&gt;950mA</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>1s</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>ریست کانال (PWM صفر فوری و شروع دوباره)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>لحظه‌ای</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>PWM=0 فوری</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P7" s="24" t="n"/>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>CH-039</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>شارژ فعال (BULK)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
+گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
+گام ۳: لحظهٔ پاک/نوشتن فلش را روی اسکوپ ببین: هر دو گیت PWM باید متوقف و خروجی صفر باشد.
+گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>شارژ فعال + ذخیرهٔ فلش</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>2da0ed1</t>
+        </is>
+      </c>
+      <c r="P8" s="24" t="n"/>
+      <c r="Q8" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="31">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="31">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="31">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="31">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="31">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="31">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="31">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="31">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="31">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="31">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="31">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="31">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="31">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="31">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="31">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="31">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="31">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="31">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="31">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="31">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q8"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D6" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="E6" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="F6" location="'تست‌های آزمایشگاهی'!A5"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3302,14 +3570,14 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" location="'برنامه تست'!A23"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -3538,7 +3806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3665,7 +3933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3895,7 +4163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -4027,7 +4295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1009,40 +1009,39 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>در BULK</t>
+          <t>یک باتری نیمه‌خالی واقعی وصل است و برق شهر برقرار؛ آمپرمتر دستی یا پنل برای دیدن جریان آماده است</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را در حالت BULK راه بینداز (باتری نیمه‌شارژ وصل باشد).
-گام ۲: در پنل، جریان تخمینی خروجی (Iest) همان کانال را باز کن.
-گام ۳: 60 ثانیه مقدار Iest را نگاه کن.
-گام ۴: باید در باند 630 تا 650 میلی‌آمپر تثبیت شود و همان‌جا پایدار بماند.</t>
+          <t>گام ۱: شارژ را شروع کن و بگذار یک دقیقه جا بیفتد.
+گام ۲: جریان شارژ را از پنل یا آمپرمتر دستی بخوان.
+گام ۳: یک دقیقه دیگر نگاه کن که جریان ثابت مانده یا نه.</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>باتری نیمه‌شارژ</t>
+          <t>باتری نیمه‌خالی در حال شارژ</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>Iest در باند 630..650mA تثبیت</t>
+          <t>جریان شارژ نزدیک سقف تنظیم‌شده (حدود ۰٫۶۴ آمپر) می‌ایستد و پایدار می‌ماند؛ بالا و پایین نمی‌پرد</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>نگه‌داشت باند</t>
+          <t>پایدار تا وقتی باتری پرتر شود</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>630≤Iest≤650 پایدار</t>
+          <t>جریان پایدار نزدیک سقف = قبول؛ نوسان شدید یا جریان خیلی کمتر/بیشتر = رد</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr"/>
@@ -1083,40 +1082,38 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>ولتاژ کانال به 14.3V می‌رسد</t>
+          <t>باتری تقریباً پر است و شارژ ادامه دارد</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را ادامه بده تا ولتاژ کانال به حدود 14.3 ولت برسد.
-گام ۲: ولتاژ باتری را از 14300 به‌آرامی تا 14600 میلی‌ولت بالا ببر (با منبع یا بار قابل تنظیم).
-گام ۳: 120 ثانیه رفتار را نگاه کن: نزدیک 14.4 ولت باید با پله‌های ریز 0.1 درصدی تثبیت شود.
-گام ۴: وقتی از 14.6 ولت رد شد باید یک پلهٔ نزولی 0.5 درصدی ببینی؛ بازهٔ پایدار قابل قبول 14.35 تا 14.45 ولت است.</t>
+          <t>گام ۱: باتری نزدیک‌به‌پر را به شارژ نگه دار.
+گام ۲: ولتاژ باتری را با مولتی‌متر و جریان شارژ را با پنل زیر نظر بگیر.</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>v_bat≈14300→14600mV</t>
+          <t>باتری تقریباً پر در شارژ</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>120s</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>تثبیت حدود 14.4V با پله ریز؛ عبور 14.6V پله نزولی 0.5٪</t>
+          <t>ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود (شارژ ملایم پایانی)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تا رسیدن به حالت نگهداری</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>14.35..14.45V پایدار</t>
+          <t>ولتاژ ثابت با جریان رو به کاهش = قبول؛ بالا رفتن ولتاژ از حد شارژ = رد</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr"/>
@@ -1157,40 +1154,38 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>در ABSORB</t>
+          <t>باتری در شارژ پایانی (جذب) است</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را در حالت ABSORB نگه دار.
-گام ۲: این سه شرط را زیر نظر بگیر: شستشوی کامل 10 دقیقه‌ای تمام شود، تیپر جریان زیر 50 میلی‌آمپر به مدت 60 ثانیه بماند، و سقف کلی 1 ساعت رد نشود.
-گام ۳: وضعیت کانال را در پنل نگاه کن (حداکثر تا 3600 ثانیه).
-گام ۴: بعد از کامل شدن شستشو باید وضعیت FLOAT شود (state=3).</t>
+          <t>گام ۱: حین شارژ پایانی، یک مصرف کوتاه و واقعی از باتری بکش (مثلاً یک لامپ را چند ثانیه روشن کن) و بردار.
+گام ۲: رفتار شارژر را نگاه کن.</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مصرف کوتاه حین شارژ پایانی</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>تا 3600s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>ورود FLOAT بعد از شستشوی کامل</t>
+          <t>شارژر به شارژ تند برنمی‌گردد؛ همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>یک‌بار</t>
+          <t>بدون برگشت به شارژ تند</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>state=3 بعد از شرط شستشو</t>
+          <t>ادامهٔ همان شارژ پایانی = قبول؛ برگشتن به جریان کامل = رد</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr"/>
@@ -1231,40 +1226,39 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>در FLOAT</t>
+          <t>باتری کاملاً پر شده و شارژ به حالت نگهداری رسیده (جریان خیلی کم)</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را در حالت FLOAT نگه دار؛ duty باید پارک و صفر باشد.
-گام ۲: ولتاژ باتری را به زیر 12.8 ولت (12800 میلی‌ولت) بیاور.
-گام ۳: 30 ثانیه وضعیت را نگاه کن.
-گام ۴: فقط وقتی زیر 12.8 ولت رفت باید برگردد به BULK (state=1) و آن هم با رمپ نرم از duty کم.</t>
+          <t>گام ۱: بگذار باتری کامل پر و شارژ آرام شود.
+گام ۲: یک بار واقعی روی خروجی بکش تا باتری کمی خالی شود.
+گام ۳: نگاه کن شارژ دوباره کی و چطور شروع می‌شود.</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>v_bat&lt;12800mV</t>
+          <t>باتری پر، بعد کمی مصرف واقعی</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>پارک روی duty صفر؛ reentry به BULK فقط زیر 12.8V</t>
+          <t>در حالت پر، جریان نگهداری خیلی کم است؛ با کمی خالی‌شدن، شارژ خودش دوباره شروع می‌شود</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>رفت‌وبرگشت خودکار پر/شارژ</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>state=1 با رمپ نرم</t>
+          <t>شروع دوبارهٔ خودکار شارژ = قبول؛ شارژ نشدن دوباره یا شارژ دائمیِ پر = رد</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr"/>
@@ -1290,72 +1284,71 @@
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>CH-009</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>تریپ JIT اول</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+          <t>CH-012</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>اعتبار sense باتری</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>شارژ فعال</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
-گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
-گام ۳: 10 ثانیه رفتار را نگاه کن: PWM همان کانال باید صفر شود.
-گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>JIT falling (PB2/PB6)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>retry خودکار</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>state=5 → ریتری 50٪ duty قبل</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>دستگاه در حال شارژ یک باتری واقعی است</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ، سیم حس‌کردن ولتاژ باتری را جدا کن.
+گام ۲: به شارژر نگاه کن؛ نباید کورکورانه به شارژ ادامه دهد.
+گام ۳: سیم را وصل کن و برگشت شارژ را ببین.</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>قطع و وصل سیم حس ولتاژ باتری</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>با قطع سیم حس، شارژ متوقف می‌ماند؛ با وصل آن، شارژ عادی برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>توقف تا برگشت حس</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>توقف شارژ حین قطع حس = قبول؛ ادامهٔ شارژ بی‌حس = رد</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr"/>
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr"/>
+      <c r="Q9" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1364,72 +1357,71 @@
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>CH-010</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>ریتری دوم</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>تریپ دوم همان کانال</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
-گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
-گام ۳: 10 ثانیه duty را نگاه کن.
-گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>ریتری دوم حداکثر 10٪ (100‰)</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>duty≤100‰</t>
-        </is>
-      </c>
-      <c r="K10" s="22" t="inlineStr"/>
+          <t>CH-013</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>مود دستی: ورود</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>پنل وصل است و دستگاه روشن</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل مود تست دستی شارژر را روشن کن.
+گام ۲: نگاه کن شارژ خودکار کنار می‌رود و شارژر فقط به فرمان دستی گوش می‌دهد.
+گام ۳: یک فرمان دستی کوچک بده و اجراش را ببین.</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>روشن‌کردن مود دستی از پنل</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>شارژر وارد مود دستی می‌شود و فقط فرمان دستی را اجرا می‌کند</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>تا خروج از مود</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>ورود درست به مود دستی = قبول؛ ادامهٔ شارژ خودکار = رد</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1438,72 +1430,71 @@
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>CH-011</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>تریپ سوم FINAL</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
+          <t>CH-014</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>مود دستی: ددمن لینک</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>دو تریپ ثبت‌شده</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
-گام ۲: JIT را برای بار سوم تریپ کن.
-گام ۳: وضعیت و رله را چک کن: باید FINAL_FAULT باشد (state=7)، هر دو PWM صفر و رله باز.
-گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>latch دائمی تا ریبوت</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr"/>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>شارژر در مود تست دستی و در حال اجرای فرمان دستی است</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>گام ۱: کابل ارتباطی پنل (ESP) را بکش تا فرمان تازه‌ای نرسد.
+گام ۲: کرنومتر بگیر و شارژر را نگاه کن.
+گام ۳: کابل را وصل کن.</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>قطع ارتباط پنل حین مود دستی</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>بعد از چند ثانیه بی‌ارتباطی، شارژ دستی خودش متوقف می‌شود؛ نباید بی‌صاحب ادامه دهد</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>توقف خودکار با قطع ارتباط</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>توقف خودکار = قبول؛ ادامهٔ شارژ بی‌ارتباط = رد</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr"/>
+      <c r="N11" s="22" t="inlineStr"/>
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="P11" s="24" t="inlineStr"/>
+      <c r="Q11" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1512,12 +1503,12 @@
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>CH-012</t>
+          <t>CH-016</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>اعتبار sense باتری</t>
+          <t>مود دستی: قطع 15V</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -1527,40 +1518,39 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>شارژ فعال</t>
+          <t>شارژر در مود تست دستی در حال کار است</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ فعال باشد.
-گام ۲: ولتاژ sense کانال را از بازه بیرون ببر: یک بار زیر 2000 میلی‌ولت و یک بار بالای 15000 میلی‌ولت.
-گام ۳: در هر دو حالت (در حد 1 ثانیه) گیت را نگاه کن: PWM همان کانال باید صفر شود.
-گام ۴: ولتاژ را به بازهٔ 2000 تا 15000 برگردان؛ PWM باید بعد از رفع خطا برگردد.</t>
+          <t>گام ۱: برق طبقهٔ قدرت شارژر را قطع کن (همان کاری که در تعمیرات می‌کنی).
+گام ۲: رفتار کانال را ببین.
+گام ۳: برق را برگردان.</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>v_bat خارج 2000..15000mV</t>
+          <t>قطع و وصل برق طبقهٔ قدرت در مود دستی</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>1s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>PWM همان کانال صفر تا رفع</t>
+          <t>کانال همان لحظه بیکار و بی‌خطر می‌شود و با برگشت برق، رفتار عادی برمی‌گردد</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>تا رفع شرط</t>
+          <t>بدون قفل اضافه</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>PWM=0</t>
+          <t>بیکار شدن فوری و برگشت تمیز = قبول؛ رفتار غیرعادی = رد</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr"/>
@@ -1586,55 +1576,54 @@
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>CH-013</t>
+          <t>CH-017</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>مود دستی: ورود</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>مود دستی: قطع کانال</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>پنل ESP وصل، ورودی ۲۴V</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: پنل ESP را وصل کن و ورودی 24 ولت بده.
-گام ۲: پارامتر 19 را روی 1 بگذار و تأیید کن تا مود دستی فعال شود (با دیالوگ تأیید).
-گام ۳: برای پارامترهای 16 و 18 مقدار 200 پرمیل duty بده.
-گام ۴: در 5 ثانیه اول چک کن: وضعیت هر دو کانال 9 (state=9) شود و duty مستقیم و بدون رمپ روی 200 پرمیل بنشیند؛ در این مود توقف 14.4 ولت و BAT_LOST غیرفعال‌اند.</t>
+          <t>هر دو کانال شارژر در مود دستی در حال کارند (دو باتری وصل)</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل فقط یک کانال را خاموش کن.
+گام ۲: هر دو کانال را نگاه کن.
+گام ۳: کانال خاموش را دوباره روشن کن.</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>ID19=1، ID16/18=200‰</t>
+          <t>خاموش/روشن کردن یک کانال از پنل</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>state=9 هر دو کانال؛ duty مستقیم بدون رمپ؛ توقف 14.4V و BAT_LOST غیرفعال</t>
+          <t>فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>تا خروج از مود</t>
+          <t>استقلال دو کانال</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>duty فوری=200‰ هر دو</t>
+          <t>استقلال کامل = قبول؛ اثر روی کانال دیگر = رد</t>
         </is>
       </c>
       <c r="K13" s="17" t="inlineStr"/>
@@ -1660,12 +1649,12 @@
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>CH-014</t>
+          <t>CH-018</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>مود دستی: ددمن لینک</t>
+          <t>خروج از مود دستی</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -1675,40 +1664,38 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>در مود دستی</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژر را در مود دستی با duty فعال نگه دار (CH-013).
-گام ۲: لینک ESP را کامل قطع کن تا هیچ فریمی به برد نرسد.
-گام ۳: از زمان قطع لینک، حداکثر 4 ثانیه duty هر دو کانال را نگاه کن.
-گام ۴: حداکثر تا 3000 میلی‌ثانیه باید هر دو duty خودکار صفر شوند و شارژر به حالت خودکار برگردد.</t>
+          <t>شارژر در مود تست دستی است</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل از مود دستی خارج شو.
+گام ۲: یک باتری نیمه‌خالی را زیر نظر بگیر.</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>سکوت لینک</t>
+          <t>خروج از مود دستی</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>4s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>خروج خودکار: هر دو duty صفر + بازگشت شارژر خودکار</t>
+          <t>شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>برگشت به خودکار</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>duty=0 در ≤3000ms</t>
+          <t>شروع شارژ خودکار = قبول؛ ماندن در مود دستی = رد</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr"/>
@@ -1734,55 +1721,54 @@
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>CH-015</t>
+          <t>CH-019</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>مود دستی: JIT و re-arm</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>سقف duty زنده</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>در مود دستی</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
-گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
-گام ۳: از پنل همان duty را دوباره برای کانال بفرست؛ کانال باید دوباره مسلح شود و درایو برگردد.
-گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
+          <t>دستگاه در حال شارژ یک باتری نیمه‌خالی است</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل سقف توان شارژ را کمتر کن.
+گام ۲: جریان شارژ را در پنل یا آمپرمتر ببین.
+گام ۳: سقف را به حالت اول برگردان.</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>JIT trip در مود دستی</t>
+          <t>کم و زیاد کردن سقف توان از پنل</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>15s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
+          <t>جریان شارژ به همان نسبت کم و زیاد می‌شود، بدون اینکه دستگاه خاموش یا خطادار شود</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>پارک تا re-arm انسانی</t>
+          <t>بدون قفل</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
+          <t>دنبال‌کردن جریان از سقف = قبول؛ بی‌اثر بودن سقف = رد</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr"/>
@@ -1808,160 +1794,160 @@
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>CH-016</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>مود دستی: قطع 15V</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+          <t>CH-036</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>استراحت حرارتی 1h-&gt;10min</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>در مود دستی، electronic load با clamp</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: در مود دستی، یک electronic load با clamp وصل کن.
-گام ۲: ولتاژ کانال را به 15.0 ولت (15000 میلی‌ولت) و بالاتر برسان.
-گام ۳: 5 ثانیه نگاه کن: بالای 15 ولت duty باید صفر باشد.
-گام ۴: ولتاژ را زیر 15 ولت بیاور؛ شارژ باید خودکار ادامه پیدا کند.</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>v_bat≥15000mV</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>duty صفر؛ با افت زیر 15V ادامهٔ خودکار</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>خودکار</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
-        <is>
-          <t>PWM=0 بالای 15V و برگشت زیرش</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr"/>
-      <c r="N16" s="22" t="inlineStr"/>
-      <c r="O16" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="24" t="inlineStr"/>
-      <c r="Q16" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>دو باتری خالی واقعی وصل و هر دو کانال آمادهٔ شارژ سنگین‌اند</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: هر دو کانال را با باتری خالی به شارژ بزن.
+گام ۲: حدود یک ساعت شارژ سنگین را زیر نظر بگیر (هر از چندی سر بزن).
+گام ۳: بعد از حدود یک ساعت، هر کانال باید حدود ده دقیقه استراحت کند: جریان صفر ولی باتری وصل می‌ماند.
+گام ۴: بعد از استراحت، شارژ باید خودش ادامه پیدا کند.</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>یک ساعت شارژ سنگین هر دو کانال</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>حدود یک ساعت و نیم</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>بعد از یک ساعت شارژ سنگین، هر کانال ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>استراحت و ادامهٔ خودکار</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>استراحت و ادامهٔ خودکار = قبول؛ شارژ بی‌وقفهٔ چندساعته یا توقف همیشگی = رد</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="29" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P16" s="19" t="n"/>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>CH-017</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>مود دستی: قطع کانال</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>در مود دستی</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: در مود دستی با هر دو کانال فعال باش (CH-013).
-گام ۲: پارامتر 11 را روی 0 بگذار (قطع کانال ۱).
-گام ۳: 2 ثانیه نگاه کن: duty کانال ۱ باید صفر شود ولی وضعیت همچنان 9 (state=9) بماند.
-گام ۴: کانال ۲ نباید تغییری کرده باشد.</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>ID11=0</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>duty کانال ۱ صفر؛ state همچنان 9</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>PWM1=0، state=9</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr"/>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr"/>
-      <c r="N17" s="17" t="inlineStr"/>
-      <c r="O17" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P17" s="19" t="inlineStr"/>
-      <c r="Q17" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+          <t>CH-037</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>ورودی خارج بازه 22-30V</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>ورودی از منبع آزمایشگاهی می‌آید تا ولتاژش را عوض کنی؛ باتری وصل است</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ ورودی را زیر ۲۲ ولت بیاور؛ شارژ نباید شروع شود.
+گام ۲: به ۲۴ ولت برگردان؛ شارژ باید شروع شود.
+گام ۳: ولتاژ را بالای ۳۰ ببر؛ شارژ باید بایستد.
+گام ۴: به ۲۴ برگردان؛ شارژ باید خودش برگردد.</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>ورودی: پایین، ۲۴، بالا، ۲۴ ولت</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>خارج از بازهٔ سالم شارژ نداریم و با برگشت ورودی به ۲۴ ولت شارژ خودش برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>بدون قفل</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>همین رفتار چهار مرحله = قبول؛ شارژ خارج از بازه یا برنگشتن = رد</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="24" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P17" s="24" t="n"/>
+      <c r="Q17" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>CH-018</t>
+          <t>CH-040</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>خروج از مود دستی</t>
+          <t>سناریوی ۶: باتری خراب دیگر شارژ نمی‌شود</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -1971,520 +1957,351 @@
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>در مود دستی</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>گام ۱: در مود دستی باش (CH-013).
-گام ۲: پارامتر 19 را از پنل روی 0 بگذار تا مود دستی خاموش شود.
-گام ۳: 20 ثانیه نگاه کن: هر دو duty صفر شوند و وضعیت از 9 خارج شود (state≠9).
-گام ۴: شارژر خودکار باید از OFF شروع کند، گیت 15 ثانیه‌ای ثبات را بگذراند و بعد وارد BULK شود.</t>
+          <t>از پنل زمان سناریوی باتری خراب (شناسهٔ ۱۲۵) را موقتاً روی چند دقیقه بگذار؛ یک باتری خالی وصل است</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت به شارژ کامل برسد.
+گام ۲: بعد از گذشت زمان تنظیم‌شده، ببین شارژ همان کانال متوقف شده و قرمز ثابت آمده.
+گام ۳: برق را قطع و وصل کن؛ شارژ آن باتری نباید دوباره شروع شود.
+گام ۴: باتری را با سالم عوض کن؛ شارژ باید عادی شروع شود.
+گام ۵: شناسهٔ ۱۲۵ را به مقدار واقعی (یک شبانه‌روز) برگردان.</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>ID19=0</t>
+          <t>شارژ باتری خالی با زمان کوتاه‌شده</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>هر دو duty صفر؛ شارژر خودکار از OFF با گیت ۱۵s دوباره</t>
+          <t>بعد از زمان، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>قفل تا تعویض باتری</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>state≠9؛ settle→BULK</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr">
+          <t>توقف ماندگار و شروع با باتری سالم = قبول؛ شارژ دوبارهٔ همان باتری = رد</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr"/>
-      <c r="N18" s="22" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P18" s="24" t="inlineStr"/>
-      <c r="Q18" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="25">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>CH-019</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>سقف duty زنده</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: پارامترهای 13 و 14 (سقف duty دو کانال) را روی 200 پرمیل بگذار.
-گام ۲: یکی‌یکی این مسیرها را امتحان کن: duty ثابت خودکار، duty دستی از پنل، و رمپ نرم شروع شارژ.
-گام ۳: در هر مسیر 10 ثانیه duty واقعی گیت را با اسکوپ یا پنل بخوان.
-گام ۴: در هیچ مسیری duty نباید از 200 پرمیل بالاتر برود.</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>ID13=200</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>همهٔ مسیرهای duty به سقف زمان-اجرا گیره می‌خورند</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>duty≤200‰ در همهٔ حالت‌ها</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr"/>
-      <c r="L19" s="20" t="inlineStr">
+          <t>CH-041</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>خطای ۷: کانال بی‌جریان قفل فنی می‌سازد</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>دستگاه در حال شارژ است و فیوز خروجی هر کانال را می‌شناسی</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: فیوز خروجی یک کانال را دربیاور.
+گام ۲: چند ثانیه صبر کن: شارژ کلاً باید قفل شود و هر سه چراغ با هم چشمک بزنند.
+گام ۳: فیوز را جا بزن؛ درست نباید بشود.
+گام ۴: خاموش و روشن کن؛ شارژ عادی باید برگردد.</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>دربیاوردن فیوز یک کانال حین شارژ</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>خطای فنی ۷ قفل می‌شود و فقط با خاموش/روشن پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>قفل تا ریست</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>قفل فنی و پاک‌شدن فقط با ریست = قبول؛ ادامهٔ شارژ بی‌جریان = رد</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="29" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr"/>
-      <c r="N19" s="17" t="inlineStr"/>
-      <c r="O19" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P19" s="19" t="inlineStr"/>
-      <c r="Q19" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="25">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>CH-036</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>استراحت حرارتی 1h-&gt;10min</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>دو کانال BULK جریان ماکس 650mA</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: هر دو کانال را در BULK با جریان نزدیک سقف (دست‌کم 600 میلی‌آمپر) راه بینداز.
-گام ۲: یک ساعت (70 دقیقه با حاشیه) بی‌وقفه شارژ کن و PWM هر دو کانال را زیر نظر بگیر.
-گام ۳: بعد از 1 ساعت شارژ سنگین، هر کانال باید 10 دقیقه استراحت حرارتی برود: PWM صفر ولی رله بسته می‌ماند.
-گام ۴: بعد از 10 دقیقه استراحت، شارژ باید خودش ادامه پیدا کند. اگر استراحت نیامد، تست رد است.</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>i&gt;=600 BULK 1h</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>70min</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>بعد 1h هر کانال 10min PWM=0 THERMAL_REST سپس ادامه</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>PASS: PWM صفر در استراحت + رله بسته. FAIL: عدم استراحت</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n"/>
-      <c r="L20" s="29" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="17" t="n"/>
-      <c r="O20" s="19" t="inlineStr">
-        <is>
-          <t>thermal</t>
-        </is>
-      </c>
-      <c r="P20" s="19" t="n"/>
-      <c r="Q20" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q20" s="31">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>CH-037</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>ورودی خارج بازه 22-30V</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Vin متغیر</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: منبع ورودی متغیر وصل کن و شارژ را در 24 ولت راه بینداز.
-گام ۲: ولتاژ ورودی را روی 20 ولت بگذار و 5 ثانیه نگاه کن: PWM باید صفر و وضعیت INPUT_WAIT باشد.
-گام ۳: ولتاژ را روی 31 ولت بگذار و 5 ثانیه نگاه کن: باز هم PWM صفر و INPUT_WAIT.
-گام ۴: به 24 ولت برگردان؛ شارژ باید برگردد. نتیجه: فقط در بازهٔ 22 تا 30 ولت شارژ مجاز است.</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Vin 20V و 31V</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>در هر دو PWM=0 و INPUT_WAIT، فقط 22-30V شارژ</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>PASS: عدم شارژ خارج بازه. FAIL: شارژ خارج بازه</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="29" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="24" t="inlineStr">
-        <is>
-          <t>thermal</t>
-        </is>
-      </c>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="25" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q21" s="31">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="Q22" s="31">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="Q23" s="31">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
       <c r="Q24" s="31">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
       <c r="Q25" s="31">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="Q26" s="31">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="Q27" s="31">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="Q28" s="31">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="31">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="31">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="31">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="31">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="31">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="31">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="31">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="31">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="31">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="31">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="31">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="31">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="31">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="31">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="31">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="31">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="31">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="31">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="31">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="31">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="31">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="31">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="31">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="31">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="31">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="31">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="31">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="31">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="31">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="Q58" s="31">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="Q59" s="31">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="Q60" s="31">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Q61" s="31">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
@@ -2504,14 +2321,6 @@
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
-    <hyperlink ref="E11" location="'برنامه تست'!A9"/>
-    <hyperlink ref="E14" location="'برنامه تست'!A13"/>
-    <hyperlink ref="E15" location="'برنامه تست'!A13"/>
-    <hyperlink ref="E17" location="'برنامه تست'!A13"/>
-    <hyperlink ref="E18" location="'برنامه تست'!A13"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2949,25 +2758,293 @@
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="31">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>CH-009</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>تریپ JIT اول</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>شارژ فعال</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
+گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
+گام ۳: 10 ثانیه رفتار را نگاه کن: PWM همان کانال باید صفر شود.
+گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>JIT falling (PB2/PB6)</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>retry خودکار</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>state=5 → ریتری 50٪ duty قبل</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="19" t="n"/>
+      <c r="Q9" s="21">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="31">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>CH-010</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>ریتری دوم</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>تریپ دوم همان کانال</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
+گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
+گام ۳: 10 ثانیه duty را نگاه کن.
+گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>ریتری دوم حداکثر 10٪ (100‰)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>duty≤100‰</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="24" t="n"/>
+      <c r="Q10" s="25">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="31">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>CH-011</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>تریپ سوم FINAL</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>دو تریپ ثبت‌شده</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
+گام ۲: JIT را برای بار سوم تریپ کن.
+گام ۳: وضعیت و رله را چک کن: باید FINAL_FAULT باشد (state=7)، هر دو PWM صفر و رله باز.
+گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>latch دائمی تا ریبوت</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P11" s="19" t="n"/>
+      <c r="Q11" s="21">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="31">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>CH-015</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>مود دستی: JIT و re-arm</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>در مود دستی</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
+گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
+گام ۳: از پنل همان duty را دوباره برای کانال بفرست؛ کانال باید دوباره مسلح شود و درایو برگردد.
+گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>JIT trip در مود دستی</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>15s</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>پارک تا re-arm انسانی</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P12" s="19" t="n"/>
+      <c r="Q12" s="21">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -3079,6 +3156,9 @@
     <hyperlink ref="D6" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink ref="E6" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink ref="F6" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="E10" location="'تست‌های آزمایشگاهی'!A9"/>
+    <hyperlink ref="E11" location="'تست‌های آزمایشگاهی'!A9"/>
+    <hyperlink ref="E12" location="'برنامه تست'!A10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3570,7 +3650,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" location="'برنامه تست'!A20"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,51 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="10">
@@ -276,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -400,6 +445,87 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -773,62 +899,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Charger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>Charger | دو شارژر مستقل ۱۲V؛ Ch1→باتری بالا (VHIGH)، Ch2→باتری پایین (VLOW)؛ پارامترهای زندهٔ ESP + مود تست دستی v1.2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="50" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>سناریوها حول رفتار قابل مشاهدهٔ هر کانال: state (تله‌متری ESP)، duty (اسکوپ PA0/PA6)، رلهٔ NC و پنل ESP نوشته شده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>ثابت‌های مرجع در charger.h: باند تنظیم 630..650mA تخمینی، خطای سخت 950mA، ابزورب 14.3/14.4/14.6V، فلوت 13.5V، reentry 12.8V، سقف duty 500‰، ددمن مود دستی 3000ms.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>تست مود دستی فقط با بار مقاومتی یا electronic load با voltage clamp؛ مقاومت آزاد شبیه‌ساز باتری نیست و منبع ورودی باید محدودشده باشد.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="50" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>هشدار: تست مود دستی بدون باتری فقط با electronic load دارای voltage clamp؛ هرگز با مقاومت آزاد.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>هشدار: منبع ورودی در تست‌های اول محدودشده باشد؛ current-limit ورودی جای حفاظت خروجی firmware نیست.</t>
         </is>
@@ -884,935 +1010,983 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Charger</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+      <c r="I1" s="54" t="n"/>
+      <c r="J1" s="54" t="n"/>
+      <c r="K1" s="54" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+      <c r="N1" s="54" t="n"/>
+      <c r="O1" s="54" t="n"/>
+      <c r="P1" s="54" t="n"/>
+      <c r="Q1" s="54" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="54" t="n"/>
+      <c r="P2" s="54" t="n"/>
+      <c r="Q2" s="54" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="51" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="51" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="51" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="51" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="51" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="51" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="51" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="51" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>CH-004</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>تنظیم BULK</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>یک باتری نیمه‌خالی واقعی وصل است و برق شهر برقرار؛ آمپرمتر دستی یا پنل برای دیدن جریان آماده است</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="56" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را شروع کن و بگذار یک دقیقه جا بیفتد.
 گام ۲: جریان شارژ را از پنل یا آمپرمتر دستی بخوان.
 گام ۳: یک دقیقه دیگر نگاه کن که جریان ثابت مانده یا نه.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
         <is>
           <t>باتری نیمه‌خالی در حال شارژ</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>جریان شارژ نزدیک سقف تنظیم‌شده (حدود ۰٫۶۴ آمپر) می‌ایستد و پایدار می‌ماند؛ بالا و پایین نمی‌پرد</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>پایدار تا وقتی باتری پرتر شود</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="56" t="inlineStr">
         <is>
           <t>جریان پایدار نزدیک سقف = قبول؛ نوسان شدید یا جریان خیلی کمتر/بیشتر = رد</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="56" t="inlineStr"/>
+      <c r="L5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="56" t="inlineStr"/>
+      <c r="N5" s="56" t="inlineStr"/>
+      <c r="O5" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="24" t="inlineStr"/>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="P5" s="58" t="inlineStr"/>
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>باتری تقریباً پر است و شارژ ادامه دارد</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>گام ۱: باتری نزدیک‌به‌پر را به شارژ نگه دار.
 گام ۲: ولتاژ باتری را با مولتی‌متر و جریان شارژ را با پنل زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="63" t="inlineStr">
         <is>
           <t>باتری تقریباً پر در شارژ</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="63" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود (شارژ ملایم پایانی)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="61" t="inlineStr">
         <is>
           <t>تا رسیدن به حالت نگهداری</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="61" t="inlineStr">
         <is>
           <t>ولتاژ ثابت با جریان رو به کاهش = قبول؛ بالا رفتن ولتاژ از حد شارژ = رد</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="61" t="inlineStr"/>
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="M6" s="61" t="inlineStr"/>
+      <c r="N6" s="61" t="inlineStr"/>
+      <c r="O6" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="19" t="inlineStr"/>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="P6" s="63" t="inlineStr"/>
+      <c r="Q6" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>CH-006</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>شستشوی ABSORB</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>باتری در شارژ پایانی (جذب) است</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="56" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ پایانی، یک مصرف کوتاه و واقعی از باتری بکش (مثلاً یک لامپ را چند ثانیه روشن کن) و بردار.
 گام ۲: رفتار شارژر را نگاه کن.</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>مصرف کوتاه حین شارژ پایانی</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>شارژر به شارژ تند برنمی‌گردد؛ همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>بدون برگشت به شارژ تند</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="56" t="inlineStr">
         <is>
           <t>ادامهٔ همان شارژ پایانی = قبول؛ برگشتن به جریان کامل = رد</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K7" s="56" t="inlineStr"/>
+      <c r="L7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="M7" s="56" t="inlineStr"/>
+      <c r="N7" s="56" t="inlineStr"/>
+      <c r="O7" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr"/>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="P7" s="58" t="inlineStr"/>
+      <c r="Q7" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>CH-007</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>FLOAT و reentry</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>باتری کاملاً پر شده و شارژ به حالت نگهداری رسیده (جریان خیلی کم)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>گام ۱: بگذار باتری کامل پر و شارژ آرام شود.
 گام ۲: یک بار واقعی روی خروجی بکش تا باتری کمی خالی شود.
 گام ۳: نگاه کن شارژ دوباره کی و چطور شروع می‌شود.</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="63" t="inlineStr">
         <is>
           <t>باتری پر، بعد کمی مصرف واقعی</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="63" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="61" t="inlineStr">
         <is>
           <t>در حالت پر، جریان نگهداری خیلی کم است؛ با کمی خالی‌شدن، شارژ خودش دوباره شروع می‌شود</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="61" t="inlineStr">
         <is>
           <t>رفت‌وبرگشت خودکار پر/شارژ</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="61" t="inlineStr">
         <is>
           <t>شروع دوبارهٔ خودکار شارژ = قبول؛ شارژ نشدن دوباره یا شارژ دائمیِ پر = رد</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="61" t="inlineStr"/>
+      <c r="L8" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr"/>
-      <c r="N8" s="17" t="inlineStr"/>
-      <c r="O8" s="19" t="inlineStr">
+      <c r="M8" s="61" t="inlineStr"/>
+      <c r="N8" s="61" t="inlineStr"/>
+      <c r="O8" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="19" t="inlineStr"/>
-      <c r="Q8" s="21" t="inlineStr">
+      <c r="P8" s="63" t="inlineStr"/>
+      <c r="Q8" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ یک باتری واقعی است</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ، سیم حس‌کردن ولتاژ باتری را جدا کن.
 گام ۲: به شارژر نگاه کن؛ نباید کورکورانه به شارژ ادامه دهد.
 گام ۳: سیم را وصل کن و برگشت شارژ را ببین.</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>قطع و وصل سیم حس ولتاژ باتری</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>با قطع سیم حس، شارژ متوقف می‌ماند؛ با وصل آن، شارژ عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="56" t="inlineStr">
         <is>
           <t>توقف تا برگشت حس</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J9" s="56" t="inlineStr">
         <is>
           <t>توقف شارژ حین قطع حس = قبول؛ ادامهٔ شارژ بی‌حس = رد</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K9" s="56" t="inlineStr"/>
+      <c r="L9" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr"/>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="M9" s="56" t="inlineStr"/>
+      <c r="N9" s="56" t="inlineStr"/>
+      <c r="O9" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr"/>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="P9" s="58" t="inlineStr"/>
+      <c r="Q9" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>پنل وصل است و دستگاه روشن</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از پنل مود تست دستی شارژر را روشن کن.
 گام ۲: نگاه کن شارژ خودکار کنار می‌رود و شارژر فقط به فرمان دستی گوش می‌دهد.
 گام ۳: یک فرمان دستی کوچک بده و اجراش را ببین.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="63" t="inlineStr">
         <is>
           <t>روشن‌کردن مود دستی از پنل</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="63" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="61" t="inlineStr">
         <is>
           <t>شارژر وارد مود دستی می‌شود و فقط فرمان دستی را اجرا می‌کند</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="61" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>ورود درست به مود دستی = قبول؛ ادامهٔ شارژ خودکار = رد</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K10" s="61" t="inlineStr"/>
+      <c r="L10" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="M10" s="61" t="inlineStr"/>
+      <c r="N10" s="61" t="inlineStr"/>
+      <c r="O10" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="19" t="inlineStr"/>
-      <c r="Q10" s="21" t="inlineStr">
+      <c r="P10" s="63" t="inlineStr"/>
+      <c r="Q10" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>CH-014</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>مود دستی: ددمن لینک</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>شارژر در مود تست دستی و در حال اجرای فرمان دستی است</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="65" t="inlineStr">
         <is>
           <t>گام ۱: کابل ارتباطی پنل (ESP) را بکش تا فرمان تازه‌ای نرسد.
 گام ۲: کرنومتر بگیر و شارژر را نگاه کن.
 گام ۳: کابل را وصل کن.</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>قطع ارتباط پنل حین مود دستی</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr">
         <is>
           <t>بعد از چند ثانیه بی‌ارتباطی، شارژ دستی خودش متوقف می‌شود؛ نباید بی‌صاحب ادامه دهد</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="56" t="inlineStr">
         <is>
           <t>توقف خودکار با قطع ارتباط</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="J11" s="56" t="inlineStr">
         <is>
           <t>توقف خودکار = قبول؛ ادامهٔ شارژ بی‌ارتباط = رد</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K11" s="56" t="inlineStr"/>
+      <c r="L11" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr"/>
-      <c r="N11" s="22" t="inlineStr"/>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="M11" s="56" t="inlineStr"/>
+      <c r="N11" s="56" t="inlineStr"/>
+      <c r="O11" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr"/>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="P11" s="58" t="inlineStr"/>
+      <c r="Q11" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>CH-016</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>مود دستی: قطع 15V</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="56" t="inlineStr">
         <is>
           <t>شارژر در مود تست دستی در حال کار است</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="56" t="inlineStr">
         <is>
           <t>گام ۱: برق طبقهٔ قدرت شارژر را قطع کن (همان کاری که در تعمیرات می‌کنی).
 گام ۲: رفتار کانال را ببین.
 گام ۳: برق را برگردان.</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="58" t="inlineStr">
         <is>
           <t>قطع و وصل برق طبقهٔ قدرت در مود دستی</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="56" t="inlineStr">
         <is>
           <t>کانال همان لحظه بیکار و بی‌خطر می‌شود و با برگشت برق، رفتار عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="56" t="inlineStr">
         <is>
           <t>بدون قفل اضافه</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="56" t="inlineStr">
         <is>
           <t>بیکار شدن فوری و برگشت تمیز = قبول؛ رفتار غیرعادی = رد</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K12" s="56" t="inlineStr"/>
+      <c r="L12" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="M12" s="56" t="inlineStr"/>
+      <c r="N12" s="56" t="inlineStr"/>
+      <c r="O12" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="P12" s="58" t="inlineStr"/>
+      <c r="Q12" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>CH-017</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>مود دستی: قطع کانال</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>هر دو کانال شارژر در مود دستی در حال کارند (دو باتری وصل)</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="66" t="inlineStr">
         <is>
           <t>گام ۱: از پنل فقط یک کانال را خاموش کن.
 گام ۲: هر دو کانال را نگاه کن.
 گام ۳: کانال خاموش را دوباره روشن کن.</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="63" t="inlineStr">
         <is>
           <t>خاموش/روشن کردن یک کانال از پنل</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="63" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="61" t="inlineStr">
         <is>
           <t>فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="61" t="inlineStr">
         <is>
           <t>استقلال دو کانال</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="61" t="inlineStr">
         <is>
           <t>استقلال کامل = قبول؛ اثر روی کانال دیگر = رد</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="K13" s="61" t="inlineStr"/>
+      <c r="L13" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="M13" s="61" t="inlineStr"/>
+      <c r="N13" s="61" t="inlineStr"/>
+      <c r="O13" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="19" t="inlineStr"/>
-      <c r="Q13" s="21" t="inlineStr">
+      <c r="P13" s="63" t="inlineStr"/>
+      <c r="Q13" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>CH-018</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="56" t="inlineStr">
         <is>
           <t>شارژر در مود تست دستی است</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="56" t="inlineStr">
         <is>
           <t>گام ۱: از پنل از مود دستی خارج شو.
 گام ۲: یک باتری نیمه‌خالی را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="56" t="inlineStr">
         <is>
           <t>شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="56" t="inlineStr">
         <is>
           <t>برگشت به خودکار</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J14" s="56" t="inlineStr">
         <is>
           <t>شروع شارژ خودکار = قبول؛ ماندن در مود دستی = رد</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K14" s="56" t="inlineStr"/>
+      <c r="L14" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="M14" s="56" t="inlineStr"/>
+      <c r="N14" s="56" t="inlineStr"/>
+      <c r="O14" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="P14" s="58" t="inlineStr"/>
+      <c r="Q14" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>CH-019</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>سقف duty زنده</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ یک باتری نیمه‌خالی است</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از پنل سقف توان شارژ را کمتر کن.
 گام ۲: جریان شارژ را در پنل یا آمپرمتر ببین.
 گام ۳: سقف را به حالت اول برگردان.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="63" t="inlineStr">
         <is>
           <t>کم و زیاد کردن سقف توان از پنل</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="63" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="61" t="inlineStr">
         <is>
           <t>جریان شارژ به همان نسبت کم و زیاد می‌شود، بدون اینکه دستگاه خاموش یا خطادار شود</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="61" t="inlineStr">
         <is>
           <t>بدون قفل</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="61" t="inlineStr">
         <is>
           <t>دنبال‌کردن جریان از سقف = قبول؛ بی‌اثر بودن سقف = رد</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr"/>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="K15" s="61" t="inlineStr"/>
+      <c r="L15" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="M15" s="61" t="inlineStr"/>
+      <c r="N15" s="61" t="inlineStr"/>
+      <c r="O15" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P15" s="19" t="inlineStr"/>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="P15" s="63" t="inlineStr"/>
+      <c r="Q15" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>CH-036</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>استراحت حرارتی 1h-&gt;10min</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="61" t="inlineStr">
         <is>
           <t>دو باتری خالی واقعی وصل و هر دو کانال آمادهٔ شارژ سنگین‌اند</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="61" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را با باتری خالی به شارژ بزن.
 گام ۲: حدود یک ساعت شارژ سنگین را زیر نظر بگیر (هر از چندی سر بزن).
@@ -1820,73 +1994,73 @@
 گام ۴: بعد از استراحت، شارژ باید خودش ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="63" t="inlineStr">
         <is>
           <t>یک ساعت شارژ سنگین هر دو کانال</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="63" t="inlineStr">
         <is>
           <t>حدود یک ساعت و نیم</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="61" t="inlineStr">
         <is>
           <t>بعد از یک ساعت شارژ سنگین، هر کانال ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>استراحت و ادامهٔ خودکار</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J16" s="61" t="inlineStr">
         <is>
           <t>استراحت و ادامهٔ خودکار = قبول؛ شارژ بی‌وقفهٔ چندساعته یا توقف همیشگی = رد</t>
         </is>
       </c>
-      <c r="K16" s="17" t="n"/>
-      <c r="L16" s="29" t="inlineStr">
+      <c r="K16" s="61" t="n"/>
+      <c r="L16" s="67" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="19" t="inlineStr">
+      <c r="M16" s="61" t="n"/>
+      <c r="N16" s="61" t="n"/>
+      <c r="O16" s="63" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P16" s="19" t="n"/>
-      <c r="Q16" s="21" t="inlineStr">
+      <c r="P16" s="63" t="n"/>
+      <c r="Q16" s="64" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>CH-037</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t>ورودی خارج بازه 22-30V</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="56" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید تا ولتاژش را عوض کنی؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="56" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را زیر ۲۲ ولت بیاور؛ شارژ نباید شروع شود.
 گام ۲: به ۲۴ ولت برگردان؛ شارژ باید شروع شود.
@@ -1894,73 +2068,73 @@
 گام ۴: به ۲۴ برگردان؛ شارژ باید خودش برگردد.</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="58" t="inlineStr">
         <is>
           <t>ورودی: پایین، ۲۴، بالا، ۲۴ ولت</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="56" t="inlineStr">
         <is>
           <t>خارج از بازهٔ سالم شارژ نداریم و با برگشت ورودی به ۲۴ ولت شارژ خودش برمی‌گردد</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="56" t="inlineStr">
         <is>
           <t>بدون قفل</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="56" t="inlineStr">
         <is>
           <t>همین رفتار چهار مرحله = قبول؛ شارژ خارج از بازه یا برنگشتن = رد</t>
         </is>
       </c>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="29" t="inlineStr">
+      <c r="K17" s="56" t="n"/>
+      <c r="L17" s="67" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M17" s="22" t="n"/>
-      <c r="N17" s="22" t="n"/>
-      <c r="O17" s="24" t="inlineStr">
+      <c r="M17" s="56" t="n"/>
+      <c r="N17" s="56" t="n"/>
+      <c r="O17" s="58" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="P17" s="58" t="n"/>
+      <c r="Q17" s="60" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>CH-040</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="56" t="inlineStr">
         <is>
           <t>سناریوی ۶: باتری خراب دیگر شارژ نمی‌شود</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="56" t="inlineStr">
         <is>
           <t>از پنل زمان سناریوی باتری خراب (شناسهٔ ۱۲۵) را موقتاً روی چند دقیقه بگذار؛ یک باتری خالی وصل است</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="56" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت به شارژ کامل برسد.
 گام ۲: بعد از گذشت زمان تنظیم‌شده، ببین شارژ همان کانال متوقف شده و قرمز ثابت آمده.
@@ -1969,68 +2143,68 @@
 گام ۵: شناسهٔ ۱۲۵ را به مقدار واقعی (یک شبانه‌روز) برگردان.</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="58" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="58" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="56" t="inlineStr">
         <is>
           <t>بعد از زمان، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="56" t="inlineStr">
         <is>
           <t>قفل تا تعویض باتری</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J18" s="56" t="inlineStr">
         <is>
           <t>توقف ماندگار و شروع با باتری سالم = قبول؛ شارژ دوبارهٔ همان باتری = رد</t>
         </is>
       </c>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="29" t="inlineStr">
+      <c r="K18" s="56" t="n"/>
+      <c r="L18" s="67" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="24" t="n"/>
-      <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="25">
+      <c r="M18" s="56" t="n"/>
+      <c r="N18" s="56" t="n"/>
+      <c r="O18" s="58" t="n"/>
+      <c r="P18" s="58" t="n"/>
+      <c r="Q18" s="60">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>CH-041</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>خطای ۷: کانال بی‌جریان قفل فنی می‌سازد</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="56" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ است و فیوز خروجی هر کانال را می‌شناسی</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="56" t="inlineStr">
         <is>
           <t>گام ۱: فیوز خروجی یک کانال را دربیاور.
 گام ۲: چند ثانیه صبر کن: شارژ کلاً باید قفل شود و هر سه چراغ با هم چشمک بزنند.
@@ -2038,270 +2212,878 @@
 گام ۴: خاموش و روشن کن؛ شارژ عادی باید برگردد.</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="58" t="inlineStr">
         <is>
           <t>دربیاوردن فیوز یک کانال حین شارژ</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="56" t="inlineStr">
         <is>
           <t>خطای فنی ۷ قفل می‌شود و فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="56" t="inlineStr">
         <is>
           <t>قفل تا ریست</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J19" s="56" t="inlineStr">
         <is>
           <t>قفل فنی و پاک‌شدن فقط با ریست = قبول؛ ادامهٔ شارژ بی‌جریان = رد</t>
         </is>
       </c>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="29" t="inlineStr">
+      <c r="K19" s="56" t="n"/>
+      <c r="L19" s="67" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="24" t="n"/>
-      <c r="P19" s="24" t="n"/>
-      <c r="Q19" s="25">
+      <c r="M19" s="56" t="n"/>
+      <c r="N19" s="56" t="n"/>
+      <c r="O19" s="58" t="n"/>
+      <c r="P19" s="58" t="n"/>
+      <c r="Q19" s="60">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="Q20" s="31">
+      <c r="A20" s="54" t="n"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="54" t="n"/>
+      <c r="L20" s="54" t="n"/>
+      <c r="M20" s="54" t="n"/>
+      <c r="N20" s="54" t="n"/>
+      <c r="O20" s="54" t="n"/>
+      <c r="P20" s="54" t="n"/>
+      <c r="Q20" s="68">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="Q21" s="31">
+      <c r="A21" s="54" t="n"/>
+      <c r="B21" s="54" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="54" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="n"/>
+      <c r="N21" s="54" t="n"/>
+      <c r="O21" s="54" t="n"/>
+      <c r="P21" s="54" t="n"/>
+      <c r="Q21" s="68">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="Q22" s="31">
+      <c r="A22" s="54" t="n"/>
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="n"/>
+      <c r="N22" s="54" t="n"/>
+      <c r="O22" s="54" t="n"/>
+      <c r="P22" s="54" t="n"/>
+      <c r="Q22" s="68">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="Q23" s="31">
+      <c r="A23" s="54" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+      <c r="N23" s="54" t="n"/>
+      <c r="O23" s="54" t="n"/>
+      <c r="P23" s="54" t="n"/>
+      <c r="Q23" s="68">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="Q24" s="31">
+      <c r="A24" s="54" t="n"/>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="n"/>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="n"/>
+      <c r="N24" s="54" t="n"/>
+      <c r="O24" s="54" t="n"/>
+      <c r="P24" s="54" t="n"/>
+      <c r="Q24" s="68">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="Q25" s="31">
+      <c r="A25" s="54" t="n"/>
+      <c r="B25" s="54" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="54" t="n"/>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="54" t="n"/>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="54" t="n"/>
+      <c r="L25" s="54" t="n"/>
+      <c r="M25" s="54" t="n"/>
+      <c r="N25" s="54" t="n"/>
+      <c r="O25" s="54" t="n"/>
+      <c r="P25" s="54" t="n"/>
+      <c r="Q25" s="68">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="Q26" s="31">
+      <c r="A26" s="54" t="n"/>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="54" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="n"/>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n"/>
+      <c r="N26" s="54" t="n"/>
+      <c r="O26" s="54" t="n"/>
+      <c r="P26" s="54" t="n"/>
+      <c r="Q26" s="68">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="Q27" s="31">
+      <c r="A27" s="54" t="n"/>
+      <c r="B27" s="54" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
+      <c r="J27" s="54" t="n"/>
+      <c r="K27" s="54" t="n"/>
+      <c r="L27" s="54" t="n"/>
+      <c r="M27" s="54" t="n"/>
+      <c r="N27" s="54" t="n"/>
+      <c r="O27" s="54" t="n"/>
+      <c r="P27" s="54" t="n"/>
+      <c r="Q27" s="68">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
-      <c r="Q28" s="31">
+      <c r="A28" s="54" t="n"/>
+      <c r="B28" s="54" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="54" t="n"/>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="54" t="n"/>
+      <c r="H28" s="54" t="n"/>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="54" t="n"/>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="n"/>
+      <c r="N28" s="54" t="n"/>
+      <c r="O28" s="54" t="n"/>
+      <c r="P28" s="54" t="n"/>
+      <c r="Q28" s="68">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="31">
+      <c r="A29" s="54" t="n"/>
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="54" t="n"/>
+      <c r="F29" s="54" t="n"/>
+      <c r="G29" s="54" t="n"/>
+      <c r="H29" s="54" t="n"/>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="n"/>
+      <c r="L29" s="54" t="n"/>
+      <c r="M29" s="54" t="n"/>
+      <c r="N29" s="54" t="n"/>
+      <c r="O29" s="54" t="n"/>
+      <c r="P29" s="54" t="n"/>
+      <c r="Q29" s="68">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="31">
+      <c r="A30" s="54" t="n"/>
+      <c r="B30" s="54" t="n"/>
+      <c r="C30" s="54" t="n"/>
+      <c r="D30" s="54" t="n"/>
+      <c r="E30" s="54" t="n"/>
+      <c r="F30" s="54" t="n"/>
+      <c r="G30" s="54" t="n"/>
+      <c r="H30" s="54" t="n"/>
+      <c r="I30" s="54" t="n"/>
+      <c r="J30" s="54" t="n"/>
+      <c r="K30" s="54" t="n"/>
+      <c r="L30" s="54" t="n"/>
+      <c r="M30" s="54" t="n"/>
+      <c r="N30" s="54" t="n"/>
+      <c r="O30" s="54" t="n"/>
+      <c r="P30" s="54" t="n"/>
+      <c r="Q30" s="68">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="31">
+      <c r="A31" s="54" t="n"/>
+      <c r="B31" s="54" t="n"/>
+      <c r="C31" s="54" t="n"/>
+      <c r="D31" s="54" t="n"/>
+      <c r="E31" s="54" t="n"/>
+      <c r="F31" s="54" t="n"/>
+      <c r="G31" s="54" t="n"/>
+      <c r="H31" s="54" t="n"/>
+      <c r="I31" s="54" t="n"/>
+      <c r="J31" s="54" t="n"/>
+      <c r="K31" s="54" t="n"/>
+      <c r="L31" s="54" t="n"/>
+      <c r="M31" s="54" t="n"/>
+      <c r="N31" s="54" t="n"/>
+      <c r="O31" s="54" t="n"/>
+      <c r="P31" s="54" t="n"/>
+      <c r="Q31" s="68">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="31">
+      <c r="A32" s="54" t="n"/>
+      <c r="B32" s="54" t="n"/>
+      <c r="C32" s="54" t="n"/>
+      <c r="D32" s="54" t="n"/>
+      <c r="E32" s="54" t="n"/>
+      <c r="F32" s="54" t="n"/>
+      <c r="G32" s="54" t="n"/>
+      <c r="H32" s="54" t="n"/>
+      <c r="I32" s="54" t="n"/>
+      <c r="J32" s="54" t="n"/>
+      <c r="K32" s="54" t="n"/>
+      <c r="L32" s="54" t="n"/>
+      <c r="M32" s="54" t="n"/>
+      <c r="N32" s="54" t="n"/>
+      <c r="O32" s="54" t="n"/>
+      <c r="P32" s="54" t="n"/>
+      <c r="Q32" s="68">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="31">
+      <c r="A33" s="54" t="n"/>
+      <c r="B33" s="54" t="n"/>
+      <c r="C33" s="54" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="54" t="n"/>
+      <c r="F33" s="54" t="n"/>
+      <c r="G33" s="54" t="n"/>
+      <c r="H33" s="54" t="n"/>
+      <c r="I33" s="54" t="n"/>
+      <c r="J33" s="54" t="n"/>
+      <c r="K33" s="54" t="n"/>
+      <c r="L33" s="54" t="n"/>
+      <c r="M33" s="54" t="n"/>
+      <c r="N33" s="54" t="n"/>
+      <c r="O33" s="54" t="n"/>
+      <c r="P33" s="54" t="n"/>
+      <c r="Q33" s="68">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="31">
+      <c r="A34" s="54" t="n"/>
+      <c r="B34" s="54" t="n"/>
+      <c r="C34" s="54" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="54" t="n"/>
+      <c r="F34" s="54" t="n"/>
+      <c r="G34" s="54" t="n"/>
+      <c r="H34" s="54" t="n"/>
+      <c r="I34" s="54" t="n"/>
+      <c r="J34" s="54" t="n"/>
+      <c r="K34" s="54" t="n"/>
+      <c r="L34" s="54" t="n"/>
+      <c r="M34" s="54" t="n"/>
+      <c r="N34" s="54" t="n"/>
+      <c r="O34" s="54" t="n"/>
+      <c r="P34" s="54" t="n"/>
+      <c r="Q34" s="68">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="31">
+      <c r="A35" s="54" t="n"/>
+      <c r="B35" s="54" t="n"/>
+      <c r="C35" s="54" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="54" t="n"/>
+      <c r="F35" s="54" t="n"/>
+      <c r="G35" s="54" t="n"/>
+      <c r="H35" s="54" t="n"/>
+      <c r="I35" s="54" t="n"/>
+      <c r="J35" s="54" t="n"/>
+      <c r="K35" s="54" t="n"/>
+      <c r="L35" s="54" t="n"/>
+      <c r="M35" s="54" t="n"/>
+      <c r="N35" s="54" t="n"/>
+      <c r="O35" s="54" t="n"/>
+      <c r="P35" s="54" t="n"/>
+      <c r="Q35" s="68">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="31">
+      <c r="A36" s="54" t="n"/>
+      <c r="B36" s="54" t="n"/>
+      <c r="C36" s="54" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="54" t="n"/>
+      <c r="F36" s="54" t="n"/>
+      <c r="G36" s="54" t="n"/>
+      <c r="H36" s="54" t="n"/>
+      <c r="I36" s="54" t="n"/>
+      <c r="J36" s="54" t="n"/>
+      <c r="K36" s="54" t="n"/>
+      <c r="L36" s="54" t="n"/>
+      <c r="M36" s="54" t="n"/>
+      <c r="N36" s="54" t="n"/>
+      <c r="O36" s="54" t="n"/>
+      <c r="P36" s="54" t="n"/>
+      <c r="Q36" s="68">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="31">
+      <c r="A37" s="54" t="n"/>
+      <c r="B37" s="54" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="54" t="n"/>
+      <c r="F37" s="54" t="n"/>
+      <c r="G37" s="54" t="n"/>
+      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="54" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="54" t="n"/>
+      <c r="L37" s="54" t="n"/>
+      <c r="M37" s="54" t="n"/>
+      <c r="N37" s="54" t="n"/>
+      <c r="O37" s="54" t="n"/>
+      <c r="P37" s="54" t="n"/>
+      <c r="Q37" s="68">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="31">
+      <c r="A38" s="54" t="n"/>
+      <c r="B38" s="54" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="54" t="n"/>
+      <c r="H38" s="54" t="n"/>
+      <c r="I38" s="54" t="n"/>
+      <c r="J38" s="54" t="n"/>
+      <c r="K38" s="54" t="n"/>
+      <c r="L38" s="54" t="n"/>
+      <c r="M38" s="54" t="n"/>
+      <c r="N38" s="54" t="n"/>
+      <c r="O38" s="54" t="n"/>
+      <c r="P38" s="54" t="n"/>
+      <c r="Q38" s="68">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="31">
+      <c r="A39" s="54" t="n"/>
+      <c r="B39" s="54" t="n"/>
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="54" t="n"/>
+      <c r="F39" s="54" t="n"/>
+      <c r="G39" s="54" t="n"/>
+      <c r="H39" s="54" t="n"/>
+      <c r="I39" s="54" t="n"/>
+      <c r="J39" s="54" t="n"/>
+      <c r="K39" s="54" t="n"/>
+      <c r="L39" s="54" t="n"/>
+      <c r="M39" s="54" t="n"/>
+      <c r="N39" s="54" t="n"/>
+      <c r="O39" s="54" t="n"/>
+      <c r="P39" s="54" t="n"/>
+      <c r="Q39" s="68">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="31">
+      <c r="A40" s="54" t="n"/>
+      <c r="B40" s="54" t="n"/>
+      <c r="C40" s="54" t="n"/>
+      <c r="D40" s="54" t="n"/>
+      <c r="E40" s="54" t="n"/>
+      <c r="F40" s="54" t="n"/>
+      <c r="G40" s="54" t="n"/>
+      <c r="H40" s="54" t="n"/>
+      <c r="I40" s="54" t="n"/>
+      <c r="J40" s="54" t="n"/>
+      <c r="K40" s="54" t="n"/>
+      <c r="L40" s="54" t="n"/>
+      <c r="M40" s="54" t="n"/>
+      <c r="N40" s="54" t="n"/>
+      <c r="O40" s="54" t="n"/>
+      <c r="P40" s="54" t="n"/>
+      <c r="Q40" s="68">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="31">
+      <c r="A41" s="54" t="n"/>
+      <c r="B41" s="54" t="n"/>
+      <c r="C41" s="54" t="n"/>
+      <c r="D41" s="54" t="n"/>
+      <c r="E41" s="54" t="n"/>
+      <c r="F41" s="54" t="n"/>
+      <c r="G41" s="54" t="n"/>
+      <c r="H41" s="54" t="n"/>
+      <c r="I41" s="54" t="n"/>
+      <c r="J41" s="54" t="n"/>
+      <c r="K41" s="54" t="n"/>
+      <c r="L41" s="54" t="n"/>
+      <c r="M41" s="54" t="n"/>
+      <c r="N41" s="54" t="n"/>
+      <c r="O41" s="54" t="n"/>
+      <c r="P41" s="54" t="n"/>
+      <c r="Q41" s="68">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="31">
+      <c r="A42" s="54" t="n"/>
+      <c r="B42" s="54" t="n"/>
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="54" t="n"/>
+      <c r="F42" s="54" t="n"/>
+      <c r="G42" s="54" t="n"/>
+      <c r="H42" s="54" t="n"/>
+      <c r="I42" s="54" t="n"/>
+      <c r="J42" s="54" t="n"/>
+      <c r="K42" s="54" t="n"/>
+      <c r="L42" s="54" t="n"/>
+      <c r="M42" s="54" t="n"/>
+      <c r="N42" s="54" t="n"/>
+      <c r="O42" s="54" t="n"/>
+      <c r="P42" s="54" t="n"/>
+      <c r="Q42" s="68">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="31">
+      <c r="A43" s="54" t="n"/>
+      <c r="B43" s="54" t="n"/>
+      <c r="C43" s="54" t="n"/>
+      <c r="D43" s="54" t="n"/>
+      <c r="E43" s="54" t="n"/>
+      <c r="F43" s="54" t="n"/>
+      <c r="G43" s="54" t="n"/>
+      <c r="H43" s="54" t="n"/>
+      <c r="I43" s="54" t="n"/>
+      <c r="J43" s="54" t="n"/>
+      <c r="K43" s="54" t="n"/>
+      <c r="L43" s="54" t="n"/>
+      <c r="M43" s="54" t="n"/>
+      <c r="N43" s="54" t="n"/>
+      <c r="O43" s="54" t="n"/>
+      <c r="P43" s="54" t="n"/>
+      <c r="Q43" s="68">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="31">
+      <c r="A44" s="54" t="n"/>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="54" t="n"/>
+      <c r="F44" s="54" t="n"/>
+      <c r="G44" s="54" t="n"/>
+      <c r="H44" s="54" t="n"/>
+      <c r="I44" s="54" t="n"/>
+      <c r="J44" s="54" t="n"/>
+      <c r="K44" s="54" t="n"/>
+      <c r="L44" s="54" t="n"/>
+      <c r="M44" s="54" t="n"/>
+      <c r="N44" s="54" t="n"/>
+      <c r="O44" s="54" t="n"/>
+      <c r="P44" s="54" t="n"/>
+      <c r="Q44" s="68">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="31">
+      <c r="A45" s="54" t="n"/>
+      <c r="B45" s="54" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="54" t="n"/>
+      <c r="F45" s="54" t="n"/>
+      <c r="G45" s="54" t="n"/>
+      <c r="H45" s="54" t="n"/>
+      <c r="I45" s="54" t="n"/>
+      <c r="J45" s="54" t="n"/>
+      <c r="K45" s="54" t="n"/>
+      <c r="L45" s="54" t="n"/>
+      <c r="M45" s="54" t="n"/>
+      <c r="N45" s="54" t="n"/>
+      <c r="O45" s="54" t="n"/>
+      <c r="P45" s="54" t="n"/>
+      <c r="Q45" s="68">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="31">
+      <c r="A46" s="54" t="n"/>
+      <c r="B46" s="54" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="54" t="n"/>
+      <c r="F46" s="54" t="n"/>
+      <c r="G46" s="54" t="n"/>
+      <c r="H46" s="54" t="n"/>
+      <c r="I46" s="54" t="n"/>
+      <c r="J46" s="54" t="n"/>
+      <c r="K46" s="54" t="n"/>
+      <c r="L46" s="54" t="n"/>
+      <c r="M46" s="54" t="n"/>
+      <c r="N46" s="54" t="n"/>
+      <c r="O46" s="54" t="n"/>
+      <c r="P46" s="54" t="n"/>
+      <c r="Q46" s="68">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="31">
+      <c r="A47" s="54" t="n"/>
+      <c r="B47" s="54" t="n"/>
+      <c r="C47" s="54" t="n"/>
+      <c r="D47" s="54" t="n"/>
+      <c r="E47" s="54" t="n"/>
+      <c r="F47" s="54" t="n"/>
+      <c r="G47" s="54" t="n"/>
+      <c r="H47" s="54" t="n"/>
+      <c r="I47" s="54" t="n"/>
+      <c r="J47" s="54" t="n"/>
+      <c r="K47" s="54" t="n"/>
+      <c r="L47" s="54" t="n"/>
+      <c r="M47" s="54" t="n"/>
+      <c r="N47" s="54" t="n"/>
+      <c r="O47" s="54" t="n"/>
+      <c r="P47" s="54" t="n"/>
+      <c r="Q47" s="68">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="31">
+      <c r="A48" s="54" t="n"/>
+      <c r="B48" s="54" t="n"/>
+      <c r="C48" s="54" t="n"/>
+      <c r="D48" s="54" t="n"/>
+      <c r="E48" s="54" t="n"/>
+      <c r="F48" s="54" t="n"/>
+      <c r="G48" s="54" t="n"/>
+      <c r="H48" s="54" t="n"/>
+      <c r="I48" s="54" t="n"/>
+      <c r="J48" s="54" t="n"/>
+      <c r="K48" s="54" t="n"/>
+      <c r="L48" s="54" t="n"/>
+      <c r="M48" s="54" t="n"/>
+      <c r="N48" s="54" t="n"/>
+      <c r="O48" s="54" t="n"/>
+      <c r="P48" s="54" t="n"/>
+      <c r="Q48" s="68">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="31">
+      <c r="A49" s="54" t="n"/>
+      <c r="B49" s="54" t="n"/>
+      <c r="C49" s="54" t="n"/>
+      <c r="D49" s="54" t="n"/>
+      <c r="E49" s="54" t="n"/>
+      <c r="F49" s="54" t="n"/>
+      <c r="G49" s="54" t="n"/>
+      <c r="H49" s="54" t="n"/>
+      <c r="I49" s="54" t="n"/>
+      <c r="J49" s="54" t="n"/>
+      <c r="K49" s="54" t="n"/>
+      <c r="L49" s="54" t="n"/>
+      <c r="M49" s="54" t="n"/>
+      <c r="N49" s="54" t="n"/>
+      <c r="O49" s="54" t="n"/>
+      <c r="P49" s="54" t="n"/>
+      <c r="Q49" s="68">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="31">
+      <c r="A50" s="54" t="n"/>
+      <c r="B50" s="54" t="n"/>
+      <c r="C50" s="54" t="n"/>
+      <c r="D50" s="54" t="n"/>
+      <c r="E50" s="54" t="n"/>
+      <c r="F50" s="54" t="n"/>
+      <c r="G50" s="54" t="n"/>
+      <c r="H50" s="54" t="n"/>
+      <c r="I50" s="54" t="n"/>
+      <c r="J50" s="54" t="n"/>
+      <c r="K50" s="54" t="n"/>
+      <c r="L50" s="54" t="n"/>
+      <c r="M50" s="54" t="n"/>
+      <c r="N50" s="54" t="n"/>
+      <c r="O50" s="54" t="n"/>
+      <c r="P50" s="54" t="n"/>
+      <c r="Q50" s="68">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="31">
+      <c r="A51" s="54" t="n"/>
+      <c r="B51" s="54" t="n"/>
+      <c r="C51" s="54" t="n"/>
+      <c r="D51" s="54" t="n"/>
+      <c r="E51" s="54" t="n"/>
+      <c r="F51" s="54" t="n"/>
+      <c r="G51" s="54" t="n"/>
+      <c r="H51" s="54" t="n"/>
+      <c r="I51" s="54" t="n"/>
+      <c r="J51" s="54" t="n"/>
+      <c r="K51" s="54" t="n"/>
+      <c r="L51" s="54" t="n"/>
+      <c r="M51" s="54" t="n"/>
+      <c r="N51" s="54" t="n"/>
+      <c r="O51" s="54" t="n"/>
+      <c r="P51" s="54" t="n"/>
+      <c r="Q51" s="68">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="31">
+      <c r="A52" s="54" t="n"/>
+      <c r="B52" s="54" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="54" t="n"/>
+      <c r="E52" s="54" t="n"/>
+      <c r="F52" s="54" t="n"/>
+      <c r="G52" s="54" t="n"/>
+      <c r="H52" s="54" t="n"/>
+      <c r="I52" s="54" t="n"/>
+      <c r="J52" s="54" t="n"/>
+      <c r="K52" s="54" t="n"/>
+      <c r="L52" s="54" t="n"/>
+      <c r="M52" s="54" t="n"/>
+      <c r="N52" s="54" t="n"/>
+      <c r="O52" s="54" t="n"/>
+      <c r="P52" s="54" t="n"/>
+      <c r="Q52" s="68">
         <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="Q53" s="31">
+      <c r="A53" s="54" t="n"/>
+      <c r="B53" s="54" t="n"/>
+      <c r="C53" s="54" t="n"/>
+      <c r="D53" s="54" t="n"/>
+      <c r="E53" s="54" t="n"/>
+      <c r="F53" s="54" t="n"/>
+      <c r="G53" s="54" t="n"/>
+      <c r="H53" s="54" t="n"/>
+      <c r="I53" s="54" t="n"/>
+      <c r="J53" s="54" t="n"/>
+      <c r="K53" s="54" t="n"/>
+      <c r="L53" s="54" t="n"/>
+      <c r="M53" s="54" t="n"/>
+      <c r="N53" s="54" t="n"/>
+      <c r="O53" s="54" t="n"/>
+      <c r="P53" s="54" t="n"/>
+      <c r="Q53" s="68">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="Q54" s="31">
+      <c r="A54" s="54" t="n"/>
+      <c r="B54" s="54" t="n"/>
+      <c r="C54" s="54" t="n"/>
+      <c r="D54" s="54" t="n"/>
+      <c r="E54" s="54" t="n"/>
+      <c r="F54" s="54" t="n"/>
+      <c r="G54" s="54" t="n"/>
+      <c r="H54" s="54" t="n"/>
+      <c r="I54" s="54" t="n"/>
+      <c r="J54" s="54" t="n"/>
+      <c r="K54" s="54" t="n"/>
+      <c r="L54" s="54" t="n"/>
+      <c r="M54" s="54" t="n"/>
+      <c r="N54" s="54" t="n"/>
+      <c r="O54" s="54" t="n"/>
+      <c r="P54" s="54" t="n"/>
+      <c r="Q54" s="68">
         <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="Q55" s="31">
+      <c r="A55" s="54" t="n"/>
+      <c r="B55" s="54" t="n"/>
+      <c r="C55" s="54" t="n"/>
+      <c r="D55" s="54" t="n"/>
+      <c r="E55" s="54" t="n"/>
+      <c r="F55" s="54" t="n"/>
+      <c r="G55" s="54" t="n"/>
+      <c r="H55" s="54" t="n"/>
+      <c r="I55" s="54" t="n"/>
+      <c r="J55" s="54" t="n"/>
+      <c r="K55" s="54" t="n"/>
+      <c r="L55" s="54" t="n"/>
+      <c r="M55" s="54" t="n"/>
+      <c r="N55" s="54" t="n"/>
+      <c r="O55" s="54" t="n"/>
+      <c r="P55" s="54" t="n"/>
+      <c r="Q55" s="68">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="Q56" s="31">
+      <c r="A56" s="54" t="n"/>
+      <c r="B56" s="54" t="n"/>
+      <c r="C56" s="54" t="n"/>
+      <c r="D56" s="54" t="n"/>
+      <c r="E56" s="54" t="n"/>
+      <c r="F56" s="54" t="n"/>
+      <c r="G56" s="54" t="n"/>
+      <c r="H56" s="54" t="n"/>
+      <c r="I56" s="54" t="n"/>
+      <c r="J56" s="54" t="n"/>
+      <c r="K56" s="54" t="n"/>
+      <c r="L56" s="54" t="n"/>
+      <c r="M56" s="54" t="n"/>
+      <c r="N56" s="54" t="n"/>
+      <c r="O56" s="54" t="n"/>
+      <c r="P56" s="54" t="n"/>
+      <c r="Q56" s="68">
         <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="Q57" s="31">
+      <c r="A57" s="54" t="n"/>
+      <c r="B57" s="54" t="n"/>
+      <c r="C57" s="54" t="n"/>
+      <c r="D57" s="54" t="n"/>
+      <c r="E57" s="54" t="n"/>
+      <c r="F57" s="54" t="n"/>
+      <c r="G57" s="54" t="n"/>
+      <c r="H57" s="54" t="n"/>
+      <c r="I57" s="54" t="n"/>
+      <c r="J57" s="54" t="n"/>
+      <c r="K57" s="54" t="n"/>
+      <c r="L57" s="54" t="n"/>
+      <c r="M57" s="54" t="n"/>
+      <c r="N57" s="54" t="n"/>
+      <c r="O57" s="54" t="n"/>
+      <c r="P57" s="54" t="n"/>
+      <c r="Q57" s="68">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
@@ -2356,129 +3138,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+      <c r="I1" s="54" t="n"/>
+      <c r="J1" s="54" t="n"/>
+      <c r="K1" s="54" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+      <c r="N1" s="54" t="n"/>
+      <c r="O1" s="54" t="n"/>
+      <c r="P1" s="54" t="n"/>
+      <c r="Q1" s="54" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="54" t="n"/>
+      <c r="P2" s="54" t="n"/>
+      <c r="Q2" s="54" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="54" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="51" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="51" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="51" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="51" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="51" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="51" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="51" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="51" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>CH-002</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>پیش‌فرض امن بوت</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>باتری و ورودی ۲۴V وصل، بوت تازه</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="56" t="inlineStr">
         <is>
           <t>گام ۱: باتری و ورودی 24 ولت را وصل کن و برد را تازه بوت کن.
 گام ۲: ولتاژ هر دو کانال باتری را چک کن که دست‌کم 12 ولت باشد (v_bat≥12V) و ورودی 24 ولت باشد.
@@ -2486,73 +3318,73 @@
 گام ۴: تا 60 ثانیه نگاه کن: هر دو PWM باید تا پایان گیت 15 ثانیه‌ای ثبات اتصال صفر بمانند (15000±2000 میلی‌ثانیه).</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
         <is>
           <t>v_in=24V، هر دو v_bat≥12V</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>هر دو PWM صفر تا پایان گیت ۱۵ ثانیهٔ ثبات اتصال</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>حفظ تا شروع BULK</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="56" t="inlineStr">
         <is>
           <t>PWM=0 تا 15000±2000ms</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="56" t="n"/>
+      <c r="L5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="56" t="n"/>
+      <c r="N5" s="56" t="n"/>
+      <c r="O5" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="P5" s="58" t="n"/>
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>CH-003</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>شروع BULK با رمپ</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>CH-002 پاس</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
 گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
@@ -2560,73 +3392,73 @@
 گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="71" t="inlineStr">
         <is>
           <t>همان CH-002</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="63" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="61" t="inlineStr">
         <is>
           <t>پله‌های duty از 10‰ صعودی</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="61" t="n"/>
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="M6" s="61" t="n"/>
+      <c r="N6" s="61" t="n"/>
+      <c r="O6" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="19" t="n"/>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="P6" s="63" t="n"/>
+      <c r="Q6" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>CH-008</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>خطای سخت جریان</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>در BULK</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="56" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK راه بینداز.
 گام ۲: بار را طوری تنظیم کن که جریان بدون فیلتر از 950 میلی‌آمپر بالاتر برود.
@@ -2634,73 +3466,73 @@
 گام ۴: PWM کانال باید فوراً صفر شود و کانال از نو شروع کند (ریست کانال).</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>I_unfilt&gt;950mA</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>ریست کانال (PWM صفر فوری و شروع دوباره)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>لحظه‌ای</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="56" t="inlineStr">
         <is>
           <t>PWM=0 فوری</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K7" s="56" t="n"/>
+      <c r="L7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="M7" s="56" t="n"/>
+      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="P7" s="58" t="n"/>
+      <c r="Q7" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>CH-039</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>شارژ فعال (BULK)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="56" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
@@ -2708,77 +3540,77 @@
 گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="58" t="inlineStr">
         <is>
           <t>شارژ فعال + ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="58" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="56" t="inlineStr">
         <is>
           <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="56" t="inlineStr">
         <is>
           <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="56" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="L8" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M8" s="56" t="n"/>
+      <c r="N8" s="56" t="n"/>
+      <c r="O8" s="58" t="inlineStr">
         <is>
           <t>2da0ed1</t>
         </is>
       </c>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="P8" s="58" t="n"/>
+      <c r="Q8" s="60" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>CH-009</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>تریپ JIT اول</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
 گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
@@ -2786,72 +3618,72 @@
 گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>JIT falling (PB2/PB6)</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="61" t="inlineStr">
         <is>
           <t>retry خودکار</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="61" t="inlineStr">
         <is>
           <t>state=5 → ریتری 50٪ duty قبل</t>
         </is>
       </c>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K9" s="61" t="n"/>
+      <c r="L9" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M9" s="61" t="n"/>
+      <c r="N9" s="61" t="n"/>
+      <c r="O9" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="n"/>
-      <c r="Q9" s="21">
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="64">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>CH-010</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
         <is>
           <t>ریتری دوم</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
         <is>
           <t>تریپ دوم همان کانال</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="65" t="inlineStr">
         <is>
           <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
 گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
@@ -2859,72 +3691,72 @@
 گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="58" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="56" t="inlineStr">
         <is>
           <t>ریتری دوم حداکثر 10٪ (100‰)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J10" s="56" t="inlineStr">
         <is>
           <t>duty≤100‰</t>
         </is>
       </c>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K10" s="56" t="n"/>
+      <c r="L10" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M10" s="56" t="n"/>
+      <c r="N10" s="56" t="n"/>
+      <c r="O10" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="25">
+      <c r="P10" s="58" t="n"/>
+      <c r="Q10" s="60">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>CH-011</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>تریپ سوم FINAL</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>دو تریپ ثبت‌شده</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="66" t="inlineStr">
         <is>
           <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
 گام ۲: JIT را برای بار سوم تریپ کن.
@@ -2932,72 +3764,72 @@
 گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="61" t="inlineStr">
         <is>
           <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="61" t="inlineStr">
         <is>
           <t>latch دائمی تا ریبوت</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="61" t="inlineStr">
         <is>
           <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
         </is>
       </c>
-      <c r="K11" s="17" t="n"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="17" t="n"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="n"/>
-      <c r="Q11" s="21">
+      <c r="P11" s="63" t="n"/>
+      <c r="Q11" s="64">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>CH-015</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>مود دستی: JIT و re-arm</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="66" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
 گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
@@ -3005,142 +3837,398 @@
 گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="63" t="inlineStr">
         <is>
           <t>JIT trip در مود دستی</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="63" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="61" t="inlineStr">
         <is>
           <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="61" t="inlineStr">
         <is>
           <t>پارک تا re-arm انسانی</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="61" t="inlineStr">
         <is>
           <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
         </is>
       </c>
-      <c r="K12" s="17" t="n"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="19" t="inlineStr">
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="21">
+      <c r="P12" s="63" t="n"/>
+      <c r="Q12" s="64">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="31">
+      <c r="A13" s="54" t="n"/>
+      <c r="B13" s="54" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n"/>
+      <c r="F13" s="54" t="n"/>
+      <c r="G13" s="54" t="n"/>
+      <c r="H13" s="54" t="n"/>
+      <c r="I13" s="54" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="54" t="n"/>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="n"/>
+      <c r="N13" s="54" t="n"/>
+      <c r="O13" s="54" t="n"/>
+      <c r="P13" s="54" t="n"/>
+      <c r="Q13" s="68">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="31">
+      <c r="A14" s="54" t="n"/>
+      <c r="B14" s="54" t="n"/>
+      <c r="C14" s="54" t="n"/>
+      <c r="D14" s="54" t="n"/>
+      <c r="E14" s="54" t="n"/>
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="54" t="n"/>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="54" t="n"/>
+      <c r="N14" s="54" t="n"/>
+      <c r="O14" s="54" t="n"/>
+      <c r="P14" s="54" t="n"/>
+      <c r="Q14" s="68">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="31">
+      <c r="A15" s="54" t="n"/>
+      <c r="B15" s="54" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="54" t="n"/>
+      <c r="F15" s="54" t="n"/>
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="54" t="n"/>
+      <c r="O15" s="54" t="n"/>
+      <c r="P15" s="54" t="n"/>
+      <c r="Q15" s="68">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="31">
+      <c r="A16" s="54" t="n"/>
+      <c r="B16" s="54" t="n"/>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n"/>
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
+      <c r="J16" s="54" t="n"/>
+      <c r="K16" s="54" t="n"/>
+      <c r="L16" s="54" t="n"/>
+      <c r="M16" s="54" t="n"/>
+      <c r="N16" s="54" t="n"/>
+      <c r="O16" s="54" t="n"/>
+      <c r="P16" s="54" t="n"/>
+      <c r="Q16" s="68">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="31">
+      <c r="A17" s="54" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="54" t="n"/>
+      <c r="L17" s="54" t="n"/>
+      <c r="M17" s="54" t="n"/>
+      <c r="N17" s="54" t="n"/>
+      <c r="O17" s="54" t="n"/>
+      <c r="P17" s="54" t="n"/>
+      <c r="Q17" s="68">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="31">
+      <c r="A18" s="54" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="54" t="n"/>
+      <c r="G18" s="54" t="n"/>
+      <c r="H18" s="54" t="n"/>
+      <c r="I18" s="54" t="n"/>
+      <c r="J18" s="54" t="n"/>
+      <c r="K18" s="54" t="n"/>
+      <c r="L18" s="54" t="n"/>
+      <c r="M18" s="54" t="n"/>
+      <c r="N18" s="54" t="n"/>
+      <c r="O18" s="54" t="n"/>
+      <c r="P18" s="54" t="n"/>
+      <c r="Q18" s="68">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="31">
+      <c r="A19" s="54" t="n"/>
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="54" t="n"/>
+      <c r="F19" s="54" t="n"/>
+      <c r="G19" s="54" t="n"/>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="54" t="n"/>
+      <c r="L19" s="54" t="n"/>
+      <c r="M19" s="54" t="n"/>
+      <c r="N19" s="54" t="n"/>
+      <c r="O19" s="54" t="n"/>
+      <c r="P19" s="54" t="n"/>
+      <c r="Q19" s="68">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="31">
+      <c r="A20" s="54" t="n"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="54" t="n"/>
+      <c r="L20" s="54" t="n"/>
+      <c r="M20" s="54" t="n"/>
+      <c r="N20" s="54" t="n"/>
+      <c r="O20" s="54" t="n"/>
+      <c r="P20" s="54" t="n"/>
+      <c r="Q20" s="68">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="31">
+      <c r="A21" s="54" t="n"/>
+      <c r="B21" s="54" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="54" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="n"/>
+      <c r="N21" s="54" t="n"/>
+      <c r="O21" s="54" t="n"/>
+      <c r="P21" s="54" t="n"/>
+      <c r="Q21" s="68">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="31">
+      <c r="A22" s="54" t="n"/>
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="n"/>
+      <c r="N22" s="54" t="n"/>
+      <c r="O22" s="54" t="n"/>
+      <c r="P22" s="54" t="n"/>
+      <c r="Q22" s="68">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="31">
+      <c r="A23" s="54" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+      <c r="N23" s="54" t="n"/>
+      <c r="O23" s="54" t="n"/>
+      <c r="P23" s="54" t="n"/>
+      <c r="Q23" s="68">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="31">
+      <c r="A24" s="54" t="n"/>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="n"/>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="n"/>
+      <c r="N24" s="54" t="n"/>
+      <c r="O24" s="54" t="n"/>
+      <c r="P24" s="54" t="n"/>
+      <c r="Q24" s="68">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="31">
+      <c r="A25" s="54" t="n"/>
+      <c r="B25" s="54" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="54" t="n"/>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="54" t="n"/>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="54" t="n"/>
+      <c r="L25" s="54" t="n"/>
+      <c r="M25" s="54" t="n"/>
+      <c r="N25" s="54" t="n"/>
+      <c r="O25" s="54" t="n"/>
+      <c r="P25" s="54" t="n"/>
+      <c r="Q25" s="68">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="31">
+      <c r="A26" s="54" t="n"/>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="54" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="n"/>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n"/>
+      <c r="N26" s="54" t="n"/>
+      <c r="O26" s="54" t="n"/>
+      <c r="P26" s="54" t="n"/>
+      <c r="Q26" s="68">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="31">
+      <c r="A27" s="54" t="n"/>
+      <c r="B27" s="54" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
+      <c r="J27" s="54" t="n"/>
+      <c r="K27" s="54" t="n"/>
+      <c r="L27" s="54" t="n"/>
+      <c r="M27" s="54" t="n"/>
+      <c r="N27" s="54" t="n"/>
+      <c r="O27" s="54" t="n"/>
+      <c r="P27" s="54" t="n"/>
+      <c r="Q27" s="68">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="31">
+      <c r="A28" s="54" t="n"/>
+      <c r="B28" s="54" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="54" t="n"/>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="54" t="n"/>
+      <c r="H28" s="54" t="n"/>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="54" t="n"/>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="n"/>
+      <c r="N28" s="54" t="n"/>
+      <c r="O28" s="54" t="n"/>
+      <c r="P28" s="54" t="n"/>
+      <c r="Q28" s="68">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
@@ -3195,129 +4283,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+      <c r="I1" s="54" t="n"/>
+      <c r="J1" s="54" t="n"/>
+      <c r="K1" s="54" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+      <c r="N1" s="54" t="n"/>
+      <c r="O1" s="54" t="n"/>
+      <c r="P1" s="54" t="n"/>
+      <c r="Q1" s="54" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="47" t="inlineStr">
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="70" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="54" t="n"/>
+      <c r="P2" s="54" t="n"/>
+      <c r="Q2" s="54" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="54" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="51" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="51" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="51" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="51" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="51" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="51" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="51" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="51" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>CH-001</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>نگاشت سخت‌افزار</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
@@ -3325,73 +4463,73 @@
 گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>PA0=TIM2_CH1، PA6=TIM3_CH1، PA1/PA7 سنس، PB2/PB6 JIT، رله NC</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>نگاشت مطابق شماتیک؛ رله با coil خاموش وصل (NC)</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="61" t="inlineStr">
         <is>
           <t>نگاشت ثابت</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr">
         <is>
           <t>PASS: تطابق کامل</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="61" t="n"/>
+      <c r="L5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="61" t="n"/>
+      <c r="N5" s="61" t="n"/>
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="64" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>CH-035</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="56" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
 گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
@@ -3399,73 +4537,73 @@
 گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="56" t="inlineStr">
         <is>
           <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="56" t="inlineStr">
         <is>
           <t>safe-idle</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="56" t="inlineStr">
         <is>
           <t>duty=0 بدون overcurrent کاذب</t>
         </is>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="29" t="inlineStr">
+      <c r="K6" s="56" t="n"/>
+      <c r="L6" s="67" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M6" s="56" t="n"/>
+      <c r="N6" s="56" t="n"/>
+      <c r="O6" s="58" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="P6" s="58" t="n"/>
+      <c r="Q6" s="60" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>CH-038</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>حفظ THERMAL_REST در SafeIdle</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>کانال در استراحت حرارتی</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="66" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
 گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
@@ -3473,171 +4611,491 @@
 گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>valid=false حین rest</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>THERMAL_REST حفظ نه OFF</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="61" t="inlineStr">
         <is>
           <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="30" t="inlineStr">
+      <c r="K7" s="61" t="n"/>
+      <c r="L7" s="72" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="61" t="n"/>
+      <c r="N7" s="61" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="O7" s="63" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P7" s="19" t="n"/>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="P7" s="63" t="n"/>
+      <c r="Q7" s="64" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="31">
+      <c r="A8" s="54" t="n"/>
+      <c r="B8" s="54" t="n"/>
+      <c r="C8" s="54" t="n"/>
+      <c r="D8" s="54" t="n"/>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n"/>
+      <c r="G8" s="54" t="n"/>
+      <c r="H8" s="54" t="n"/>
+      <c r="I8" s="54" t="n"/>
+      <c r="J8" s="54" t="n"/>
+      <c r="K8" s="54" t="n"/>
+      <c r="L8" s="54" t="n"/>
+      <c r="M8" s="54" t="n"/>
+      <c r="N8" s="54" t="n"/>
+      <c r="O8" s="54" t="n"/>
+      <c r="P8" s="54" t="n"/>
+      <c r="Q8" s="68">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="31">
+      <c r="A9" s="54" t="n"/>
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="54" t="n"/>
+      <c r="L9" s="54" t="n"/>
+      <c r="M9" s="54" t="n"/>
+      <c r="N9" s="54" t="n"/>
+      <c r="O9" s="54" t="n"/>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="68">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="31">
+      <c r="A10" s="54" t="n"/>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="54" t="n"/>
+      <c r="L10" s="54" t="n"/>
+      <c r="M10" s="54" t="n"/>
+      <c r="N10" s="54" t="n"/>
+      <c r="O10" s="54" t="n"/>
+      <c r="P10" s="54" t="n"/>
+      <c r="Q10" s="68">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="31">
+      <c r="A11" s="54" t="n"/>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="54" t="n"/>
+      <c r="D11" s="54" t="n"/>
+      <c r="E11" s="54" t="n"/>
+      <c r="F11" s="54" t="n"/>
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="54" t="n"/>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="54" t="n"/>
+      <c r="L11" s="54" t="n"/>
+      <c r="M11" s="54" t="n"/>
+      <c r="N11" s="54" t="n"/>
+      <c r="O11" s="54" t="n"/>
+      <c r="P11" s="54" t="n"/>
+      <c r="Q11" s="68">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="31">
+      <c r="A12" s="54" t="n"/>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
+      <c r="D12" s="54" t="n"/>
+      <c r="E12" s="54" t="n"/>
+      <c r="F12" s="54" t="n"/>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
+      <c r="J12" s="54" t="n"/>
+      <c r="K12" s="54" t="n"/>
+      <c r="L12" s="54" t="n"/>
+      <c r="M12" s="54" t="n"/>
+      <c r="N12" s="54" t="n"/>
+      <c r="O12" s="54" t="n"/>
+      <c r="P12" s="54" t="n"/>
+      <c r="Q12" s="68">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="31">
+      <c r="A13" s="54" t="n"/>
+      <c r="B13" s="54" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n"/>
+      <c r="F13" s="54" t="n"/>
+      <c r="G13" s="54" t="n"/>
+      <c r="H13" s="54" t="n"/>
+      <c r="I13" s="54" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="54" t="n"/>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="n"/>
+      <c r="N13" s="54" t="n"/>
+      <c r="O13" s="54" t="n"/>
+      <c r="P13" s="54" t="n"/>
+      <c r="Q13" s="68">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="31">
+      <c r="A14" s="54" t="n"/>
+      <c r="B14" s="54" t="n"/>
+      <c r="C14" s="54" t="n"/>
+      <c r="D14" s="54" t="n"/>
+      <c r="E14" s="54" t="n"/>
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="54" t="n"/>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="54" t="n"/>
+      <c r="N14" s="54" t="n"/>
+      <c r="O14" s="54" t="n"/>
+      <c r="P14" s="54" t="n"/>
+      <c r="Q14" s="68">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="31">
+      <c r="A15" s="54" t="n"/>
+      <c r="B15" s="54" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="54" t="n"/>
+      <c r="F15" s="54" t="n"/>
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="54" t="n"/>
+      <c r="O15" s="54" t="n"/>
+      <c r="P15" s="54" t="n"/>
+      <c r="Q15" s="68">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="31">
+      <c r="A16" s="54" t="n"/>
+      <c r="B16" s="54" t="n"/>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n"/>
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
+      <c r="J16" s="54" t="n"/>
+      <c r="K16" s="54" t="n"/>
+      <c r="L16" s="54" t="n"/>
+      <c r="M16" s="54" t="n"/>
+      <c r="N16" s="54" t="n"/>
+      <c r="O16" s="54" t="n"/>
+      <c r="P16" s="54" t="n"/>
+      <c r="Q16" s="68">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="31">
+      <c r="A17" s="54" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="54" t="n"/>
+      <c r="L17" s="54" t="n"/>
+      <c r="M17" s="54" t="n"/>
+      <c r="N17" s="54" t="n"/>
+      <c r="O17" s="54" t="n"/>
+      <c r="P17" s="54" t="n"/>
+      <c r="Q17" s="68">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="31">
+      <c r="A18" s="54" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="54" t="n"/>
+      <c r="G18" s="54" t="n"/>
+      <c r="H18" s="54" t="n"/>
+      <c r="I18" s="54" t="n"/>
+      <c r="J18" s="54" t="n"/>
+      <c r="K18" s="54" t="n"/>
+      <c r="L18" s="54" t="n"/>
+      <c r="M18" s="54" t="n"/>
+      <c r="N18" s="54" t="n"/>
+      <c r="O18" s="54" t="n"/>
+      <c r="P18" s="54" t="n"/>
+      <c r="Q18" s="68">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="31">
+      <c r="A19" s="54" t="n"/>
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="54" t="n"/>
+      <c r="F19" s="54" t="n"/>
+      <c r="G19" s="54" t="n"/>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="54" t="n"/>
+      <c r="L19" s="54" t="n"/>
+      <c r="M19" s="54" t="n"/>
+      <c r="N19" s="54" t="n"/>
+      <c r="O19" s="54" t="n"/>
+      <c r="P19" s="54" t="n"/>
+      <c r="Q19" s="68">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="31">
+      <c r="A20" s="54" t="n"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="54" t="n"/>
+      <c r="L20" s="54" t="n"/>
+      <c r="M20" s="54" t="n"/>
+      <c r="N20" s="54" t="n"/>
+      <c r="O20" s="54" t="n"/>
+      <c r="P20" s="54" t="n"/>
+      <c r="Q20" s="68">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="31">
+      <c r="A21" s="54" t="n"/>
+      <c r="B21" s="54" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="54" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="n"/>
+      <c r="N21" s="54" t="n"/>
+      <c r="O21" s="54" t="n"/>
+      <c r="P21" s="54" t="n"/>
+      <c r="Q21" s="68">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="31">
+      <c r="A22" s="54" t="n"/>
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="n"/>
+      <c r="N22" s="54" t="n"/>
+      <c r="O22" s="54" t="n"/>
+      <c r="P22" s="54" t="n"/>
+      <c r="Q22" s="68">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="31">
+      <c r="A23" s="54" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+      <c r="N23" s="54" t="n"/>
+      <c r="O23" s="54" t="n"/>
+      <c r="P23" s="54" t="n"/>
+      <c r="Q23" s="68">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="31">
+      <c r="A24" s="54" t="n"/>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="n"/>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="n"/>
+      <c r="N24" s="54" t="n"/>
+      <c r="O24" s="54" t="n"/>
+      <c r="P24" s="54" t="n"/>
+      <c r="Q24" s="68">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="31">
+      <c r="A25" s="54" t="n"/>
+      <c r="B25" s="54" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="54" t="n"/>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="54" t="n"/>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="54" t="n"/>
+      <c r="L25" s="54" t="n"/>
+      <c r="M25" s="54" t="n"/>
+      <c r="N25" s="54" t="n"/>
+      <c r="O25" s="54" t="n"/>
+      <c r="P25" s="54" t="n"/>
+      <c r="Q25" s="68">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="31">
+      <c r="A26" s="54" t="n"/>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="54" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="n"/>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n"/>
+      <c r="N26" s="54" t="n"/>
+      <c r="O26" s="54" t="n"/>
+      <c r="P26" s="54" t="n"/>
+      <c r="Q26" s="68">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="31">
+      <c r="A27" s="54" t="n"/>
+      <c r="B27" s="54" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
+      <c r="J27" s="54" t="n"/>
+      <c r="K27" s="54" t="n"/>
+      <c r="L27" s="54" t="n"/>
+      <c r="M27" s="54" t="n"/>
+      <c r="N27" s="54" t="n"/>
+      <c r="O27" s="54" t="n"/>
+      <c r="P27" s="54" t="n"/>
+      <c r="Q27" s="68">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
@@ -3675,201 +5133,207 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Charger</t>
         </is>
       </c>
-      <c r="B1" s="42" t="n"/>
-      <c r="C1" s="42" t="n"/>
-      <c r="D1" s="42" t="n"/>
-      <c r="E1" s="43" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="73" t="n"/>
+      <c r="C1" s="73" t="n"/>
+      <c r="D1" s="73" t="n"/>
+      <c r="E1" s="74" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="75" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="75" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>گیت ثبات اتصال</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
         <is>
           <t>۱۵s دیدن ولتاژ باتری</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="76" t="inlineStr">
         <is>
           <t>OFF→BULK فقط بعد از ثبات</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>charger.h (2026-09-19)</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="76" t="inlineStr">
         <is>
           <t>JIT-ریتری و reentry معاف</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>باند تنظیم BULK</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>630..650mA Iest</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>پله‌های duty برای نگه‌داشت باند</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>CHG_REGULATE_LOW_MA / CHG_BULK_CURRENT_MAX_MA</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="76" t="inlineStr">
         <is>
           <t>تصمیم روی جریان تخمینی خروجی</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>خطای سخت جریان</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>&gt;950mA</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>ریست کانال</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="76" t="inlineStr">
         <is>
           <t>CHG_CURRENT_HARD_FAULT_MA</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="76" t="inlineStr">
         <is>
           <t>حداکثر ~10ms تأخیر با فیلترها</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>ورود 14.3 / نگه‌داشت 14.4 / فرار 14.6V</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>پله 0.1٪ / نزول 0.5٪</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>CHG_ABSORB_*</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="76" t="inlineStr">
         <is>
           <t>شستشوی ۱۰ دقیقه کل مدت</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>JIT</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>lockout 3s، ریتری ۵۰٪، دوم ≤۱۰٪، سوم FINAL</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>ریتری تک‌تک از صف</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>CHG_JIT_LOCKOUT_MS / CHG_DUTY_RETRY_SECOND_MAX</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="76" t="inlineStr">
         <is>
           <t>در مود دستی: بدون ریتری، فقط re-arm</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>مود دستی v1.2</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>ID19، ددمن 3s، قطع 15V، سقف، قطع کانال</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>duty مستقیم از 16/18</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="76" t="inlineStr">
         <is>
           <t>CHG_MANUAL_WATCHDOG_MS و §5.2 سند ESP</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="76" t="inlineStr">
         <is>
           <t>فریز Fault_Evaluate حین مود</t>
         </is>
@@ -3912,93 +5376,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Charger</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+      <c r="I1" s="54" t="n"/>
+      <c r="J1" s="54" t="n"/>
+      <c r="K1" s="54" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="42" t="n"/>
-      <c r="C2" s="42" t="n"/>
-      <c r="D2" s="42" t="n"/>
-      <c r="E2" s="42" t="n"/>
-      <c r="F2" s="42" t="n"/>
-      <c r="G2" s="42" t="n"/>
-      <c r="H2" s="42" t="n"/>
-      <c r="I2" s="42" t="n"/>
-      <c r="J2" s="42" t="n"/>
-      <c r="K2" s="42" t="n"/>
-      <c r="L2" s="42" t="n"/>
-      <c r="M2" s="43" t="n"/>
+      <c r="B2" s="73" t="n"/>
+      <c r="C2" s="73" t="n"/>
+      <c r="D2" s="73" t="n"/>
+      <c r="E2" s="73" t="n"/>
+      <c r="F2" s="73" t="n"/>
+      <c r="G2" s="73" t="n"/>
+      <c r="H2" s="73" t="n"/>
+      <c r="I2" s="73" t="n"/>
+      <c r="J2" s="73" t="n"/>
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="74" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="75" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="75" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="75" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" s="75" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="75" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="75" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="32" t="inlineStr">
+      <c r="J3" s="75" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="32" t="inlineStr">
+      <c r="K3" s="75" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="32" t="inlineStr">
+      <c r="L3" s="75" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="32" t="inlineStr">
+      <c r="M3" s="75" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -4029,209 +5505,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Charger</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Charger — دو کانال ۱۲V مستقل</t>
         </is>
       </c>
+      <c r="C5" s="54" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — پوشش v1.2 مود دستی)</t>
         </is>
       </c>
+      <c r="C6" s="54" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="54" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="54" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>پنل ESP + اسکوپ + مولتی‌متر + منبع محدودشده</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="54" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="n"/>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="78" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="54" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="75" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="79" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="79" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="79" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="79" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="79">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="79" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="79" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="79">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="79" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="79">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="79" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="79" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="79">
         <f>IF(19=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/19)</f>
         <v/>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="79" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="54" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4258,117 +5758,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="54" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="54" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="54" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="54" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="54" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="54" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="54" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="A9" s="54" t="n"/>
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="A10" s="54" t="n"/>
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37" t="inlineStr">
+      <c r="A11" s="54" t="n"/>
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="54" t="n"/>
+      <c r="B12" s="54" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="80" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
+      <c r="B13" s="54" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
+      <c r="B14" s="54" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
+      <c r="B15" s="54" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
+      <c r="B16" s="54" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
+      <c r="B17" s="54" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4390,60 +5909,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول شارژر (Charger)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="40" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Charger_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="54" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="54" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,6 +188,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -237,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -317,11 +321,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -526,6 +531,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -892,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -957,6 +965,14 @@
       <c r="A10" s="50" t="inlineStr">
         <is>
           <t>هشدار: منبع ورودی در تست‌های اول محدودشده باشد؛ current-limit ورودی جای حفاظت خروجی firmware نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -1015,22 +1031,6 @@
           <t>برنامهٔ تست عملی — ماژول Charger</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="54" t="n"/>
-      <c r="D1" s="54" t="n"/>
-      <c r="E1" s="54" t="n"/>
-      <c r="F1" s="54" t="n"/>
-      <c r="G1" s="54" t="n"/>
-      <c r="H1" s="54" t="n"/>
-      <c r="I1" s="54" t="n"/>
-      <c r="J1" s="54" t="n"/>
-      <c r="K1" s="54" t="n"/>
-      <c r="L1" s="54" t="n"/>
-      <c r="M1" s="54" t="n"/>
-      <c r="N1" s="54" t="n"/>
-      <c r="O1" s="54" t="n"/>
-      <c r="P1" s="54" t="n"/>
-      <c r="Q1" s="54" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="inlineStr">
@@ -1038,22 +1038,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="54" t="n"/>
-      <c r="D2" s="54" t="n"/>
-      <c r="E2" s="54" t="n"/>
-      <c r="F2" s="54" t="n"/>
-      <c r="G2" s="54" t="n"/>
-      <c r="H2" s="54" t="n"/>
-      <c r="I2" s="54" t="n"/>
-      <c r="J2" s="54" t="n"/>
-      <c r="K2" s="54" t="n"/>
-      <c r="L2" s="54" t="n"/>
-      <c r="M2" s="54" t="n"/>
-      <c r="N2" s="54" t="n"/>
-      <c r="O2" s="54" t="n"/>
-      <c r="P2" s="54" t="n"/>
-      <c r="Q2" s="54" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
@@ -1061,22 +1045,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="54" t="n"/>
-      <c r="D3" s="54" t="n"/>
-      <c r="E3" s="54" t="n"/>
-      <c r="F3" s="54" t="n"/>
-      <c r="G3" s="54" t="n"/>
-      <c r="H3" s="54" t="n"/>
-      <c r="I3" s="54" t="n"/>
-      <c r="J3" s="54" t="n"/>
-      <c r="K3" s="54" t="n"/>
-      <c r="L3" s="54" t="n"/>
-      <c r="M3" s="54" t="n"/>
-      <c r="N3" s="54" t="n"/>
-      <c r="O3" s="54" t="n"/>
-      <c r="P3" s="54" t="n"/>
-      <c r="Q3" s="54" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="51" t="inlineStr">
@@ -1126,7 +1094,7 @@
       </c>
       <c r="J4" s="51" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="51" t="inlineStr">
@@ -1168,448 +1136,439 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="55" t="inlineStr">
         <is>
+          <t>CH-042</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>شروع شارژ با وصل ورودی</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>باتری نیمه‌خالی وصل و جاافتاده؛ ورودی قطع</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: با ورودیِ قطع مطمئن شو شارژی در کار نیست (جریان صفر).
+گام ۲: ورودی ۲۴ ولت را وصل کن.
+گام ۳: تا یک دقیقه نگاه کن؛ شارژ باید خودش شروع شود.
+گام ۴: ورودی را قطع کن؛ شارژ باید بایستد.</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>ورودی ۲۴ ولت وصل و قطع</t>
+        </is>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H5" s="56" t="inlineStr">
+        <is>
+          <t>با وصل ورودی شارژ خودکار شروع و با قطع آن متوقف می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: با وصل ورودی، جریان شارژ در پنل (یا با مولتی‌متر) بالا می‌رود و چراغ زرد چشمک می‌زند؛ با قطع ورودی جریان صفر می‌شود. اگر شارژ شروع نشد یا با قطع ورودی ادامه داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="56" t="n"/>
+      <c r="L5" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="56" t="n"/>
+      <c r="N5" s="56" t="n"/>
+      <c r="O5" s="58" t="n"/>
+      <c r="P5" s="58" t="n"/>
+      <c r="Q5" s="60">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
           <t>CH-004</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>تنظیم BULK</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>یک باتری نیمه‌خالی واقعی وصل است و برق شهر برقرار؛ آمپرمتر دستی یا پنل برای دیدن جریان آماده است</t>
         </is>
       </c>
-      <c r="E5" s="56" t="inlineStr">
+      <c r="E6" s="56" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را شروع کن و بگذار یک دقیقه جا بیفتد.
 گام ۲: جریان شارژ را از پنل یا آمپرمتر دستی بخوان.
 گام ۳: یک دقیقه دیگر نگاه کن که جریان ثابت مانده یا نه.</t>
         </is>
       </c>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>باتری نیمه‌خالی در حال شارژ</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="56" t="inlineStr">
+      <c r="H6" s="56" t="inlineStr">
         <is>
           <t>جریان شارژ نزدیک سقف تنظیم‌شده (حدود ۰٫۶۴ آمپر) می‌ایستد و پایدار می‌ماند؛ بالا و پایین نمی‌پرد</t>
         </is>
       </c>
-      <c r="I5" s="56" t="inlineStr">
+      <c r="I6" s="56" t="inlineStr">
         <is>
           <t>پایدار تا وقتی باتری پرتر شود</t>
         </is>
       </c>
-      <c r="J5" s="56" t="inlineStr">
-        <is>
-          <t>جریان پایدار نزدیک سقف = قبول؛ نوسان شدید یا جریان خیلی کمتر/بیشتر = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="56" t="inlineStr"/>
-      <c r="L5" s="59" t="inlineStr">
+      <c r="J6" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: جریان شارژ (در پنل یا با مولتی‌متر) نزدیک سقف تنظیم‌شده می‌ایستد و پایدار می‌ماند و بالا و پایین نمی‌پرد. اگر نوسان شدید داشت یا خیلی کمتر یا بیشتر بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="56" t="n"/>
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="56" t="inlineStr"/>
-      <c r="N5" s="56" t="inlineStr"/>
-      <c r="O5" s="58" t="inlineStr">
+      <c r="M6" s="56" t="n"/>
+      <c r="N6" s="56" t="n"/>
+      <c r="O6" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="58" t="inlineStr"/>
-      <c r="Q5" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="P6" s="58" t="n"/>
+      <c r="Q6" s="60">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>باتری تقریباً پر است و شارژ ادامه دارد</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E7" s="61" t="inlineStr">
         <is>
           <t>گام ۱: باتری نزدیک‌به‌پر را به شارژ نگه دار.
 گام ۲: ولتاژ باتری را با مولتی‌متر و جریان شارژ را با پنل زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>باتری تقریباً پر در شارژ</t>
         </is>
       </c>
-      <c r="G6" s="63" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="61" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود (شارژ ملایم پایانی)</t>
         </is>
       </c>
-      <c r="I6" s="61" t="inlineStr">
+      <c r="I7" s="61" t="inlineStr">
         <is>
           <t>تا رسیدن به حالت نگهداری</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
-        <is>
-          <t>ولتاژ ثابت با جریان رو به کاهش = قبول؛ بالا رفتن ولتاژ از حد شارژ = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="61" t="inlineStr"/>
-      <c r="L6" s="59" t="inlineStr">
+      <c r="J7" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود. اگر ولتاژ از حد شارژ بالا رفت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K7" s="61" t="n"/>
+      <c r="L7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="61" t="inlineStr"/>
-      <c r="N6" s="61" t="inlineStr"/>
-      <c r="O6" s="63" t="inlineStr">
+      <c r="M7" s="61" t="n"/>
+      <c r="N7" s="61" t="n"/>
+      <c r="O7" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="63" t="inlineStr"/>
-      <c r="Q6" s="64" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
-        <is>
-          <t>CH-006</t>
-        </is>
-      </c>
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>شستشوی ABSORB</t>
-        </is>
-      </c>
-      <c r="C7" s="58" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D7" s="56" t="inlineStr">
-        <is>
-          <t>باتری در شارژ پایانی (جذب) است</t>
-        </is>
-      </c>
-      <c r="E7" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: حین شارژ پایانی، یک مصرف کوتاه و واقعی از باتری بکش (مثلاً یک لامپ را چند ثانیه روشن کن) و بردار.
-گام ۲: رفتار شارژر را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F7" s="58" t="inlineStr">
-        <is>
-          <t>مصرف کوتاه حین شارژ پایانی</t>
-        </is>
-      </c>
-      <c r="G7" s="58" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H7" s="56" t="inlineStr">
-        <is>
-          <t>شارژر به شارژ تند برنمی‌گردد؛ همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود</t>
-        </is>
-      </c>
-      <c r="I7" s="56" t="inlineStr">
-        <is>
-          <t>بدون برگشت به شارژ تند</t>
-        </is>
-      </c>
-      <c r="J7" s="56" t="inlineStr">
-        <is>
-          <t>ادامهٔ همان شارژ پایانی = قبول؛ برگشتن به جریان کامل = رد</t>
-        </is>
-      </c>
-      <c r="K7" s="56" t="inlineStr"/>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="56" t="inlineStr"/>
-      <c r="N7" s="56" t="inlineStr"/>
-      <c r="O7" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="58" t="inlineStr"/>
-      <c r="Q7" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P7" s="63" t="n"/>
+      <c r="Q7" s="64">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="55" t="inlineStr">
         <is>
-          <t>CH-007</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>FLOAT و reentry</t>
-        </is>
-      </c>
-      <c r="C8" s="63" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D8" s="61" t="inlineStr">
-        <is>
-          <t>باتری کاملاً پر شده و شارژ به حالت نگهداری رسیده (جریان خیلی کم)</t>
-        </is>
-      </c>
-      <c r="E8" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: بگذار باتری کامل پر و شارژ آرام شود.
-گام ۲: یک بار واقعی روی خروجی بکش تا باتری کمی خالی شود.
-گام ۳: نگاه کن شارژ دوباره کی و چطور شروع می‌شود.</t>
-        </is>
-      </c>
-      <c r="F8" s="63" t="inlineStr">
-        <is>
-          <t>باتری پر، بعد کمی مصرف واقعی</t>
-        </is>
-      </c>
-      <c r="G8" s="63" t="inlineStr">
-        <is>
-          <t>ده دقیقه</t>
-        </is>
-      </c>
-      <c r="H8" s="61" t="inlineStr">
-        <is>
-          <t>در حالت پر، جریان نگهداری خیلی کم است؛ با کمی خالی‌شدن، شارژ خودش دوباره شروع می‌شود</t>
-        </is>
-      </c>
-      <c r="I8" s="61" t="inlineStr">
-        <is>
-          <t>رفت‌وبرگشت خودکار پر/شارژ</t>
-        </is>
-      </c>
-      <c r="J8" s="61" t="inlineStr">
-        <is>
-          <t>شروع دوبارهٔ خودکار شارژ = قبول؛ شارژ نشدن دوباره یا شارژ دائمیِ پر = رد</t>
-        </is>
-      </c>
-      <c r="K8" s="61" t="inlineStr"/>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M8" s="61" t="inlineStr"/>
-      <c r="N8" s="61" t="inlineStr"/>
-      <c r="O8" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P8" s="63" t="inlineStr"/>
-      <c r="Q8" s="64" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="55" t="inlineStr">
-        <is>
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C8" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ یک باتری واقعی است</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr">
+      <c r="E8" s="56" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ، سیم حس‌کردن ولتاژ باتری را جدا کن.
 گام ۲: به شارژر نگاه کن؛ نباید کورکورانه به شارژ ادامه دهد.
 گام ۳: سیم را وصل کن و برگشت شارژ را ببین.</t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
+      <c r="F8" s="58" t="inlineStr">
         <is>
           <t>قطع و وصل سیم حس ولتاژ باتری</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G8" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="56" t="inlineStr">
+      <c r="H8" s="56" t="inlineStr">
         <is>
           <t>با قطع سیم حس، شارژ متوقف می‌ماند؛ با وصل آن، شارژ عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I9" s="56" t="inlineStr">
+      <c r="I8" s="56" t="inlineStr">
         <is>
           <t>توقف تا برگشت حس</t>
         </is>
       </c>
-      <c r="J9" s="56" t="inlineStr">
-        <is>
-          <t>توقف شارژ حین قطع حس = قبول؛ ادامهٔ شارژ بی‌حس = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="56" t="inlineStr"/>
-      <c r="L9" s="59" t="inlineStr">
+      <c r="J8" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: با قطع سیم حس، شارژ متوقف می‌ماند و با وصل آن شارژ عادی برمی‌گردد. اگر بی‌حس هم شارژ ادامه داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K8" s="56" t="n"/>
+      <c r="L8" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="56" t="inlineStr"/>
-      <c r="N9" s="56" t="inlineStr"/>
-      <c r="O9" s="58" t="inlineStr">
+      <c r="M8" s="56" t="n"/>
+      <c r="N8" s="56" t="n"/>
+      <c r="O8" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="58" t="inlineStr"/>
-      <c r="Q9" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="P8" s="58" t="n"/>
+      <c r="Q8" s="60">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>پنل وصل است و دستگاه روشن</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>گام ۱: از پنل مود تست دستی شارژر را روشن کن.
 گام ۲: نگاه کن شارژ خودکار کنار می‌رود و شارژر فقط به فرمان دستی گوش می‌دهد.
 گام ۳: یک فرمان دستی کوچک بده و اجراش را ببین.</t>
         </is>
       </c>
-      <c r="F10" s="63" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>روشن‌کردن مود دستی از پنل</t>
         </is>
       </c>
-      <c r="G10" s="63" t="inlineStr">
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="61" t="inlineStr">
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>شارژر وارد مود دستی می‌شود و فقط فرمان دستی را اجرا می‌کند</t>
         </is>
       </c>
-      <c r="I10" s="61" t="inlineStr">
+      <c r="I9" s="61" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
-        <is>
-          <t>ورود درست به مود دستی = قبول؛ ادامهٔ شارژ خودکار = رد</t>
-        </is>
-      </c>
-      <c r="K10" s="61" t="inlineStr"/>
+      <c r="J9" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: شارژر وارد مود دستی می‌شود و فقط فرمان دستی پنل را اجرا می‌کند. اگر شارژ خودکار ادامه داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K9" s="61" t="n"/>
+      <c r="L9" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="61" t="n"/>
+      <c r="N9" s="61" t="n"/>
+      <c r="O9" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="64">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>CH-018</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>شارژر در مود تست دستی است</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل از مود دستی خارج شو.
+گام ۲: یک باتری نیمه‌خالی را زیر نظر بگیر.</t>
+        </is>
+      </c>
+      <c r="F10" s="58" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی</t>
+        </is>
+      </c>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="inlineStr">
+        <is>
+          <t>برگشت به خودکار</t>
+        </is>
+      </c>
+      <c r="J10" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود. اگر در مود دستی ماند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K10" s="56" t="n"/>
       <c r="L10" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="61" t="inlineStr"/>
-      <c r="N10" s="61" t="inlineStr"/>
-      <c r="O10" s="63" t="inlineStr">
+      <c r="M10" s="56" t="n"/>
+      <c r="N10" s="56" t="n"/>
+      <c r="O10" s="58" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="63" t="inlineStr"/>
-      <c r="Q10" s="64" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P10" s="58" t="n"/>
+      <c r="Q10" s="60">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="55" t="inlineStr">
         <is>
-          <t>CH-014</t>
+          <t>CH-037</t>
         </is>
       </c>
       <c r="B11" s="56" t="inlineStr">
         <is>
-          <t>مود دستی: ددمن لینک</t>
+          <t>ورودی خارج بازه 22-30V</t>
         </is>
       </c>
       <c r="C11" s="57" t="inlineStr">
@@ -1619,448 +1578,10 @@
       </c>
       <c r="D11" s="56" t="inlineStr">
         <is>
-          <t>شارژر در مود تست دستی و در حال اجرای فرمان دستی است</t>
-        </is>
-      </c>
-      <c r="E11" s="65" t="inlineStr">
-        <is>
-          <t>گام ۱: کابل ارتباطی پنل (ESP) را بکش تا فرمان تازه‌ای نرسد.
-گام ۲: کرنومتر بگیر و شارژر را نگاه کن.
-گام ۳: کابل را وصل کن.</t>
-        </is>
-      </c>
-      <c r="F11" s="58" t="inlineStr">
-        <is>
-          <t>قطع ارتباط پنل حین مود دستی</t>
-        </is>
-      </c>
-      <c r="G11" s="58" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H11" s="56" t="inlineStr">
-        <is>
-          <t>بعد از چند ثانیه بی‌ارتباطی، شارژ دستی خودش متوقف می‌شود؛ نباید بی‌صاحب ادامه دهد</t>
-        </is>
-      </c>
-      <c r="I11" s="56" t="inlineStr">
-        <is>
-          <t>توقف خودکار با قطع ارتباط</t>
-        </is>
-      </c>
-      <c r="J11" s="56" t="inlineStr">
-        <is>
-          <t>توقف خودکار = قبول؛ ادامهٔ شارژ بی‌ارتباط = رد</t>
-        </is>
-      </c>
-      <c r="K11" s="56" t="inlineStr"/>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="56" t="inlineStr"/>
-      <c r="N11" s="56" t="inlineStr"/>
-      <c r="O11" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="58" t="inlineStr"/>
-      <c r="Q11" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
-        <is>
-          <t>CH-016</t>
-        </is>
-      </c>
-      <c r="B12" s="56" t="inlineStr">
-        <is>
-          <t>مود دستی: قطع 15V</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="56" t="inlineStr">
-        <is>
-          <t>شارژر در مود تست دستی در حال کار است</t>
-        </is>
-      </c>
-      <c r="E12" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: برق طبقهٔ قدرت شارژر را قطع کن (همان کاری که در تعمیرات می‌کنی).
-گام ۲: رفتار کانال را ببین.
-گام ۳: برق را برگردان.</t>
-        </is>
-      </c>
-      <c r="F12" s="58" t="inlineStr">
-        <is>
-          <t>قطع و وصل برق طبقهٔ قدرت در مود دستی</t>
-        </is>
-      </c>
-      <c r="G12" s="58" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H12" s="56" t="inlineStr">
-        <is>
-          <t>کانال همان لحظه بیکار و بی‌خطر می‌شود و با برگشت برق، رفتار عادی برمی‌گردد</t>
-        </is>
-      </c>
-      <c r="I12" s="56" t="inlineStr">
-        <is>
-          <t>بدون قفل اضافه</t>
-        </is>
-      </c>
-      <c r="J12" s="56" t="inlineStr">
-        <is>
-          <t>بیکار شدن فوری و برگشت تمیز = قبول؛ رفتار غیرعادی = رد</t>
-        </is>
-      </c>
-      <c r="K12" s="56" t="inlineStr"/>
-      <c r="L12" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="56" t="inlineStr"/>
-      <c r="N12" s="56" t="inlineStr"/>
-      <c r="O12" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="58" t="inlineStr"/>
-      <c r="Q12" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
-        <is>
-          <t>CH-017</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="inlineStr">
-        <is>
-          <t>مود دستی: قطع کانال</t>
-        </is>
-      </c>
-      <c r="C13" s="63" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D13" s="61" t="inlineStr">
-        <is>
-          <t>هر دو کانال شارژر در مود دستی در حال کارند (دو باتری وصل)</t>
-        </is>
-      </c>
-      <c r="E13" s="66" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل فقط یک کانال را خاموش کن.
-گام ۲: هر دو کانال را نگاه کن.
-گام ۳: کانال خاموش را دوباره روشن کن.</t>
-        </is>
-      </c>
-      <c r="F13" s="63" t="inlineStr">
-        <is>
-          <t>خاموش/روشن کردن یک کانال از پنل</t>
-        </is>
-      </c>
-      <c r="G13" s="63" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H13" s="61" t="inlineStr">
-        <is>
-          <t>فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد</t>
-        </is>
-      </c>
-      <c r="I13" s="61" t="inlineStr">
-        <is>
-          <t>استقلال دو کانال</t>
-        </is>
-      </c>
-      <c r="J13" s="61" t="inlineStr">
-        <is>
-          <t>استقلال کامل = قبول؛ اثر روی کانال دیگر = رد</t>
-        </is>
-      </c>
-      <c r="K13" s="61" t="inlineStr"/>
-      <c r="L13" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="61" t="inlineStr"/>
-      <c r="N13" s="61" t="inlineStr"/>
-      <c r="O13" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="63" t="inlineStr"/>
-      <c r="Q13" s="64" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="55" t="inlineStr">
-        <is>
-          <t>CH-018</t>
-        </is>
-      </c>
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>خروج از مود دستی</t>
-        </is>
-      </c>
-      <c r="C14" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="56" t="inlineStr">
-        <is>
-          <t>شارژر در مود تست دستی است</t>
-        </is>
-      </c>
-      <c r="E14" s="56" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل از مود دستی خارج شو.
-گام ۲: یک باتری نیمه‌خالی را زیر نظر بگیر.</t>
-        </is>
-      </c>
-      <c r="F14" s="58" t="inlineStr">
-        <is>
-          <t>خروج از مود دستی</t>
-        </is>
-      </c>
-      <c r="G14" s="58" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H14" s="56" t="inlineStr">
-        <is>
-          <t>شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود</t>
-        </is>
-      </c>
-      <c r="I14" s="56" t="inlineStr">
-        <is>
-          <t>برگشت به خودکار</t>
-        </is>
-      </c>
-      <c r="J14" s="56" t="inlineStr">
-        <is>
-          <t>شروع شارژ خودکار = قبول؛ ماندن در مود دستی = رد</t>
-        </is>
-      </c>
-      <c r="K14" s="56" t="inlineStr"/>
-      <c r="L14" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M14" s="56" t="inlineStr"/>
-      <c r="N14" s="56" t="inlineStr"/>
-      <c r="O14" s="58" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P14" s="58" t="inlineStr"/>
-      <c r="Q14" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
-        <is>
-          <t>CH-019</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="inlineStr">
-        <is>
-          <t>سقف duty زنده</t>
-        </is>
-      </c>
-      <c r="C15" s="63" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D15" s="61" t="inlineStr">
-        <is>
-          <t>دستگاه در حال شارژ یک باتری نیمه‌خالی است</t>
-        </is>
-      </c>
-      <c r="E15" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل سقف توان شارژ را کمتر کن.
-گام ۲: جریان شارژ را در پنل یا آمپرمتر ببین.
-گام ۳: سقف را به حالت اول برگردان.</t>
-        </is>
-      </c>
-      <c r="F15" s="63" t="inlineStr">
-        <is>
-          <t>کم و زیاد کردن سقف توان از پنل</t>
-        </is>
-      </c>
-      <c r="G15" s="63" t="inlineStr">
-        <is>
-          <t>پنج دقیقه</t>
-        </is>
-      </c>
-      <c r="H15" s="61" t="inlineStr">
-        <is>
-          <t>جریان شارژ به همان نسبت کم و زیاد می‌شود، بدون اینکه دستگاه خاموش یا خطادار شود</t>
-        </is>
-      </c>
-      <c r="I15" s="61" t="inlineStr">
-        <is>
-          <t>بدون قفل</t>
-        </is>
-      </c>
-      <c r="J15" s="61" t="inlineStr">
-        <is>
-          <t>دنبال‌کردن جریان از سقف = قبول؛ بی‌اثر بودن سقف = رد</t>
-        </is>
-      </c>
-      <c r="K15" s="61" t="inlineStr"/>
-      <c r="L15" s="59" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M15" s="61" t="inlineStr"/>
-      <c r="N15" s="61" t="inlineStr"/>
-      <c r="O15" s="63" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P15" s="63" t="inlineStr"/>
-      <c r="Q15" s="64" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
-        <is>
-          <t>CH-036</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>استراحت حرارتی 1h-&gt;10min</t>
-        </is>
-      </c>
-      <c r="C16" s="62" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>دو باتری خالی واقعی وصل و هر دو کانال آمادهٔ شارژ سنگین‌اند</t>
-        </is>
-      </c>
-      <c r="E16" s="61" t="inlineStr">
-        <is>
-          <t>گام ۱: هر دو کانال را با باتری خالی به شارژ بزن.
-گام ۲: حدود یک ساعت شارژ سنگین را زیر نظر بگیر (هر از چندی سر بزن).
-گام ۳: بعد از حدود یک ساعت، هر کانال باید حدود ده دقیقه استراحت کند: جریان صفر ولی باتری وصل می‌ماند.
-گام ۴: بعد از استراحت، شارژ باید خودش ادامه پیدا کند.</t>
-        </is>
-      </c>
-      <c r="F16" s="63" t="inlineStr">
-        <is>
-          <t>یک ساعت شارژ سنگین هر دو کانال</t>
-        </is>
-      </c>
-      <c r="G16" s="63" t="inlineStr">
-        <is>
-          <t>حدود یک ساعت و نیم</t>
-        </is>
-      </c>
-      <c r="H16" s="61" t="inlineStr">
-        <is>
-          <t>بعد از یک ساعت شارژ سنگین، هر کانال ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد</t>
-        </is>
-      </c>
-      <c r="I16" s="61" t="inlineStr">
-        <is>
-          <t>استراحت و ادامهٔ خودکار</t>
-        </is>
-      </c>
-      <c r="J16" s="61" t="inlineStr">
-        <is>
-          <t>استراحت و ادامهٔ خودکار = قبول؛ شارژ بی‌وقفهٔ چندساعته یا توقف همیشگی = رد</t>
-        </is>
-      </c>
-      <c r="K16" s="61" t="n"/>
-      <c r="L16" s="67" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M16" s="61" t="n"/>
-      <c r="N16" s="61" t="n"/>
-      <c r="O16" s="63" t="inlineStr">
-        <is>
-          <t>thermal</t>
-        </is>
-      </c>
-      <c r="P16" s="63" t="n"/>
-      <c r="Q16" s="64" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="55" t="inlineStr">
-        <is>
-          <t>CH-037</t>
-        </is>
-      </c>
-      <c r="B17" s="56" t="inlineStr">
-        <is>
-          <t>ورودی خارج بازه 22-30V</t>
-        </is>
-      </c>
-      <c r="C17" s="57" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید تا ولتاژش را عوض کنی؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E17" s="56" t="inlineStr">
+      <c r="E11" s="56" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را زیر ۲۲ ولت بیاور؛ شارژ نباید شروع شود.
 گام ۲: به ۲۴ ولت برگردان؛ شارژ باید شروع شود.
@@ -2068,73 +1589,72 @@
 گام ۴: به ۲۴ برگردان؛ شارژ باید خودش برگردد.</t>
         </is>
       </c>
-      <c r="F17" s="58" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>ورودی: پایین، ۲۴، بالا، ۲۴ ولت</t>
         </is>
       </c>
-      <c r="G17" s="58" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H17" s="56" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr">
         <is>
           <t>خارج از بازهٔ سالم شارژ نداریم و با برگشت ورودی به ۲۴ ولت شارژ خودش برمی‌گردد</t>
         </is>
       </c>
-      <c r="I17" s="56" t="inlineStr">
+      <c r="I11" s="56" t="inlineStr">
         <is>
           <t>بدون قفل</t>
         </is>
       </c>
-      <c r="J17" s="56" t="inlineStr">
-        <is>
-          <t>همین رفتار چهار مرحله = قبول؛ شارژ خارج از بازه یا برنگشتن = رد</t>
-        </is>
-      </c>
-      <c r="K17" s="56" t="n"/>
-      <c r="L17" s="67" t="inlineStr">
+      <c r="J11" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: خارج از بازهٔ سالم ورودی شارژی نیست و با برگشت ورودی به ۲۴ ولت شارژ خودش برمی‌گردد. اگر خارج از بازه شارژ کرد یا برنگشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K11" s="56" t="n"/>
+      <c r="L11" s="67" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M17" s="56" t="n"/>
-      <c r="N17" s="56" t="n"/>
-      <c r="O17" s="58" t="inlineStr">
+      <c r="M11" s="56" t="n"/>
+      <c r="N11" s="56" t="n"/>
+      <c r="O11" s="58" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
-      <c r="P17" s="58" t="n"/>
-      <c r="Q17" s="60" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="P11" s="58" t="n"/>
+      <c r="Q11" s="60">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>CH-040</t>
         </is>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>سناریوی ۶: باتری خراب دیگر شارژ نمی‌شود</t>
         </is>
       </c>
-      <c r="C18" s="57" t="inlineStr">
+      <c r="C12" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="56" t="inlineStr">
+      <c r="D12" s="56" t="inlineStr">
         <is>
           <t>از پنل زمان سناریوی باتری خراب (شناسهٔ ۱۲۵) را موقتاً روی چند دقیقه بگذار؛ یک باتری خالی وصل است</t>
         </is>
       </c>
-      <c r="E18" s="56" t="inlineStr">
+      <c r="E12" s="56" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت به شارژ کامل برسد.
 گام ۲: بعد از گذشت زمان تنظیم‌شده، ببین شارژ همان کانال متوقف شده و قرمز ثابت آمده.
@@ -2143,68 +1663,68 @@
 گام ۵: شناسهٔ ۱۲۵ را به مقدار واقعی (یک شبانه‌روز) برگردان.</t>
         </is>
       </c>
-      <c r="F18" s="58" t="inlineStr">
+      <c r="F12" s="58" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H18" s="56" t="inlineStr">
+      <c r="H12" s="56" t="inlineStr">
         <is>
           <t>بعد از زمان، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود</t>
         </is>
       </c>
-      <c r="I18" s="56" t="inlineStr">
+      <c r="I12" s="56" t="inlineStr">
         <is>
           <t>قفل تا تعویض باتری</t>
         </is>
       </c>
-      <c r="J18" s="56" t="inlineStr">
-        <is>
-          <t>توقف ماندگار و شروع با باتری سالم = قبول؛ شارژ دوبارهٔ همان باتری = رد</t>
-        </is>
-      </c>
-      <c r="K18" s="56" t="n"/>
-      <c r="L18" s="67" t="inlineStr">
+      <c r="J12" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از زمان تنظیم‌شده، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود؛ با باتری سالم شارژ عادی شروع می‌شود. اگر همان باتری دوباره شارژ شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K12" s="56" t="n"/>
+      <c r="L12" s="67" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="56" t="n"/>
-      <c r="N18" s="56" t="n"/>
-      <c r="O18" s="58" t="n"/>
-      <c r="P18" s="58" t="n"/>
-      <c r="Q18" s="60">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="M12" s="56" t="n"/>
+      <c r="N12" s="56" t="n"/>
+      <c r="O12" s="58" t="n"/>
+      <c r="P12" s="58" t="n"/>
+      <c r="Q12" s="60">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>CH-041</t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>خطای ۷: کانال بی‌جریان قفل فنی می‌سازد</t>
         </is>
       </c>
-      <c r="C19" s="57" t="inlineStr">
+      <c r="C13" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
+      <c r="D13" s="56" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ است و فیوز خروجی هر کانال را می‌شناسی</t>
         </is>
       </c>
-      <c r="E19" s="56" t="inlineStr">
+      <c r="E13" s="56" t="inlineStr">
         <is>
           <t>گام ۱: فیوز خروجی یک کانال را دربیاور.
 گام ۲: چند ثانیه صبر کن: شارژ کلاً باید قفل شود و هر سه چراغ با هم چشمک بزنند.
@@ -2212,881 +1732,1252 @@
 گام ۴: خاموش و روشن کن؛ شارژ عادی باید برگردد.</t>
         </is>
       </c>
-      <c r="F19" s="58" t="inlineStr">
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>دربیاوردن فیوز یک کانال حین شارژ</t>
         </is>
       </c>
-      <c r="G19" s="58" t="inlineStr">
+      <c r="G13" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="56" t="inlineStr">
+      <c r="H13" s="56" t="inlineStr">
         <is>
           <t>خطای فنی ۷ قفل می‌شود و فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
-      <c r="I19" s="56" t="inlineStr">
+      <c r="I13" s="56" t="inlineStr">
         <is>
           <t>قفل تا ریست</t>
         </is>
       </c>
-      <c r="J19" s="56" t="inlineStr">
-        <is>
-          <t>قفل فنی و پاک‌شدن فقط با ریست = قبول؛ ادامهٔ شارژ بی‌جریان = رد</t>
-        </is>
-      </c>
-      <c r="K19" s="56" t="n"/>
-      <c r="L19" s="67" t="inlineStr">
+      <c r="J13" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: خطای فنی قفل می‌شود و فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود. اگر شارژ بی‌جریان ادامه داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K13" s="56" t="n"/>
+      <c r="L13" s="67" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="56" t="n"/>
-      <c r="N19" s="56" t="n"/>
-      <c r="O19" s="58" t="n"/>
-      <c r="P19" s="58" t="n"/>
-      <c r="Q19" s="60">
+      <c r="M13" s="56" t="n"/>
+      <c r="N13" s="56" t="n"/>
+      <c r="O13" s="58" t="n"/>
+      <c r="P13" s="58" t="n"/>
+      <c r="Q13" s="60">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>CH-006</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>شستشوی ABSORB</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>باتری در شارژ پایانی (جذب) است</t>
+        </is>
+      </c>
+      <c r="E14" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ پایانی، یک مصرف کوتاه و واقعی از باتری بکش (مثلاً یک لامپ را چند ثانیه روشن کن) و بردار.
+گام ۲: رفتار شارژر را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F14" s="58" t="inlineStr">
+        <is>
+          <t>مصرف کوتاه حین شارژ پایانی</t>
+        </is>
+      </c>
+      <c r="G14" s="58" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="inlineStr">
+        <is>
+          <t>شارژر به شارژ تند برنمی‌گردد؛ همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود</t>
+        </is>
+      </c>
+      <c r="I14" s="56" t="inlineStr">
+        <is>
+          <t>بدون برگشت به شارژ تند</t>
+        </is>
+      </c>
+      <c r="J14" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: شارژر به شارژ تند برنمی‌گردد و همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود. اگر به جریان کامل برگشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K14" s="56" t="n"/>
+      <c r="L14" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M14" s="56" t="n"/>
+      <c r="N14" s="56" t="n"/>
+      <c r="O14" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P14" s="58" t="n"/>
+      <c r="Q14" s="60">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>CH-007</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>FLOAT و reentry</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>باتری کاملاً پر شده و شارژ به حالت نگهداری رسیده (جریان خیلی کم)</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: بگذار باتری کامل پر و شارژ آرام شود.
+گام ۲: یک بار واقعی روی خروجی بکش تا باتری کمی خالی شود.
+گام ۳: نگاه کن شارژ دوباره کی و چطور شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="F15" s="63" t="inlineStr">
+        <is>
+          <t>باتری پر، بعد کمی مصرف واقعی</t>
+        </is>
+      </c>
+      <c r="G15" s="63" t="inlineStr">
+        <is>
+          <t>ده دقیقه</t>
+        </is>
+      </c>
+      <c r="H15" s="61" t="inlineStr">
+        <is>
+          <t>در حالت پر، جریان نگهداری خیلی کم است؛ با کمی خالی‌شدن، شارژ خودش دوباره شروع می‌شود</t>
+        </is>
+      </c>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>رفت‌وبرگشت خودکار پر/شارژ</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: در حالت پر جریان نگهداری خیلی کم است و با کمی خالی‌شدن باتری، شارژ خودش دوباره شروع می‌شود. اگر دوباره شارژ نشد یا بی‌وقفه شارژ کرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="n"/>
+      <c r="O15" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P15" s="63" t="n"/>
+      <c r="Q15" s="64">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>CH-014</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>مود دستی: ددمن لینک</t>
+        </is>
+      </c>
+      <c r="C16" s="57" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>شارژر در مود تست دستی و در حال اجرای فرمان دستی است</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>گام ۱: کابل ارتباطی پنل (ESP) را بکش تا فرمان تازه‌ای نرسد.
+گام ۲: کرنومتر بگیر و شارژر را نگاه کن.
+گام ۳: کابل را وصل کن.</t>
+        </is>
+      </c>
+      <c r="F16" s="58" t="inlineStr">
+        <is>
+          <t>قطع ارتباط پنل حین مود دستی</t>
+        </is>
+      </c>
+      <c r="G16" s="58" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H16" s="56" t="inlineStr">
+        <is>
+          <t>بعد از چند ثانیه بی‌ارتباطی، شارژ دستی خودش متوقف می‌شود؛ نباید بی‌صاحب ادامه دهد</t>
+        </is>
+      </c>
+      <c r="I16" s="56" t="inlineStr">
+        <is>
+          <t>توقف خودکار با قطع ارتباط</t>
+        </is>
+      </c>
+      <c r="J16" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از چند ثانیه قطع ارتباط، شارژ دستی خودش متوقف می‌شود و بی‌صاحب ادامه نمی‌دهد. اگر بی‌ارتباط هم ادامه داد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K16" s="56" t="n"/>
+      <c r="L16" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M16" s="56" t="n"/>
+      <c r="N16" s="56" t="n"/>
+      <c r="O16" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P16" s="58" t="n"/>
+      <c r="Q16" s="60">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>CH-016</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>مود دستی: قطع 15V</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>شارژر در مود تست دستی در حال کار است</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="inlineStr">
+        <is>
+          <t>گام ۱: برق طبقهٔ قدرت شارژر را قطع کن (همان کاری که در تعمیرات می‌کنی).
+گام ۲: رفتار کانال را ببین.
+گام ۳: برق را برگردان.</t>
+        </is>
+      </c>
+      <c r="F17" s="58" t="inlineStr">
+        <is>
+          <t>قطع و وصل برق طبقهٔ قدرت در مود دستی</t>
+        </is>
+      </c>
+      <c r="G17" s="58" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H17" s="56" t="inlineStr">
+        <is>
+          <t>کانال همان لحظه بیکار و بی‌خطر می‌شود و با برگشت برق، رفتار عادی برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I17" s="56" t="inlineStr">
+        <is>
+          <t>بدون قفل اضافه</t>
+        </is>
+      </c>
+      <c r="J17" s="56" t="inlineStr">
+        <is>
+          <t>باید ببینید: کانال همان لحظه بیکار و بی‌خطر می‌شود و با برگشت برق رفتار عادی برمی‌گردد. اگر رفتار غیرعادی دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K17" s="56" t="n"/>
+      <c r="L17" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="56" t="n"/>
+      <c r="N17" s="56" t="n"/>
+      <c r="O17" s="58" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P17" s="58" t="n"/>
+      <c r="Q17" s="60">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>CH-017</t>
+        </is>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>مود دستی: قطع کانال</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D18" s="61" t="inlineStr">
+        <is>
+          <t>هر دو کانال شارژر در مود دستی در حال کارند (دو باتری وصل)</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل فقط یک کانال را خاموش کن.
+گام ۲: هر دو کانال را نگاه کن.
+گام ۳: کانال خاموش را دوباره روشن کن.</t>
+        </is>
+      </c>
+      <c r="F18" s="63" t="inlineStr">
+        <is>
+          <t>خاموش/روشن کردن یک کانال از پنل</t>
+        </is>
+      </c>
+      <c r="G18" s="63" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H18" s="61" t="inlineStr">
+        <is>
+          <t>فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد</t>
+        </is>
+      </c>
+      <c r="I18" s="61" t="inlineStr">
+        <is>
+          <t>استقلال دو کانال</t>
+        </is>
+      </c>
+      <c r="J18" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد. اگر روی کانال دیگر اثر گذاشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K18" s="61" t="n"/>
+      <c r="L18" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="61" t="n"/>
+      <c r="N18" s="61" t="n"/>
+      <c r="O18" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P18" s="63" t="n"/>
+      <c r="Q18" s="64">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>CH-019</t>
+        </is>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>سقف duty زنده</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>دستگاه در حال شارژ یک باتری نیمه‌خالی است</t>
+        </is>
+      </c>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل سقف توان شارژ را کمتر کن.
+گام ۲: جریان شارژ را در پنل یا آمپرمتر ببین.
+گام ۳: سقف را به حالت اول برگردان.</t>
+        </is>
+      </c>
+      <c r="F19" s="63" t="inlineStr">
+        <is>
+          <t>کم و زیاد کردن سقف توان از پنل</t>
+        </is>
+      </c>
+      <c r="G19" s="63" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H19" s="61" t="inlineStr">
+        <is>
+          <t>جریان شارژ به همان نسبت کم و زیاد می‌شود، بدون اینکه دستگاه خاموش یا خطادار شود</t>
+        </is>
+      </c>
+      <c r="I19" s="61" t="inlineStr">
+        <is>
+          <t>بدون قفل</t>
+        </is>
+      </c>
+      <c r="J19" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: جریان شارژ به همان نسبت سقف کم و زیاد می‌شود و دستگاه خاموش یا خطادار نمی‌شود. اگر سقف بی‌اثر بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K19" s="61" t="n"/>
+      <c r="L19" s="59" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="61" t="n"/>
+      <c r="N19" s="61" t="n"/>
+      <c r="O19" s="63" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P19" s="63" t="n"/>
+      <c r="Q19" s="64">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="54" t="n"/>
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="54" t="n"/>
-      <c r="G20" s="54" t="n"/>
-      <c r="H20" s="54" t="n"/>
-      <c r="I20" s="54" t="n"/>
-      <c r="J20" s="54" t="n"/>
-      <c r="K20" s="54" t="n"/>
-      <c r="L20" s="54" t="n"/>
-      <c r="M20" s="54" t="n"/>
-      <c r="N20" s="54" t="n"/>
-      <c r="O20" s="54" t="n"/>
-      <c r="P20" s="54" t="n"/>
-      <c r="Q20" s="68">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="54" t="n"/>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="54" t="n"/>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
-      <c r="K21" s="54" t="n"/>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="54" t="n"/>
-      <c r="O21" s="54" t="n"/>
-      <c r="P21" s="54" t="n"/>
-      <c r="Q21" s="68">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="54" t="n"/>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="54" t="n"/>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
-      <c r="K22" s="54" t="n"/>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="54" t="n"/>
-      <c r="O22" s="54" t="n"/>
-      <c r="P22" s="54" t="n"/>
-      <c r="Q22" s="68">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="54" t="n"/>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="54" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
-      <c r="K23" s="54" t="n"/>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="54" t="n"/>
-      <c r="O23" s="54" t="n"/>
-      <c r="P23" s="54" t="n"/>
-      <c r="Q23" s="68">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="54" t="n"/>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="54" t="n"/>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
-      <c r="K24" s="54" t="n"/>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="54" t="n"/>
-      <c r="O24" s="54" t="n"/>
-      <c r="P24" s="54" t="n"/>
-      <c r="Q24" s="68">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="54" t="n"/>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="54" t="n"/>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
-      <c r="K25" s="54" t="n"/>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="54" t="n"/>
-      <c r="O25" s="54" t="n"/>
-      <c r="P25" s="54" t="n"/>
-      <c r="Q25" s="68">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="54" t="n"/>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="54" t="n"/>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
-      <c r="K26" s="54" t="n"/>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="54" t="n"/>
-      <c r="O26" s="54" t="n"/>
-      <c r="P26" s="54" t="n"/>
-      <c r="Q26" s="68">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="54" t="n"/>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="54" t="n"/>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="54" t="n"/>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
-      <c r="K27" s="54" t="n"/>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="54" t="n"/>
-      <c r="O27" s="54" t="n"/>
-      <c r="P27" s="54" t="n"/>
-      <c r="Q27" s="68">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="54" t="n"/>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="54" t="n"/>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="54" t="n"/>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="54" t="n"/>
-      <c r="O28" s="54" t="n"/>
-      <c r="P28" s="54" t="n"/>
-      <c r="Q28" s="68">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>CH-036</t>
+        </is>
+      </c>
+      <c r="B20" s="61" t="inlineStr">
+        <is>
+          <t>استراحت حرارتی 1h-&gt;10min</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>دو باتری خالی واقعی وصل و هر دو کانال آمادهٔ شارژ سنگین‌اند</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>گام ۱: هر دو کانال را با باتری خالی به شارژ بزن.
+گام ۲: حدود یک ساعت شارژ سنگین را زیر نظر بگیر (هر از چندی سر بزن).
+گام ۳: بعد از حدود یک ساعت، هر کانال باید حدود ده دقیقه استراحت کند: جریان صفر ولی باتری وصل می‌ماند.
+گام ۴: بعد از استراحت، شارژ باید خودش ادامه پیدا کند.</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>یک ساعت شارژ سنگین هر دو کانال</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>حدود یک ساعت و نیم</t>
+        </is>
+      </c>
+      <c r="H20" s="61" t="inlineStr">
+        <is>
+          <t>بعد از یک ساعت شارژ سنگین، هر کانال ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I20" s="61" t="inlineStr">
+        <is>
+          <t>استراحت و ادامهٔ خودکار</t>
+        </is>
+      </c>
+      <c r="J20" s="61" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از حدود یک ساعت شارژ سنگین، کانال حدود ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد. اگر بی‌وقفه چند ساعت شارژ کرد یا برای همیشه ایستاد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K20" s="61" t="n"/>
+      <c r="L20" s="67" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M20" s="61" t="n"/>
+      <c r="N20" s="61" t="n"/>
+      <c r="O20" s="63" t="inlineStr">
+        <is>
+          <t>thermal</t>
+        </is>
+      </c>
+      <c r="P20" s="63" t="n"/>
+      <c r="Q20" s="64">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="n"/>
+      <c r="B21" s="83" t="n"/>
+      <c r="C21" s="83" t="n"/>
+      <c r="D21" s="83" t="n"/>
+      <c r="E21" s="83" t="n"/>
+      <c r="F21" s="83" t="n"/>
+      <c r="G21" s="83" t="n"/>
+      <c r="H21" s="83" t="n"/>
+      <c r="I21" s="83" t="n"/>
+      <c r="J21" s="83" t="n"/>
+      <c r="K21" s="83" t="n"/>
+      <c r="L21" s="83" t="n"/>
+      <c r="M21" s="83" t="n"/>
+      <c r="N21" s="83" t="n"/>
+      <c r="O21" s="83" t="n"/>
+      <c r="P21" s="83" t="n"/>
+      <c r="Q21" s="84" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="n"/>
+      <c r="B22" s="83" t="n"/>
+      <c r="C22" s="83" t="n"/>
+      <c r="D22" s="83" t="n"/>
+      <c r="E22" s="83" t="n"/>
+      <c r="F22" s="83" t="n"/>
+      <c r="G22" s="83" t="n"/>
+      <c r="H22" s="83" t="n"/>
+      <c r="I22" s="83" t="n"/>
+      <c r="J22" s="83" t="n"/>
+      <c r="K22" s="83" t="n"/>
+      <c r="L22" s="83" t="n"/>
+      <c r="M22" s="83" t="n"/>
+      <c r="N22" s="83" t="n"/>
+      <c r="O22" s="83" t="n"/>
+      <c r="P22" s="83" t="n"/>
+      <c r="Q22" s="84" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="83" t="n"/>
+      <c r="B23" s="83" t="n"/>
+      <c r="C23" s="83" t="n"/>
+      <c r="D23" s="83" t="n"/>
+      <c r="E23" s="83" t="n"/>
+      <c r="F23" s="83" t="n"/>
+      <c r="G23" s="83" t="n"/>
+      <c r="H23" s="83" t="n"/>
+      <c r="I23" s="83" t="n"/>
+      <c r="J23" s="83" t="n"/>
+      <c r="K23" s="83" t="n"/>
+      <c r="L23" s="83" t="n"/>
+      <c r="M23" s="83" t="n"/>
+      <c r="N23" s="83" t="n"/>
+      <c r="O23" s="83" t="n"/>
+      <c r="P23" s="83" t="n"/>
+      <c r="Q23" s="84" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="83" t="n"/>
+      <c r="B24" s="83" t="n"/>
+      <c r="C24" s="83" t="n"/>
+      <c r="D24" s="83" t="n"/>
+      <c r="E24" s="83" t="n"/>
+      <c r="F24" s="83" t="n"/>
+      <c r="G24" s="83" t="n"/>
+      <c r="H24" s="83" t="n"/>
+      <c r="I24" s="83" t="n"/>
+      <c r="J24" s="83" t="n"/>
+      <c r="K24" s="83" t="n"/>
+      <c r="L24" s="83" t="n"/>
+      <c r="M24" s="83" t="n"/>
+      <c r="N24" s="83" t="n"/>
+      <c r="O24" s="83" t="n"/>
+      <c r="P24" s="83" t="n"/>
+      <c r="Q24" s="84" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="83" t="n"/>
+      <c r="B25" s="83" t="n"/>
+      <c r="C25" s="83" t="n"/>
+      <c r="D25" s="83" t="n"/>
+      <c r="E25" s="83" t="n"/>
+      <c r="F25" s="83" t="n"/>
+      <c r="G25" s="83" t="n"/>
+      <c r="H25" s="83" t="n"/>
+      <c r="I25" s="83" t="n"/>
+      <c r="J25" s="83" t="n"/>
+      <c r="K25" s="83" t="n"/>
+      <c r="L25" s="83" t="n"/>
+      <c r="M25" s="83" t="n"/>
+      <c r="N25" s="83" t="n"/>
+      <c r="O25" s="83" t="n"/>
+      <c r="P25" s="83" t="n"/>
+      <c r="Q25" s="84" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="83" t="n"/>
+      <c r="B26" s="83" t="n"/>
+      <c r="C26" s="83" t="n"/>
+      <c r="D26" s="83" t="n"/>
+      <c r="E26" s="83" t="n"/>
+      <c r="F26" s="83" t="n"/>
+      <c r="G26" s="83" t="n"/>
+      <c r="H26" s="83" t="n"/>
+      <c r="I26" s="83" t="n"/>
+      <c r="J26" s="83" t="n"/>
+      <c r="K26" s="83" t="n"/>
+      <c r="L26" s="83" t="n"/>
+      <c r="M26" s="83" t="n"/>
+      <c r="N26" s="83" t="n"/>
+      <c r="O26" s="83" t="n"/>
+      <c r="P26" s="83" t="n"/>
+      <c r="Q26" s="84" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="83" t="n"/>
+      <c r="B27" s="83" t="n"/>
+      <c r="C27" s="83" t="n"/>
+      <c r="D27" s="83" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
+      <c r="G27" s="83" t="n"/>
+      <c r="H27" s="83" t="n"/>
+      <c r="I27" s="83" t="n"/>
+      <c r="J27" s="83" t="n"/>
+      <c r="K27" s="83" t="n"/>
+      <c r="L27" s="83" t="n"/>
+      <c r="M27" s="83" t="n"/>
+      <c r="N27" s="83" t="n"/>
+      <c r="O27" s="83" t="n"/>
+      <c r="P27" s="83" t="n"/>
+      <c r="Q27" s="84" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="83" t="n"/>
+      <c r="B28" s="83" t="n"/>
+      <c r="C28" s="83" t="n"/>
+      <c r="D28" s="83" t="n"/>
+      <c r="E28" s="83" t="n"/>
+      <c r="F28" s="83" t="n"/>
+      <c r="G28" s="83" t="n"/>
+      <c r="H28" s="83" t="n"/>
+      <c r="I28" s="83" t="n"/>
+      <c r="J28" s="83" t="n"/>
+      <c r="K28" s="83" t="n"/>
+      <c r="L28" s="83" t="n"/>
+      <c r="M28" s="83" t="n"/>
+      <c r="N28" s="83" t="n"/>
+      <c r="O28" s="83" t="n"/>
+      <c r="P28" s="83" t="n"/>
+      <c r="Q28" s="84" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="54" t="n"/>
-      <c r="B29" s="54" t="n"/>
-      <c r="C29" s="54" t="n"/>
-      <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="54" t="n"/>
-      <c r="G29" s="54" t="n"/>
-      <c r="H29" s="54" t="n"/>
-      <c r="I29" s="54" t="n"/>
-      <c r="J29" s="54" t="n"/>
-      <c r="K29" s="54" t="n"/>
-      <c r="L29" s="54" t="n"/>
-      <c r="M29" s="54" t="n"/>
-      <c r="N29" s="54" t="n"/>
-      <c r="O29" s="54" t="n"/>
-      <c r="P29" s="54" t="n"/>
-      <c r="Q29" s="68">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A29" s="83" t="n"/>
+      <c r="B29" s="83" t="n"/>
+      <c r="C29" s="83" t="n"/>
+      <c r="D29" s="83" t="n"/>
+      <c r="E29" s="83" t="n"/>
+      <c r="F29" s="83" t="n"/>
+      <c r="G29" s="83" t="n"/>
+      <c r="H29" s="83" t="n"/>
+      <c r="I29" s="83" t="n"/>
+      <c r="J29" s="83" t="n"/>
+      <c r="K29" s="83" t="n"/>
+      <c r="L29" s="83" t="n"/>
+      <c r="M29" s="83" t="n"/>
+      <c r="N29" s="83" t="n"/>
+      <c r="O29" s="83" t="n"/>
+      <c r="P29" s="83" t="n"/>
+      <c r="Q29" s="84" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="n"/>
-      <c r="B30" s="54" t="n"/>
-      <c r="C30" s="54" t="n"/>
-      <c r="D30" s="54" t="n"/>
-      <c r="E30" s="54" t="n"/>
-      <c r="F30" s="54" t="n"/>
-      <c r="G30" s="54" t="n"/>
-      <c r="H30" s="54" t="n"/>
-      <c r="I30" s="54" t="n"/>
-      <c r="J30" s="54" t="n"/>
-      <c r="K30" s="54" t="n"/>
-      <c r="L30" s="54" t="n"/>
-      <c r="M30" s="54" t="n"/>
-      <c r="N30" s="54" t="n"/>
-      <c r="O30" s="54" t="n"/>
-      <c r="P30" s="54" t="n"/>
-      <c r="Q30" s="68">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A30" s="83" t="n"/>
+      <c r="B30" s="83" t="n"/>
+      <c r="C30" s="83" t="n"/>
+      <c r="D30" s="83" t="n"/>
+      <c r="E30" s="83" t="n"/>
+      <c r="F30" s="83" t="n"/>
+      <c r="G30" s="83" t="n"/>
+      <c r="H30" s="83" t="n"/>
+      <c r="I30" s="83" t="n"/>
+      <c r="J30" s="83" t="n"/>
+      <c r="K30" s="83" t="n"/>
+      <c r="L30" s="83" t="n"/>
+      <c r="M30" s="83" t="n"/>
+      <c r="N30" s="83" t="n"/>
+      <c r="O30" s="83" t="n"/>
+      <c r="P30" s="83" t="n"/>
+      <c r="Q30" s="84" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="54" t="n"/>
-      <c r="B31" s="54" t="n"/>
-      <c r="C31" s="54" t="n"/>
-      <c r="D31" s="54" t="n"/>
-      <c r="E31" s="54" t="n"/>
-      <c r="F31" s="54" t="n"/>
-      <c r="G31" s="54" t="n"/>
-      <c r="H31" s="54" t="n"/>
-      <c r="I31" s="54" t="n"/>
-      <c r="J31" s="54" t="n"/>
-      <c r="K31" s="54" t="n"/>
-      <c r="L31" s="54" t="n"/>
-      <c r="M31" s="54" t="n"/>
-      <c r="N31" s="54" t="n"/>
-      <c r="O31" s="54" t="n"/>
-      <c r="P31" s="54" t="n"/>
-      <c r="Q31" s="68">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A31" s="83" t="n"/>
+      <c r="B31" s="83" t="n"/>
+      <c r="C31" s="83" t="n"/>
+      <c r="D31" s="83" t="n"/>
+      <c r="E31" s="83" t="n"/>
+      <c r="F31" s="83" t="n"/>
+      <c r="G31" s="83" t="n"/>
+      <c r="H31" s="83" t="n"/>
+      <c r="I31" s="83" t="n"/>
+      <c r="J31" s="83" t="n"/>
+      <c r="K31" s="83" t="n"/>
+      <c r="L31" s="83" t="n"/>
+      <c r="M31" s="83" t="n"/>
+      <c r="N31" s="83" t="n"/>
+      <c r="O31" s="83" t="n"/>
+      <c r="P31" s="83" t="n"/>
+      <c r="Q31" s="84" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="n"/>
-      <c r="B32" s="54" t="n"/>
-      <c r="C32" s="54" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="54" t="n"/>
-      <c r="F32" s="54" t="n"/>
-      <c r="G32" s="54" t="n"/>
-      <c r="H32" s="54" t="n"/>
-      <c r="I32" s="54" t="n"/>
-      <c r="J32" s="54" t="n"/>
-      <c r="K32" s="54" t="n"/>
-      <c r="L32" s="54" t="n"/>
-      <c r="M32" s="54" t="n"/>
-      <c r="N32" s="54" t="n"/>
-      <c r="O32" s="54" t="n"/>
-      <c r="P32" s="54" t="n"/>
-      <c r="Q32" s="68">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A32" s="83" t="n"/>
+      <c r="B32" s="83" t="n"/>
+      <c r="C32" s="83" t="n"/>
+      <c r="D32" s="83" t="n"/>
+      <c r="E32" s="83" t="n"/>
+      <c r="F32" s="83" t="n"/>
+      <c r="G32" s="83" t="n"/>
+      <c r="H32" s="83" t="n"/>
+      <c r="I32" s="83" t="n"/>
+      <c r="J32" s="83" t="n"/>
+      <c r="K32" s="83" t="n"/>
+      <c r="L32" s="83" t="n"/>
+      <c r="M32" s="83" t="n"/>
+      <c r="N32" s="83" t="n"/>
+      <c r="O32" s="83" t="n"/>
+      <c r="P32" s="83" t="n"/>
+      <c r="Q32" s="84" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="54" t="n"/>
-      <c r="B33" s="54" t="n"/>
-      <c r="C33" s="54" t="n"/>
-      <c r="D33" s="54" t="n"/>
-      <c r="E33" s="54" t="n"/>
-      <c r="F33" s="54" t="n"/>
-      <c r="G33" s="54" t="n"/>
-      <c r="H33" s="54" t="n"/>
-      <c r="I33" s="54" t="n"/>
-      <c r="J33" s="54" t="n"/>
-      <c r="K33" s="54" t="n"/>
-      <c r="L33" s="54" t="n"/>
-      <c r="M33" s="54" t="n"/>
-      <c r="N33" s="54" t="n"/>
-      <c r="O33" s="54" t="n"/>
-      <c r="P33" s="54" t="n"/>
-      <c r="Q33" s="68">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A33" s="83" t="n"/>
+      <c r="B33" s="83" t="n"/>
+      <c r="C33" s="83" t="n"/>
+      <c r="D33" s="83" t="n"/>
+      <c r="E33" s="83" t="n"/>
+      <c r="F33" s="83" t="n"/>
+      <c r="G33" s="83" t="n"/>
+      <c r="H33" s="83" t="n"/>
+      <c r="I33" s="83" t="n"/>
+      <c r="J33" s="83" t="n"/>
+      <c r="K33" s="83" t="n"/>
+      <c r="L33" s="83" t="n"/>
+      <c r="M33" s="83" t="n"/>
+      <c r="N33" s="83" t="n"/>
+      <c r="O33" s="83" t="n"/>
+      <c r="P33" s="83" t="n"/>
+      <c r="Q33" s="84" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="n"/>
-      <c r="B34" s="54" t="n"/>
-      <c r="C34" s="54" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="54" t="n"/>
-      <c r="F34" s="54" t="n"/>
-      <c r="G34" s="54" t="n"/>
-      <c r="H34" s="54" t="n"/>
-      <c r="I34" s="54" t="n"/>
-      <c r="J34" s="54" t="n"/>
-      <c r="K34" s="54" t="n"/>
-      <c r="L34" s="54" t="n"/>
-      <c r="M34" s="54" t="n"/>
-      <c r="N34" s="54" t="n"/>
-      <c r="O34" s="54" t="n"/>
-      <c r="P34" s="54" t="n"/>
-      <c r="Q34" s="68">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A34" s="83" t="n"/>
+      <c r="B34" s="83" t="n"/>
+      <c r="C34" s="83" t="n"/>
+      <c r="D34" s="83" t="n"/>
+      <c r="E34" s="83" t="n"/>
+      <c r="F34" s="83" t="n"/>
+      <c r="G34" s="83" t="n"/>
+      <c r="H34" s="83" t="n"/>
+      <c r="I34" s="83" t="n"/>
+      <c r="J34" s="83" t="n"/>
+      <c r="K34" s="83" t="n"/>
+      <c r="L34" s="83" t="n"/>
+      <c r="M34" s="83" t="n"/>
+      <c r="N34" s="83" t="n"/>
+      <c r="O34" s="83" t="n"/>
+      <c r="P34" s="83" t="n"/>
+      <c r="Q34" s="84" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="54" t="n"/>
-      <c r="B35" s="54" t="n"/>
-      <c r="C35" s="54" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="54" t="n"/>
-      <c r="F35" s="54" t="n"/>
-      <c r="G35" s="54" t="n"/>
-      <c r="H35" s="54" t="n"/>
-      <c r="I35" s="54" t="n"/>
-      <c r="J35" s="54" t="n"/>
-      <c r="K35" s="54" t="n"/>
-      <c r="L35" s="54" t="n"/>
-      <c r="M35" s="54" t="n"/>
-      <c r="N35" s="54" t="n"/>
-      <c r="O35" s="54" t="n"/>
-      <c r="P35" s="54" t="n"/>
-      <c r="Q35" s="68">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A35" s="83" t="n"/>
+      <c r="B35" s="83" t="n"/>
+      <c r="C35" s="83" t="n"/>
+      <c r="D35" s="83" t="n"/>
+      <c r="E35" s="83" t="n"/>
+      <c r="F35" s="83" t="n"/>
+      <c r="G35" s="83" t="n"/>
+      <c r="H35" s="83" t="n"/>
+      <c r="I35" s="83" t="n"/>
+      <c r="J35" s="83" t="n"/>
+      <c r="K35" s="83" t="n"/>
+      <c r="L35" s="83" t="n"/>
+      <c r="M35" s="83" t="n"/>
+      <c r="N35" s="83" t="n"/>
+      <c r="O35" s="83" t="n"/>
+      <c r="P35" s="83" t="n"/>
+      <c r="Q35" s="84" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="n"/>
-      <c r="B36" s="54" t="n"/>
-      <c r="C36" s="54" t="n"/>
-      <c r="D36" s="54" t="n"/>
-      <c r="E36" s="54" t="n"/>
-      <c r="F36" s="54" t="n"/>
-      <c r="G36" s="54" t="n"/>
-      <c r="H36" s="54" t="n"/>
-      <c r="I36" s="54" t="n"/>
-      <c r="J36" s="54" t="n"/>
-      <c r="K36" s="54" t="n"/>
-      <c r="L36" s="54" t="n"/>
-      <c r="M36" s="54" t="n"/>
-      <c r="N36" s="54" t="n"/>
-      <c r="O36" s="54" t="n"/>
-      <c r="P36" s="54" t="n"/>
-      <c r="Q36" s="68">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A36" s="83" t="n"/>
+      <c r="B36" s="83" t="n"/>
+      <c r="C36" s="83" t="n"/>
+      <c r="D36" s="83" t="n"/>
+      <c r="E36" s="83" t="n"/>
+      <c r="F36" s="83" t="n"/>
+      <c r="G36" s="83" t="n"/>
+      <c r="H36" s="83" t="n"/>
+      <c r="I36" s="83" t="n"/>
+      <c r="J36" s="83" t="n"/>
+      <c r="K36" s="83" t="n"/>
+      <c r="L36" s="83" t="n"/>
+      <c r="M36" s="83" t="n"/>
+      <c r="N36" s="83" t="n"/>
+      <c r="O36" s="83" t="n"/>
+      <c r="P36" s="83" t="n"/>
+      <c r="Q36" s="84" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="n"/>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="54" t="n"/>
-      <c r="G37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="54" t="n"/>
-      <c r="O37" s="54" t="n"/>
-      <c r="P37" s="54" t="n"/>
-      <c r="Q37" s="68">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A37" s="83" t="n"/>
+      <c r="B37" s="83" t="n"/>
+      <c r="C37" s="83" t="n"/>
+      <c r="D37" s="83" t="n"/>
+      <c r="E37" s="83" t="n"/>
+      <c r="F37" s="83" t="n"/>
+      <c r="G37" s="83" t="n"/>
+      <c r="H37" s="83" t="n"/>
+      <c r="I37" s="83" t="n"/>
+      <c r="J37" s="83" t="n"/>
+      <c r="K37" s="83" t="n"/>
+      <c r="L37" s="83" t="n"/>
+      <c r="M37" s="83" t="n"/>
+      <c r="N37" s="83" t="n"/>
+      <c r="O37" s="83" t="n"/>
+      <c r="P37" s="83" t="n"/>
+      <c r="Q37" s="84" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="n"/>
-      <c r="B38" s="54" t="n"/>
-      <c r="C38" s="54" t="n"/>
-      <c r="D38" s="54" t="n"/>
-      <c r="E38" s="54" t="n"/>
-      <c r="F38" s="54" t="n"/>
-      <c r="G38" s="54" t="n"/>
-      <c r="H38" s="54" t="n"/>
-      <c r="I38" s="54" t="n"/>
-      <c r="J38" s="54" t="n"/>
-      <c r="K38" s="54" t="n"/>
-      <c r="L38" s="54" t="n"/>
-      <c r="M38" s="54" t="n"/>
-      <c r="N38" s="54" t="n"/>
-      <c r="O38" s="54" t="n"/>
-      <c r="P38" s="54" t="n"/>
-      <c r="Q38" s="68">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A38" s="83" t="n"/>
+      <c r="B38" s="83" t="n"/>
+      <c r="C38" s="83" t="n"/>
+      <c r="D38" s="83" t="n"/>
+      <c r="E38" s="83" t="n"/>
+      <c r="F38" s="83" t="n"/>
+      <c r="G38" s="83" t="n"/>
+      <c r="H38" s="83" t="n"/>
+      <c r="I38" s="83" t="n"/>
+      <c r="J38" s="83" t="n"/>
+      <c r="K38" s="83" t="n"/>
+      <c r="L38" s="83" t="n"/>
+      <c r="M38" s="83" t="n"/>
+      <c r="N38" s="83" t="n"/>
+      <c r="O38" s="83" t="n"/>
+      <c r="P38" s="83" t="n"/>
+      <c r="Q38" s="84" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="54" t="n"/>
-      <c r="B39" s="54" t="n"/>
-      <c r="C39" s="54" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="n"/>
-      <c r="F39" s="54" t="n"/>
-      <c r="G39" s="54" t="n"/>
-      <c r="H39" s="54" t="n"/>
-      <c r="I39" s="54" t="n"/>
-      <c r="J39" s="54" t="n"/>
-      <c r="K39" s="54" t="n"/>
-      <c r="L39" s="54" t="n"/>
-      <c r="M39" s="54" t="n"/>
-      <c r="N39" s="54" t="n"/>
-      <c r="O39" s="54" t="n"/>
-      <c r="P39" s="54" t="n"/>
-      <c r="Q39" s="68">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A39" s="83" t="n"/>
+      <c r="B39" s="83" t="n"/>
+      <c r="C39" s="83" t="n"/>
+      <c r="D39" s="83" t="n"/>
+      <c r="E39" s="83" t="n"/>
+      <c r="F39" s="83" t="n"/>
+      <c r="G39" s="83" t="n"/>
+      <c r="H39" s="83" t="n"/>
+      <c r="I39" s="83" t="n"/>
+      <c r="J39" s="83" t="n"/>
+      <c r="K39" s="83" t="n"/>
+      <c r="L39" s="83" t="n"/>
+      <c r="M39" s="83" t="n"/>
+      <c r="N39" s="83" t="n"/>
+      <c r="O39" s="83" t="n"/>
+      <c r="P39" s="83" t="n"/>
+      <c r="Q39" s="84" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="54" t="n"/>
-      <c r="B40" s="54" t="n"/>
-      <c r="C40" s="54" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="F40" s="54" t="n"/>
-      <c r="G40" s="54" t="n"/>
-      <c r="H40" s="54" t="n"/>
-      <c r="I40" s="54" t="n"/>
-      <c r="J40" s="54" t="n"/>
-      <c r="K40" s="54" t="n"/>
-      <c r="L40" s="54" t="n"/>
-      <c r="M40" s="54" t="n"/>
-      <c r="N40" s="54" t="n"/>
-      <c r="O40" s="54" t="n"/>
-      <c r="P40" s="54" t="n"/>
-      <c r="Q40" s="68">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A40" s="83" t="n"/>
+      <c r="B40" s="83" t="n"/>
+      <c r="C40" s="83" t="n"/>
+      <c r="D40" s="83" t="n"/>
+      <c r="E40" s="83" t="n"/>
+      <c r="F40" s="83" t="n"/>
+      <c r="G40" s="83" t="n"/>
+      <c r="H40" s="83" t="n"/>
+      <c r="I40" s="83" t="n"/>
+      <c r="J40" s="83" t="n"/>
+      <c r="K40" s="83" t="n"/>
+      <c r="L40" s="83" t="n"/>
+      <c r="M40" s="83" t="n"/>
+      <c r="N40" s="83" t="n"/>
+      <c r="O40" s="83" t="n"/>
+      <c r="P40" s="83" t="n"/>
+      <c r="Q40" s="84" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="54" t="n"/>
-      <c r="B41" s="54" t="n"/>
-      <c r="C41" s="54" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="54" t="n"/>
-      <c r="F41" s="54" t="n"/>
-      <c r="G41" s="54" t="n"/>
-      <c r="H41" s="54" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="54" t="n"/>
-      <c r="K41" s="54" t="n"/>
-      <c r="L41" s="54" t="n"/>
-      <c r="M41" s="54" t="n"/>
-      <c r="N41" s="54" t="n"/>
-      <c r="O41" s="54" t="n"/>
-      <c r="P41" s="54" t="n"/>
-      <c r="Q41" s="68">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A41" s="83" t="n"/>
+      <c r="B41" s="83" t="n"/>
+      <c r="C41" s="83" t="n"/>
+      <c r="D41" s="83" t="n"/>
+      <c r="E41" s="83" t="n"/>
+      <c r="F41" s="83" t="n"/>
+      <c r="G41" s="83" t="n"/>
+      <c r="H41" s="83" t="n"/>
+      <c r="I41" s="83" t="n"/>
+      <c r="J41" s="83" t="n"/>
+      <c r="K41" s="83" t="n"/>
+      <c r="L41" s="83" t="n"/>
+      <c r="M41" s="83" t="n"/>
+      <c r="N41" s="83" t="n"/>
+      <c r="O41" s="83" t="n"/>
+      <c r="P41" s="83" t="n"/>
+      <c r="Q41" s="84" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="54" t="n"/>
-      <c r="B42" s="54" t="n"/>
-      <c r="C42" s="54" t="n"/>
-      <c r="D42" s="54" t="n"/>
-      <c r="E42" s="54" t="n"/>
-      <c r="F42" s="54" t="n"/>
-      <c r="G42" s="54" t="n"/>
-      <c r="H42" s="54" t="n"/>
-      <c r="I42" s="54" t="n"/>
-      <c r="J42" s="54" t="n"/>
-      <c r="K42" s="54" t="n"/>
-      <c r="L42" s="54" t="n"/>
-      <c r="M42" s="54" t="n"/>
-      <c r="N42" s="54" t="n"/>
-      <c r="O42" s="54" t="n"/>
-      <c r="P42" s="54" t="n"/>
-      <c r="Q42" s="68">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A42" s="83" t="n"/>
+      <c r="B42" s="83" t="n"/>
+      <c r="C42" s="83" t="n"/>
+      <c r="D42" s="83" t="n"/>
+      <c r="E42" s="83" t="n"/>
+      <c r="F42" s="83" t="n"/>
+      <c r="G42" s="83" t="n"/>
+      <c r="H42" s="83" t="n"/>
+      <c r="I42" s="83" t="n"/>
+      <c r="J42" s="83" t="n"/>
+      <c r="K42" s="83" t="n"/>
+      <c r="L42" s="83" t="n"/>
+      <c r="M42" s="83" t="n"/>
+      <c r="N42" s="83" t="n"/>
+      <c r="O42" s="83" t="n"/>
+      <c r="P42" s="83" t="n"/>
+      <c r="Q42" s="84" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="54" t="n"/>
-      <c r="B43" s="54" t="n"/>
-      <c r="C43" s="54" t="n"/>
-      <c r="D43" s="54" t="n"/>
-      <c r="E43" s="54" t="n"/>
-      <c r="F43" s="54" t="n"/>
-      <c r="G43" s="54" t="n"/>
-      <c r="H43" s="54" t="n"/>
-      <c r="I43" s="54" t="n"/>
-      <c r="J43" s="54" t="n"/>
-      <c r="K43" s="54" t="n"/>
-      <c r="L43" s="54" t="n"/>
-      <c r="M43" s="54" t="n"/>
-      <c r="N43" s="54" t="n"/>
-      <c r="O43" s="54" t="n"/>
-      <c r="P43" s="54" t="n"/>
-      <c r="Q43" s="68">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A43" s="83" t="n"/>
+      <c r="B43" s="83" t="n"/>
+      <c r="C43" s="83" t="n"/>
+      <c r="D43" s="83" t="n"/>
+      <c r="E43" s="83" t="n"/>
+      <c r="F43" s="83" t="n"/>
+      <c r="G43" s="83" t="n"/>
+      <c r="H43" s="83" t="n"/>
+      <c r="I43" s="83" t="n"/>
+      <c r="J43" s="83" t="n"/>
+      <c r="K43" s="83" t="n"/>
+      <c r="L43" s="83" t="n"/>
+      <c r="M43" s="83" t="n"/>
+      <c r="N43" s="83" t="n"/>
+      <c r="O43" s="83" t="n"/>
+      <c r="P43" s="83" t="n"/>
+      <c r="Q43" s="84" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="54" t="n"/>
-      <c r="B44" s="54" t="n"/>
-      <c r="C44" s="54" t="n"/>
-      <c r="D44" s="54" t="n"/>
-      <c r="E44" s="54" t="n"/>
-      <c r="F44" s="54" t="n"/>
-      <c r="G44" s="54" t="n"/>
-      <c r="H44" s="54" t="n"/>
-      <c r="I44" s="54" t="n"/>
-      <c r="J44" s="54" t="n"/>
-      <c r="K44" s="54" t="n"/>
-      <c r="L44" s="54" t="n"/>
-      <c r="M44" s="54" t="n"/>
-      <c r="N44" s="54" t="n"/>
-      <c r="O44" s="54" t="n"/>
-      <c r="P44" s="54" t="n"/>
-      <c r="Q44" s="68">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A44" s="83" t="n"/>
+      <c r="B44" s="83" t="n"/>
+      <c r="C44" s="83" t="n"/>
+      <c r="D44" s="83" t="n"/>
+      <c r="E44" s="83" t="n"/>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="83" t="n"/>
+      <c r="H44" s="83" t="n"/>
+      <c r="I44" s="83" t="n"/>
+      <c r="J44" s="83" t="n"/>
+      <c r="K44" s="83" t="n"/>
+      <c r="L44" s="83" t="n"/>
+      <c r="M44" s="83" t="n"/>
+      <c r="N44" s="83" t="n"/>
+      <c r="O44" s="83" t="n"/>
+      <c r="P44" s="83" t="n"/>
+      <c r="Q44" s="84" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="n"/>
-      <c r="B45" s="54" t="n"/>
-      <c r="C45" s="54" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="54" t="n"/>
-      <c r="F45" s="54" t="n"/>
-      <c r="G45" s="54" t="n"/>
-      <c r="H45" s="54" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="54" t="n"/>
-      <c r="K45" s="54" t="n"/>
-      <c r="L45" s="54" t="n"/>
-      <c r="M45" s="54" t="n"/>
-      <c r="N45" s="54" t="n"/>
-      <c r="O45" s="54" t="n"/>
-      <c r="P45" s="54" t="n"/>
-      <c r="Q45" s="68">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
+      <c r="A45" s="83" t="n"/>
+      <c r="B45" s="83" t="n"/>
+      <c r="C45" s="83" t="n"/>
+      <c r="D45" s="83" t="n"/>
+      <c r="E45" s="83" t="n"/>
+      <c r="F45" s="83" t="n"/>
+      <c r="G45" s="83" t="n"/>
+      <c r="H45" s="83" t="n"/>
+      <c r="I45" s="83" t="n"/>
+      <c r="J45" s="83" t="n"/>
+      <c r="K45" s="83" t="n"/>
+      <c r="L45" s="83" t="n"/>
+      <c r="M45" s="83" t="n"/>
+      <c r="N45" s="83" t="n"/>
+      <c r="O45" s="83" t="n"/>
+      <c r="P45" s="83" t="n"/>
+      <c r="Q45" s="84" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="54" t="n"/>
-      <c r="B46" s="54" t="n"/>
-      <c r="C46" s="54" t="n"/>
-      <c r="D46" s="54" t="n"/>
-      <c r="E46" s="54" t="n"/>
-      <c r="F46" s="54" t="n"/>
-      <c r="G46" s="54" t="n"/>
-      <c r="H46" s="54" t="n"/>
-      <c r="I46" s="54" t="n"/>
-      <c r="J46" s="54" t="n"/>
-      <c r="K46" s="54" t="n"/>
-      <c r="L46" s="54" t="n"/>
-      <c r="M46" s="54" t="n"/>
-      <c r="N46" s="54" t="n"/>
-      <c r="O46" s="54" t="n"/>
-      <c r="P46" s="54" t="n"/>
-      <c r="Q46" s="68">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
+      <c r="A46" s="83" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="G46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="I46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
+      <c r="K46" s="83" t="n"/>
+      <c r="L46" s="83" t="n"/>
+      <c r="M46" s="83" t="n"/>
+      <c r="N46" s="83" t="n"/>
+      <c r="O46" s="83" t="n"/>
+      <c r="P46" s="83" t="n"/>
+      <c r="Q46" s="84" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="54" t="n"/>
-      <c r="B47" s="54" t="n"/>
-      <c r="C47" s="54" t="n"/>
-      <c r="D47" s="54" t="n"/>
-      <c r="E47" s="54" t="n"/>
-      <c r="F47" s="54" t="n"/>
-      <c r="G47" s="54" t="n"/>
-      <c r="H47" s="54" t="n"/>
-      <c r="I47" s="54" t="n"/>
-      <c r="J47" s="54" t="n"/>
-      <c r="K47" s="54" t="n"/>
-      <c r="L47" s="54" t="n"/>
-      <c r="M47" s="54" t="n"/>
-      <c r="N47" s="54" t="n"/>
-      <c r="O47" s="54" t="n"/>
-      <c r="P47" s="54" t="n"/>
-      <c r="Q47" s="68">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
+      <c r="A47" s="83" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="G47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="I47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
+      <c r="K47" s="83" t="n"/>
+      <c r="L47" s="83" t="n"/>
+      <c r="M47" s="83" t="n"/>
+      <c r="N47" s="83" t="n"/>
+      <c r="O47" s="83" t="n"/>
+      <c r="P47" s="83" t="n"/>
+      <c r="Q47" s="84" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="n"/>
-      <c r="B48" s="54" t="n"/>
-      <c r="C48" s="54" t="n"/>
-      <c r="D48" s="54" t="n"/>
-      <c r="E48" s="54" t="n"/>
-      <c r="F48" s="54" t="n"/>
-      <c r="G48" s="54" t="n"/>
-      <c r="H48" s="54" t="n"/>
-      <c r="I48" s="54" t="n"/>
-      <c r="J48" s="54" t="n"/>
-      <c r="K48" s="54" t="n"/>
-      <c r="L48" s="54" t="n"/>
-      <c r="M48" s="54" t="n"/>
-      <c r="N48" s="54" t="n"/>
-      <c r="O48" s="54" t="n"/>
-      <c r="P48" s="54" t="n"/>
-      <c r="Q48" s="68">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
+      <c r="A48" s="83" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="G48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="I48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
+      <c r="K48" s="83" t="n"/>
+      <c r="L48" s="83" t="n"/>
+      <c r="M48" s="83" t="n"/>
+      <c r="N48" s="83" t="n"/>
+      <c r="O48" s="83" t="n"/>
+      <c r="P48" s="83" t="n"/>
+      <c r="Q48" s="84" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="54" t="n"/>
-      <c r="B49" s="54" t="n"/>
-      <c r="C49" s="54" t="n"/>
-      <c r="D49" s="54" t="n"/>
-      <c r="E49" s="54" t="n"/>
-      <c r="F49" s="54" t="n"/>
-      <c r="G49" s="54" t="n"/>
-      <c r="H49" s="54" t="n"/>
-      <c r="I49" s="54" t="n"/>
-      <c r="J49" s="54" t="n"/>
-      <c r="K49" s="54" t="n"/>
-      <c r="L49" s="54" t="n"/>
-      <c r="M49" s="54" t="n"/>
-      <c r="N49" s="54" t="n"/>
-      <c r="O49" s="54" t="n"/>
-      <c r="P49" s="54" t="n"/>
-      <c r="Q49" s="68">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
+      <c r="A49" s="83" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="G49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="I49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
+      <c r="K49" s="83" t="n"/>
+      <c r="L49" s="83" t="n"/>
+      <c r="M49" s="83" t="n"/>
+      <c r="N49" s="83" t="n"/>
+      <c r="O49" s="83" t="n"/>
+      <c r="P49" s="83" t="n"/>
+      <c r="Q49" s="84" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="54" t="n"/>
-      <c r="B50" s="54" t="n"/>
-      <c r="C50" s="54" t="n"/>
-      <c r="D50" s="54" t="n"/>
-      <c r="E50" s="54" t="n"/>
-      <c r="F50" s="54" t="n"/>
-      <c r="G50" s="54" t="n"/>
-      <c r="H50" s="54" t="n"/>
-      <c r="I50" s="54" t="n"/>
-      <c r="J50" s="54" t="n"/>
-      <c r="K50" s="54" t="n"/>
-      <c r="L50" s="54" t="n"/>
-      <c r="M50" s="54" t="n"/>
-      <c r="N50" s="54" t="n"/>
-      <c r="O50" s="54" t="n"/>
-      <c r="P50" s="54" t="n"/>
-      <c r="Q50" s="68">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
+      <c r="A50" s="83" t="n"/>
+      <c r="B50" s="83" t="n"/>
+      <c r="C50" s="83" t="n"/>
+      <c r="D50" s="83" t="n"/>
+      <c r="E50" s="83" t="n"/>
+      <c r="F50" s="83" t="n"/>
+      <c r="G50" s="83" t="n"/>
+      <c r="H50" s="83" t="n"/>
+      <c r="I50" s="83" t="n"/>
+      <c r="J50" s="83" t="n"/>
+      <c r="K50" s="83" t="n"/>
+      <c r="L50" s="83" t="n"/>
+      <c r="M50" s="83" t="n"/>
+      <c r="N50" s="83" t="n"/>
+      <c r="O50" s="83" t="n"/>
+      <c r="P50" s="83" t="n"/>
+      <c r="Q50" s="84" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="54" t="n"/>
-      <c r="B51" s="54" t="n"/>
-      <c r="C51" s="54" t="n"/>
-      <c r="D51" s="54" t="n"/>
-      <c r="E51" s="54" t="n"/>
-      <c r="F51" s="54" t="n"/>
-      <c r="G51" s="54" t="n"/>
-      <c r="H51" s="54" t="n"/>
-      <c r="I51" s="54" t="n"/>
-      <c r="J51" s="54" t="n"/>
-      <c r="K51" s="54" t="n"/>
-      <c r="L51" s="54" t="n"/>
-      <c r="M51" s="54" t="n"/>
-      <c r="N51" s="54" t="n"/>
-      <c r="O51" s="54" t="n"/>
-      <c r="P51" s="54" t="n"/>
-      <c r="Q51" s="68">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
+      <c r="A51" s="83" t="n"/>
+      <c r="B51" s="83" t="n"/>
+      <c r="C51" s="83" t="n"/>
+      <c r="D51" s="83" t="n"/>
+      <c r="E51" s="83" t="n"/>
+      <c r="F51" s="83" t="n"/>
+      <c r="G51" s="83" t="n"/>
+      <c r="H51" s="83" t="n"/>
+      <c r="I51" s="83" t="n"/>
+      <c r="J51" s="83" t="n"/>
+      <c r="K51" s="83" t="n"/>
+      <c r="L51" s="83" t="n"/>
+      <c r="M51" s="83" t="n"/>
+      <c r="N51" s="83" t="n"/>
+      <c r="O51" s="83" t="n"/>
+      <c r="P51" s="83" t="n"/>
+      <c r="Q51" s="84" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="n"/>
-      <c r="B52" s="54" t="n"/>
-      <c r="C52" s="54" t="n"/>
-      <c r="D52" s="54" t="n"/>
-      <c r="E52" s="54" t="n"/>
-      <c r="F52" s="54" t="n"/>
-      <c r="G52" s="54" t="n"/>
-      <c r="H52" s="54" t="n"/>
-      <c r="I52" s="54" t="n"/>
-      <c r="J52" s="54" t="n"/>
-      <c r="K52" s="54" t="n"/>
-      <c r="L52" s="54" t="n"/>
-      <c r="M52" s="54" t="n"/>
-      <c r="N52" s="54" t="n"/>
-      <c r="O52" s="54" t="n"/>
-      <c r="P52" s="54" t="n"/>
-      <c r="Q52" s="68">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
+      <c r="A52" s="83" t="n"/>
+      <c r="B52" s="83" t="n"/>
+      <c r="C52" s="83" t="n"/>
+      <c r="D52" s="83" t="n"/>
+      <c r="E52" s="83" t="n"/>
+      <c r="F52" s="83" t="n"/>
+      <c r="G52" s="83" t="n"/>
+      <c r="H52" s="83" t="n"/>
+      <c r="I52" s="83" t="n"/>
+      <c r="J52" s="83" t="n"/>
+      <c r="K52" s="83" t="n"/>
+      <c r="L52" s="83" t="n"/>
+      <c r="M52" s="83" t="n"/>
+      <c r="N52" s="83" t="n"/>
+      <c r="O52" s="83" t="n"/>
+      <c r="P52" s="83" t="n"/>
+      <c r="Q52" s="84" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="n"/>
-      <c r="B53" s="54" t="n"/>
-      <c r="C53" s="54" t="n"/>
-      <c r="D53" s="54" t="n"/>
-      <c r="E53" s="54" t="n"/>
-      <c r="F53" s="54" t="n"/>
-      <c r="G53" s="54" t="n"/>
-      <c r="H53" s="54" t="n"/>
-      <c r="I53" s="54" t="n"/>
-      <c r="J53" s="54" t="n"/>
-      <c r="K53" s="54" t="n"/>
-      <c r="L53" s="54" t="n"/>
-      <c r="M53" s="54" t="n"/>
-      <c r="N53" s="54" t="n"/>
-      <c r="O53" s="54" t="n"/>
-      <c r="P53" s="54" t="n"/>
-      <c r="Q53" s="68">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
+      <c r="A53" s="83" t="n"/>
+      <c r="B53" s="83" t="n"/>
+      <c r="C53" s="83" t="n"/>
+      <c r="D53" s="83" t="n"/>
+      <c r="E53" s="83" t="n"/>
+      <c r="F53" s="83" t="n"/>
+      <c r="G53" s="83" t="n"/>
+      <c r="H53" s="83" t="n"/>
+      <c r="I53" s="83" t="n"/>
+      <c r="J53" s="83" t="n"/>
+      <c r="K53" s="83" t="n"/>
+      <c r="L53" s="83" t="n"/>
+      <c r="M53" s="83" t="n"/>
+      <c r="N53" s="83" t="n"/>
+      <c r="O53" s="83" t="n"/>
+      <c r="P53" s="83" t="n"/>
+      <c r="Q53" s="84" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="n"/>
-      <c r="B54" s="54" t="n"/>
-      <c r="C54" s="54" t="n"/>
-      <c r="D54" s="54" t="n"/>
-      <c r="E54" s="54" t="n"/>
-      <c r="F54" s="54" t="n"/>
-      <c r="G54" s="54" t="n"/>
-      <c r="H54" s="54" t="n"/>
-      <c r="I54" s="54" t="n"/>
-      <c r="J54" s="54" t="n"/>
-      <c r="K54" s="54" t="n"/>
-      <c r="L54" s="54" t="n"/>
-      <c r="M54" s="54" t="n"/>
-      <c r="N54" s="54" t="n"/>
-      <c r="O54" s="54" t="n"/>
-      <c r="P54" s="54" t="n"/>
-      <c r="Q54" s="68">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
+      <c r="A54" s="83" t="n"/>
+      <c r="B54" s="83" t="n"/>
+      <c r="C54" s="83" t="n"/>
+      <c r="D54" s="83" t="n"/>
+      <c r="E54" s="83" t="n"/>
+      <c r="F54" s="83" t="n"/>
+      <c r="G54" s="83" t="n"/>
+      <c r="H54" s="83" t="n"/>
+      <c r="I54" s="83" t="n"/>
+      <c r="J54" s="83" t="n"/>
+      <c r="K54" s="83" t="n"/>
+      <c r="L54" s="83" t="n"/>
+      <c r="M54" s="83" t="n"/>
+      <c r="N54" s="83" t="n"/>
+      <c r="O54" s="83" t="n"/>
+      <c r="P54" s="83" t="n"/>
+      <c r="Q54" s="84" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="54" t="n"/>
-      <c r="B55" s="54" t="n"/>
-      <c r="C55" s="54" t="n"/>
-      <c r="D55" s="54" t="n"/>
-      <c r="E55" s="54" t="n"/>
-      <c r="F55" s="54" t="n"/>
-      <c r="G55" s="54" t="n"/>
-      <c r="H55" s="54" t="n"/>
-      <c r="I55" s="54" t="n"/>
-      <c r="J55" s="54" t="n"/>
-      <c r="K55" s="54" t="n"/>
-      <c r="L55" s="54" t="n"/>
-      <c r="M55" s="54" t="n"/>
-      <c r="N55" s="54" t="n"/>
-      <c r="O55" s="54" t="n"/>
-      <c r="P55" s="54" t="n"/>
-      <c r="Q55" s="68">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
+      <c r="A55" s="83" t="n"/>
+      <c r="B55" s="83" t="n"/>
+      <c r="C55" s="83" t="n"/>
+      <c r="D55" s="83" t="n"/>
+      <c r="E55" s="83" t="n"/>
+      <c r="F55" s="83" t="n"/>
+      <c r="G55" s="83" t="n"/>
+      <c r="H55" s="83" t="n"/>
+      <c r="I55" s="83" t="n"/>
+      <c r="J55" s="83" t="n"/>
+      <c r="K55" s="83" t="n"/>
+      <c r="L55" s="83" t="n"/>
+      <c r="M55" s="83" t="n"/>
+      <c r="N55" s="83" t="n"/>
+      <c r="O55" s="83" t="n"/>
+      <c r="P55" s="83" t="n"/>
+      <c r="Q55" s="84" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="54" t="n"/>
-      <c r="B56" s="54" t="n"/>
-      <c r="C56" s="54" t="n"/>
-      <c r="D56" s="54" t="n"/>
-      <c r="E56" s="54" t="n"/>
-      <c r="F56" s="54" t="n"/>
-      <c r="G56" s="54" t="n"/>
-      <c r="H56" s="54" t="n"/>
-      <c r="I56" s="54" t="n"/>
-      <c r="J56" s="54" t="n"/>
-      <c r="K56" s="54" t="n"/>
-      <c r="L56" s="54" t="n"/>
-      <c r="M56" s="54" t="n"/>
-      <c r="N56" s="54" t="n"/>
-      <c r="O56" s="54" t="n"/>
-      <c r="P56" s="54" t="n"/>
-      <c r="Q56" s="68">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
+      <c r="A56" s="83" t="n"/>
+      <c r="B56" s="83" t="n"/>
+      <c r="C56" s="83" t="n"/>
+      <c r="D56" s="83" t="n"/>
+      <c r="E56" s="83" t="n"/>
+      <c r="F56" s="83" t="n"/>
+      <c r="G56" s="83" t="n"/>
+      <c r="H56" s="83" t="n"/>
+      <c r="I56" s="83" t="n"/>
+      <c r="J56" s="83" t="n"/>
+      <c r="K56" s="83" t="n"/>
+      <c r="L56" s="83" t="n"/>
+      <c r="M56" s="83" t="n"/>
+      <c r="N56" s="83" t="n"/>
+      <c r="O56" s="83" t="n"/>
+      <c r="P56" s="83" t="n"/>
+      <c r="Q56" s="84" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="54" t="n"/>
-      <c r="B57" s="54" t="n"/>
-      <c r="C57" s="54" t="n"/>
-      <c r="D57" s="54" t="n"/>
-      <c r="E57" s="54" t="n"/>
-      <c r="F57" s="54" t="n"/>
-      <c r="G57" s="54" t="n"/>
-      <c r="H57" s="54" t="n"/>
-      <c r="I57" s="54" t="n"/>
-      <c r="J57" s="54" t="n"/>
-      <c r="K57" s="54" t="n"/>
-      <c r="L57" s="54" t="n"/>
-      <c r="M57" s="54" t="n"/>
-      <c r="N57" s="54" t="n"/>
-      <c r="O57" s="54" t="n"/>
-      <c r="P57" s="54" t="n"/>
-      <c r="Q57" s="68">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
-        <v/>
-      </c>
+      <c r="A57" s="83" t="n"/>
+      <c r="B57" s="83" t="n"/>
+      <c r="C57" s="83" t="n"/>
+      <c r="D57" s="83" t="n"/>
+      <c r="E57" s="83" t="n"/>
+      <c r="F57" s="83" t="n"/>
+      <c r="G57" s="83" t="n"/>
+      <c r="H57" s="83" t="n"/>
+      <c r="I57" s="83" t="n"/>
+      <c r="J57" s="83" t="n"/>
+      <c r="K57" s="83" t="n"/>
+      <c r="L57" s="83" t="n"/>
+      <c r="M57" s="83" t="n"/>
+      <c r="N57" s="83" t="n"/>
+      <c r="O57" s="83" t="n"/>
+      <c r="P57" s="83" t="n"/>
+      <c r="Q57" s="84" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q61"/>
@@ -3096,10 +2987,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -4246,7 +4137,7 @@
     <hyperlink ref="F6" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink ref="E10" location="'تست‌های آزمایشگاهی'!A9"/>
     <hyperlink ref="E11" location="'تست‌های آزمایشگاهی'!A9"/>
-    <hyperlink ref="E12" location="'برنامه تست'!A10"/>
+    <hyperlink ref="E12" location="'برنامه تست'!A9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5108,7 +4999,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" location="'برنامه تست'!A16"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5138,10 +5029,10 @@
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Charger</t>
         </is>
       </c>
-      <c r="B1" s="73" t="n"/>
-      <c r="C1" s="73" t="n"/>
-      <c r="D1" s="73" t="n"/>
-      <c r="E1" s="74" t="n"/>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="54" t="n"/>
@@ -5381,18 +5272,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Charger</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="54" t="n"/>
-      <c r="D1" s="54" t="n"/>
-      <c r="E1" s="54" t="n"/>
-      <c r="F1" s="54" t="n"/>
-      <c r="G1" s="54" t="n"/>
-      <c r="H1" s="54" t="n"/>
-      <c r="I1" s="54" t="n"/>
-      <c r="J1" s="54" t="n"/>
-      <c r="K1" s="54" t="n"/>
-      <c r="L1" s="54" t="n"/>
-      <c r="M1" s="54" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="51" t="inlineStr">
@@ -5400,18 +5279,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="73" t="n"/>
-      <c r="C2" s="73" t="n"/>
-      <c r="D2" s="73" t="n"/>
-      <c r="E2" s="73" t="n"/>
-      <c r="F2" s="73" t="n"/>
-      <c r="G2" s="73" t="n"/>
-      <c r="H2" s="73" t="n"/>
-      <c r="I2" s="73" t="n"/>
-      <c r="J2" s="73" t="n"/>
-      <c r="K2" s="73" t="n"/>
-      <c r="L2" s="73" t="n"/>
-      <c r="M2" s="74" t="n"/>
+      <c r="B2" s="42" t="n"/>
+      <c r="C2" s="42" t="n"/>
+      <c r="D2" s="42" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="42" t="n"/>
+      <c r="G2" s="42" t="n"/>
+      <c r="H2" s="42" t="n"/>
+      <c r="I2" s="42" t="n"/>
+      <c r="J2" s="42" t="n"/>
+      <c r="K2" s="42" t="n"/>
+      <c r="L2" s="42" t="n"/>
+      <c r="M2" s="43" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="75" t="inlineStr">
@@ -5510,8 +5389,6 @@
           <t>تأیید نهایی اعتبارسنجی — ماژول Charger</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="54" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="inlineStr">
@@ -5519,8 +5396,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="54" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
@@ -5528,8 +5403,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="54" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="50" t="inlineStr">
@@ -5914,8 +5787,6 @@
           <t>ماشین حالت ماژول شارژر (Charger)</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="54" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="54" t="n"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -968,6 +968,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
@@ -1358,7 +1359,7 @@
       </c>
       <c r="C8" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="56" t="inlineStr">
@@ -1430,7 +1431,7 @@
       </c>
       <c r="C9" s="62" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D9" s="61" t="inlineStr">
@@ -1502,7 +1503,7 @@
       </c>
       <c r="C10" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D10" s="56" t="inlineStr">
@@ -1573,7 +1574,7 @@
       </c>
       <c r="C11" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D11" s="56" t="inlineStr">
@@ -1646,7 +1647,7 @@
       </c>
       <c r="C12" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D12" s="56" t="inlineStr">
@@ -1716,7 +1717,7 @@
       </c>
       <c r="C13" s="57" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -916,7 +916,9 @@
     <row r="2">
       <c r="A2" s="50" t="inlineStr">
         <is>
-          <t>Charger | دو شارژر مستقل ۱۲V؛ Ch1→باتری بالا (VHIGH)، Ch2→باتری پایین (VLOW)؛ پارامترهای زندهٔ ESP + مود تست دستی v1.2</t>
+          <t>Charger | دو شارژر جدا داریم. هر کدام برای یک باتری ۱۲ ولت است.
+کانال ۱ برای باتری بالا (VHIGH) و کانال ۲ برای باتری پایین (VLOW) است.
+تنظیم‌ها از پنل (ESP) زنده عوض می‌شوند. یک مود تست دستی هم داریم (نسخه 1.2).</t>
         </is>
       </c>
     </row>
@@ -933,21 +935,33 @@
     <row r="5">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>سناریوها حول رفتار قابل مشاهدهٔ هر کانال: state (تله‌متری ESP)، duty (اسکوپ PA0/PA6)، رلهٔ NC و پنل ESP نوشته شده‌اند.</t>
+          <t>تست‌ها دور رفتار هر کانال نوشته شده‌اند؛ چیزی که می‌شود دید:
+وضعیت کانال را در پنل (تله‌متری ESP) می‌بینی.
+پهنای پالس (duty) را با اسکوپ روی PA0 و PA6 می‌بینی.
+رله از نوع NC است (در حالت عادی وصل است) و پنل ESP هم هست.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
-          <t>ثابت‌های مرجع در charger.h: باند تنظیم 630..650mA تخمینی، خطای سخت 950mA، ابزورب 14.3/14.4/14.6V، فلوت 13.5V، reentry 12.8V، سقف duty 500‰، ددمن مود دستی 3000ms.</t>
+          <t>عددهای مرجع در فایل charger.h:
+جریان تنظیم: حدود 630 تا 650 میلی‌آمپر.
+خطای سخت: 950 میلی‌آمپر.
+ولتاژ جذب (ابزورب): 14.3 و 14.4 و 14.6 ولت.
+ولتاژ شناور (فلوت): 13.5 ولت.
+برگشت به شارژ: 12.8 ولت.
+سقف پهنای پالس (duty): 500 در هزار.
+ددتایم مود دستی: 3000 میلی‌ثانیه.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="50" t="inlineStr">
         <is>
-          <t>تست مود دستی فقط با بار مقاومتی یا electronic load با voltage clamp؛ مقاومت آزاد شبیه‌ساز باتری نیست و منبع ورودی باید محدودشده باشد.</t>
+          <t>مود دستی را فقط با بار مقاومتی یا بار الکترونیکیِ دارای محدودکنندهٔ ولتاژ تست کن.
+مقاومت آزاد شبیه باتری نیست؛ با آن تست نکن.
+جریان منبع ورودی هم باید محدود شده باشد.</t>
         </is>
       </c>
     </row>
@@ -957,23 +971,27 @@
     <row r="9">
       <c r="A9" s="50" t="inlineStr">
         <is>
-          <t>هشدار: تست مود دستی بدون باتری فقط با electronic load دارای voltage clamp؛ هرگز با مقاومت آزاد.</t>
+          <t>هشدار: مود دستی بدون باتری فقط با بار الکترونیکیِ دارای محدودکنندهٔ ولتاژ مجاز است. با مقاومت آزاد هرگز تست نکن.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="50" t="inlineStr">
         <is>
-          <t>هشدار: منبع ورودی در تست‌های اول محدودشده باشد؛ current-limit ورودی جای حفاظت خروجی firmware نیست.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>هشدار: در تست‌های اول، جریان منبع ورودی را محدود کن.
+محدودکردن جریان ورودی جای حفاظت خروجیِ برنامه را نمی‌گیرد.</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1108,7 @@
       </c>
       <c r="I4" s="51" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="51" t="inlineStr">
@@ -1115,12 +1133,12 @@
       </c>
       <c r="N4" s="51" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="51" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="51" t="inlineStr">
@@ -1185,7 +1203,10 @@
       </c>
       <c r="J5" s="56" t="inlineStr">
         <is>
-          <t>باید ببینید: با وصل ورودی، جریان شارژ در پنل (یا با مولتی‌متر) بالا می‌رود و چراغ زرد چشمک می‌زند؛ با قطع ورودی جریان صفر می‌شود. اگر شارژ شروع نشد یا با قطع ورودی ادامه داشت، قبول نیست.</t>
+          <t>باید ببینید:
+با وصل ورودی، جریان شارژ در پنل (یا با مولتی‌متر) بالا می‌رود و چراغ زرد چشمک می‌زند.
+با قطع ورودی، جریان صفر می‌شود.
+اگر شارژ شروع نشد یا با قطع ورودی ادامه داشت، قبول نیست.</t>
         </is>
       </c>
       <c r="K5" s="56" t="n"/>
@@ -1266,7 +1287,7 @@
       <c r="N6" s="56" t="n"/>
       <c r="O6" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="58" t="n"/>
@@ -1337,7 +1358,7 @@
       <c r="N7" s="61" t="n"/>
       <c r="O7" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="63" t="n"/>
@@ -1409,7 +1430,7 @@
       <c r="N8" s="56" t="n"/>
       <c r="O8" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="58" t="n"/>
@@ -1481,7 +1502,7 @@
       <c r="N9" s="61" t="n"/>
       <c r="O9" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="63" t="n"/>
@@ -1552,7 +1573,7 @@
       <c r="N10" s="56" t="n"/>
       <c r="O10" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="58" t="n"/>
@@ -1835,7 +1856,7 @@
       <c r="N14" s="56" t="n"/>
       <c r="O14" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P14" s="58" t="n"/>
@@ -1907,7 +1928,7 @@
       <c r="N15" s="61" t="n"/>
       <c r="O15" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P15" s="63" t="n"/>
@@ -1979,7 +2000,7 @@
       <c r="N16" s="56" t="n"/>
       <c r="O16" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P16" s="58" t="n"/>
@@ -2051,7 +2072,7 @@
       <c r="N17" s="56" t="n"/>
       <c r="O17" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P17" s="58" t="n"/>
@@ -2123,7 +2144,7 @@
       <c r="N18" s="61" t="n"/>
       <c r="O18" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P18" s="63" t="n"/>
@@ -2195,7 +2216,7 @@
       <c r="N19" s="61" t="n"/>
       <c r="O19" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P19" s="63" t="n"/>
@@ -3137,7 +3158,7 @@
       </c>
       <c r="I4" s="51" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="51" t="inlineStr">
@@ -3162,12 +3183,12 @@
       </c>
       <c r="N4" s="51" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="51" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="51" t="inlineStr">
@@ -3245,7 +3266,7 @@
       <c r="N5" s="56" t="n"/>
       <c r="O5" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="58" t="n"/>
@@ -3319,7 +3340,7 @@
       <c r="N6" s="61" t="n"/>
       <c r="O6" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="63" t="n"/>
@@ -3393,7 +3414,7 @@
       <c r="N7" s="56" t="n"/>
       <c r="O7" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="58" t="n"/>
@@ -3426,10 +3447,11 @@
       </c>
       <c r="E8" s="56" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را در حالت BULK فعال کن و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
-گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل، یا صبر کن تا ذخیرهٔ دوره‌ای Diag (حدود هر 60 ثانیه) خودش برسد.
-گام ۳: لحظهٔ پاک/نوشتن فلش را روی اسکوپ ببین: هر دو گیت PWM باید متوقف و خروجی صفر باشد.
-گام ۴: بلافاصله بعد از تمام شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد/تنظیم هم سالم ذخیره شده باشد. هیچ پالس PWM حین پاک‌کردن صفحه قبول نیست.</t>
+          <t>گام ۱: شارژ را در حالت BULK فعال کن و اسکوپ را روی گیت هر دو کانال بگذار.
+گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل. یا صبر کن تا ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
+گام ۳: لحظهٔ پاک‌کردن و نوشتن فلش را روی اسکوپ ببین. هر دو گیت PWM باید متوقف باشند و خروجی صفر باشد.
+گام ۴: بلافاصله بعد از تمام‌شدن ذخیره، شارژ باید بدون پرش ادامه پیدا کند.
+گام ۵: رکورد و تنظیم هم باید سالم ذخیره شده باشد. هیچ پالس PWM هنگام پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
       <c r="F8" s="58" t="inlineStr">
@@ -3545,7 +3567,7 @@
       <c r="N9" s="61" t="n"/>
       <c r="O9" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="63" t="n"/>
@@ -3618,7 +3640,7 @@
       <c r="N10" s="56" t="n"/>
       <c r="O10" s="58" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="58" t="n"/>
@@ -3691,7 +3713,7 @@
       <c r="N11" s="61" t="n"/>
       <c r="O11" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="63" t="n"/>
@@ -3764,7 +3786,7 @@
       <c r="N12" s="61" t="n"/>
       <c r="O12" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="63" t="n"/>
@@ -4282,7 +4304,7 @@
       </c>
       <c r="I4" s="51" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="51" t="inlineStr">
@@ -4307,12 +4329,12 @@
       </c>
       <c r="N4" s="51" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="51" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="51" t="inlineStr">
@@ -4350,9 +4372,10 @@
       <c r="E5" s="66" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
-گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن: PA0 = TIM2_CH1، PA6 = TIM3_CH1، PA1/PA7 = سنس جریان، PB2/PB6 = JIT، رله از نوع NC.
-گام ۳: بررسی کن رله وقتی سیم‌پیچش خاموش است وصل باشد (NC).
-گام ۴: هر اختلاف بین شماتیک و کد را یادداشت کن؛ قبولی فقط با تطابق کامل است.</t>
+گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن:
+PA0 با TIM2_CH1 است. PA6 با TIM3_CH1 است. PA1 و PA7 برای حس جریان‌اند. PB2 و PB6 برای JIT هستند.
+گام ۳: رله از نوع NC است؛ یعنی وقتی سیم‌پیچش خاموش است، وصل است. همین را هم بررسی کن.
+گام ۴: هر اختلافی بین شماتیک و کد دیدی، یادداشت کن. قبولی فقط با تطابق کامل است.</t>
         </is>
       </c>
       <c r="F5" s="63" t="inlineStr">
@@ -4390,7 +4413,7 @@
       <c r="N5" s="61" t="n"/>
       <c r="O5" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="63" t="n"/>
@@ -4497,10 +4520,11 @@
       </c>
       <c r="E7" s="66" t="inlineStr">
         <is>
-          <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل CH-036) تا در THERMAL_REST باشد.
-گام ۲: حین استراحت، snapshot نامعتبر (valid=false) بده.
-گام ۳: 2 ثانیه وضعیت را نگاه کن: باید THERMAL_REST حفظ شود، نه اینکه به OFF برود.
-گام ۴: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد و بعد از معتبر شدن snapshot، استراحت سر جایش ادامه پیدا کند.</t>
+          <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل تست CH-036) تا در THERMAL_REST باشد.
+گام ۲: هنگام استراحت، دادهٔ نامعتبر بده (valid=false).
+گام ۳: 2 ثانیه وضعیت را نگاه کن. باید THERMAL_REST بماند، نه اینکه به OFF برود.
+گام ۴: بعد از معتبرشدن داده، استراحت باید سر جایش ادامه پیدا کند.
+گام ۵: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد.</t>
         </is>
       </c>
       <c r="F7" s="63" t="inlineStr">
@@ -5341,7 +5365,7 @@
       </c>
       <c r="J3" s="75" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="75" t="inlineStr">
@@ -5460,12 +5484,12 @@
     <row r="8">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="54" t="n"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -193,7 +193,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -238,6 +238,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -326,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -534,6 +544,35 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -907,7 +946,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Charger</t>
         </is>
@@ -923,7 +962,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -983,6 +1022,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
@@ -1045,7 +1085,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Charger</t>
         </is>
@@ -1066,87 +1106,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="51" t="inlineStr">
+      <c r="D4" s="86" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" s="86" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr">
+      <c r="F4" s="86" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="G4" s="86" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="51" t="inlineStr">
+      <c r="H4" s="86" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="51" t="inlineStr">
+      <c r="I4" s="86" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="86" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="51" t="inlineStr">
+      <c r="K4" s="86" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="51" t="inlineStr">
+      <c r="L4" s="86" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="51" t="inlineStr">
+      <c r="M4" s="86" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="51" t="inlineStr">
+      <c r="N4" s="86" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="51" t="inlineStr">
+      <c r="O4" s="86" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="51" t="inlineStr">
+      <c r="P4" s="86" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="51" t="inlineStr">
+      <c r="Q4" s="86" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1230,49 +1270,49 @@
           <t>CH-004</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>تنظیم BULK</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="87" t="inlineStr">
         <is>
           <t>یک باتری نیمه‌خالی واقعی وصل است و برق شهر برقرار؛ آمپرمتر دستی یا پنل برای دیدن جریان آماده است</t>
         </is>
       </c>
-      <c r="E6" s="56" t="inlineStr">
+      <c r="E6" s="87" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را شروع کن و بگذار یک دقیقه جا بیفتد.
 گام ۲: جریان شارژ را از پنل یا آمپرمتر دستی بخوان.
 گام ۳: یک دقیقه دیگر نگاه کن که جریان ثابت مانده یا نه.</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="89" t="inlineStr">
         <is>
           <t>باتری نیمه‌خالی در حال شارژ</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="89" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="56" t="inlineStr">
+      <c r="H6" s="87" t="inlineStr">
         <is>
           <t>جریان شارژ نزدیک سقف تنظیم‌شده (حدود ۰٫۶۴ آمپر) می‌ایستد و پایدار می‌ماند؛ بالا و پایین نمی‌پرد</t>
         </is>
       </c>
-      <c r="I6" s="56" t="inlineStr">
+      <c r="I6" s="87" t="inlineStr">
         <is>
           <t>پایدار تا وقتی باتری پرتر شود</t>
         </is>
       </c>
-      <c r="J6" s="56" t="inlineStr">
+      <c r="J6" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: جریان شارژ (در پنل یا با مولتی‌متر) نزدیک سقف تنظیم‌شده می‌ایستد و پایدار می‌ماند و بالا و پایین نمی‌پرد. اگر نوسان شدید داشت یا خیلی کمتر یا بیشتر بود، قبول نیست.</t>
         </is>
@@ -1285,13 +1325,13 @@
       </c>
       <c r="M6" s="56" t="n"/>
       <c r="N6" s="56" t="n"/>
-      <c r="O6" s="58" t="inlineStr">
+      <c r="O6" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="58" t="n"/>
-      <c r="Q6" s="60">
+      <c r="Q6" s="90">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -1302,48 +1342,48 @@
           <t>CH-005</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>باتری تقریباً پر است و شارژ ادامه دارد</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="56" t="inlineStr">
         <is>
           <t>گام ۱: باتری نزدیک‌به‌پر را به شارژ نگه دار.
 گام ۲: ولتاژ باتری را با مولتی‌متر و جریان شارژ را با پنل زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>باتری تقریباً پر در شارژ</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="61" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود (شارژ ملایم پایانی)</t>
         </is>
       </c>
-      <c r="I7" s="61" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>تا رسیدن به حالت نگهداری</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="56" t="inlineStr">
         <is>
           <t>باید ببینید: ولتاژ باتری تقریباً ثابت می‌ماند و جریان شارژ آرام‌آرام کم می‌شود. اگر ولتاژ از حد شارژ بالا رفت، قبول نیست.</t>
         </is>
@@ -1356,13 +1396,13 @@
       </c>
       <c r="M7" s="61" t="n"/>
       <c r="N7" s="61" t="n"/>
-      <c r="O7" s="63" t="inlineStr">
+      <c r="O7" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="63" t="n"/>
-      <c r="Q7" s="64">
+      <c r="Q7" s="60">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -1373,49 +1413,49 @@
           <t>CH-012</t>
         </is>
       </c>
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>اعتبار sense باتری</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="87" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ یک باتری واقعی است</t>
         </is>
       </c>
-      <c r="E8" s="56" t="inlineStr">
+      <c r="E8" s="87" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ، سیم حس‌کردن ولتاژ باتری را جدا کن.
 گام ۲: به شارژر نگاه کن؛ نباید کورکورانه به شارژ ادامه دهد.
 گام ۳: سیم را وصل کن و برگشت شارژ را ببین.</t>
         </is>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="F8" s="89" t="inlineStr">
         <is>
           <t>قطع و وصل سیم حس ولتاژ باتری</t>
         </is>
       </c>
-      <c r="G8" s="58" t="inlineStr">
+      <c r="G8" s="89" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="56" t="inlineStr">
+      <c r="H8" s="87" t="inlineStr">
         <is>
           <t>با قطع سیم حس، شارژ متوقف می‌ماند؛ با وصل آن، شارژ عادی برمی‌گردد</t>
         </is>
       </c>
-      <c r="I8" s="56" t="inlineStr">
+      <c r="I8" s="87" t="inlineStr">
         <is>
           <t>توقف تا برگشت حس</t>
         </is>
       </c>
-      <c r="J8" s="56" t="inlineStr">
+      <c r="J8" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: با قطع سیم حس، شارژ متوقف می‌ماند و با وصل آن شارژ عادی برمی‌گردد. اگر بی‌حس هم شارژ ادامه داشت، قبول نیست.</t>
         </is>
@@ -1428,13 +1468,13 @@
       </c>
       <c r="M8" s="56" t="n"/>
       <c r="N8" s="56" t="n"/>
-      <c r="O8" s="58" t="inlineStr">
+      <c r="O8" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="58" t="n"/>
-      <c r="Q8" s="60">
+      <c r="Q8" s="90">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -1445,49 +1485,49 @@
           <t>CH-013</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>مود دستی: ورود</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>پنل وصل است و دستگاه روشن</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr">
         <is>
           <t>گام ۱: از پنل مود تست دستی شارژر را روشن کن.
 گام ۲: نگاه کن شارژ خودکار کنار می‌رود و شارژر فقط به فرمان دستی گوش می‌دهد.
 گام ۳: یک فرمان دستی کوچک بده و اجراش را ببین.</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>روشن‌کردن مود دستی از پنل</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="61" t="inlineStr">
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>شارژر وارد مود دستی می‌شود و فقط فرمان دستی را اجرا می‌کند</t>
         </is>
       </c>
-      <c r="I9" s="61" t="inlineStr">
+      <c r="I9" s="56" t="inlineStr">
         <is>
           <t>تا خروج از مود</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="56" t="inlineStr">
         <is>
           <t>باید ببینید: شارژر وارد مود دستی می‌شود و فقط فرمان دستی پنل را اجرا می‌کند. اگر شارژ خودکار ادامه داشت، قبول نیست.</t>
         </is>
@@ -1500,13 +1540,13 @@
       </c>
       <c r="M9" s="61" t="n"/>
       <c r="N9" s="61" t="n"/>
-      <c r="O9" s="63" t="inlineStr">
+      <c r="O9" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="63" t="n"/>
-      <c r="Q9" s="64">
+      <c r="Q9" s="60">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -1517,48 +1557,48 @@
           <t>CH-018</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="87" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C10" s="57" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="87" t="inlineStr">
         <is>
           <t>شارژر در مود تست دستی است</t>
         </is>
       </c>
-      <c r="E10" s="56" t="inlineStr">
+      <c r="E10" s="87" t="inlineStr">
         <is>
           <t>گام ۱: از پنل از مود دستی خارج شو.
 گام ۲: یک باتری نیمه‌خالی را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F10" s="58" t="inlineStr">
+      <c r="F10" s="89" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="G10" s="58" t="inlineStr">
+      <c r="G10" s="89" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="56" t="inlineStr">
+      <c r="H10" s="87" t="inlineStr">
         <is>
           <t>شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود</t>
         </is>
       </c>
-      <c r="I10" s="56" t="inlineStr">
+      <c r="I10" s="87" t="inlineStr">
         <is>
           <t>برگشت به خودکار</t>
         </is>
       </c>
-      <c r="J10" s="56" t="inlineStr">
+      <c r="J10" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: شارژ خودکار عادی از سر گرفته می‌شود و باتری مثل همیشه شارژ می‌شود. اگر در مود دستی ماند، قبول نیست.</t>
         </is>
@@ -1571,13 +1611,13 @@
       </c>
       <c r="M10" s="56" t="n"/>
       <c r="N10" s="56" t="n"/>
-      <c r="O10" s="58" t="inlineStr">
+      <c r="O10" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="58" t="n"/>
-      <c r="Q10" s="60">
+      <c r="Q10" s="90">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -1661,22 +1701,22 @@
           <t>CH-040</t>
         </is>
       </c>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>سناریوی ۶: باتری خراب دیگر شارژ نمی‌شود</t>
         </is>
       </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="56" t="inlineStr">
+      <c r="D12" s="87" t="inlineStr">
         <is>
           <t>از پنل زمان سناریوی باتری خراب (شناسهٔ ۱۲۵) را موقتاً روی چند دقیقه بگذار؛ یک باتری خالی وصل است</t>
         </is>
       </c>
-      <c r="E12" s="56" t="inlineStr">
+      <c r="E12" s="87" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت به شارژ کامل برسد.
 گام ۲: بعد از گذشت زمان تنظیم‌شده، ببین شارژ همان کانال متوقف شده و قرمز ثابت آمده.
@@ -1685,27 +1725,27 @@
 گام ۵: شناسهٔ ۱۲۵ را به مقدار واقعی (یک شبانه‌روز) برگردان.</t>
         </is>
       </c>
-      <c r="F12" s="58" t="inlineStr">
+      <c r="F12" s="89" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده</t>
         </is>
       </c>
-      <c r="G12" s="58" t="inlineStr">
+      <c r="G12" s="89" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H12" s="56" t="inlineStr">
+      <c r="H12" s="87" t="inlineStr">
         <is>
           <t>بعد از زمان، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود</t>
         </is>
       </c>
-      <c r="I12" s="56" t="inlineStr">
+      <c r="I12" s="87" t="inlineStr">
         <is>
           <t>قفل تا تعویض باتری</t>
         </is>
       </c>
-      <c r="J12" s="56" t="inlineStr">
+      <c r="J12" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از زمان تنظیم‌شده، آن باتری دیگر شارژ نمی‌شود تا وقتی واقعاً عوض شود؛ با باتری سالم شارژ عادی شروع می‌شود. اگر همان باتری دوباره شارژ شد، قبول نیست.</t>
         </is>
@@ -1720,7 +1760,7 @@
       <c r="N12" s="56" t="n"/>
       <c r="O12" s="58" t="n"/>
       <c r="P12" s="58" t="n"/>
-      <c r="Q12" s="60">
+      <c r="Q12" s="90">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -1800,48 +1840,48 @@
           <t>CH-006</t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="87" t="inlineStr">
         <is>
           <t>شستشوی ABSORB</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="89" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
+      <c r="D14" s="87" t="inlineStr">
         <is>
           <t>باتری در شارژ پایانی (جذب) است</t>
         </is>
       </c>
-      <c r="E14" s="56" t="inlineStr">
+      <c r="E14" s="87" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ پایانی، یک مصرف کوتاه و واقعی از باتری بکش (مثلاً یک لامپ را چند ثانیه روشن کن) و بردار.
 گام ۲: رفتار شارژر را نگاه کن.</t>
         </is>
       </c>
-      <c r="F14" s="58" t="inlineStr">
+      <c r="F14" s="89" t="inlineStr">
         <is>
           <t>مصرف کوتاه حین شارژ پایانی</t>
         </is>
       </c>
-      <c r="G14" s="58" t="inlineStr">
+      <c r="G14" s="89" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="56" t="inlineStr">
+      <c r="H14" s="87" t="inlineStr">
         <is>
           <t>شارژر به شارژ تند برنمی‌گردد؛ همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود</t>
         </is>
       </c>
-      <c r="I14" s="56" t="inlineStr">
+      <c r="I14" s="87" t="inlineStr">
         <is>
           <t>بدون برگشت به شارژ تند</t>
         </is>
       </c>
-      <c r="J14" s="56" t="inlineStr">
+      <c r="J14" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: شارژر به شارژ تند برنمی‌گردد و همان شارژ پایانی آرام را ادامه می‌دهد تا باتری کامل شود. اگر به جریان کامل برگشت، قبول نیست.</t>
         </is>
@@ -1854,13 +1894,13 @@
       </c>
       <c r="M14" s="56" t="n"/>
       <c r="N14" s="56" t="n"/>
-      <c r="O14" s="58" t="inlineStr">
+      <c r="O14" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P14" s="58" t="n"/>
-      <c r="Q14" s="60">
+      <c r="Q14" s="90">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -1871,49 +1911,49 @@
           <t>CH-007</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>FLOAT و reentry</t>
         </is>
       </c>
-      <c r="C15" s="63" t="inlineStr">
+      <c r="C15" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr">
+      <c r="D15" s="56" t="inlineStr">
         <is>
           <t>باتری کاملاً پر شده و شارژ به حالت نگهداری رسیده (جریان خیلی کم)</t>
         </is>
       </c>
-      <c r="E15" s="61" t="inlineStr">
+      <c r="E15" s="56" t="inlineStr">
         <is>
           <t>گام ۱: بگذار باتری کامل پر و شارژ آرام شود.
 گام ۲: یک بار واقعی روی خروجی بکش تا باتری کمی خالی شود.
 گام ۳: نگاه کن شارژ دوباره کی و چطور شروع می‌شود.</t>
         </is>
       </c>
-      <c r="F15" s="63" t="inlineStr">
+      <c r="F15" s="58" t="inlineStr">
         <is>
           <t>باتری پر، بعد کمی مصرف واقعی</t>
         </is>
       </c>
-      <c r="G15" s="63" t="inlineStr">
+      <c r="G15" s="58" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="61" t="inlineStr">
+      <c r="H15" s="56" t="inlineStr">
         <is>
           <t>در حالت پر، جریان نگهداری خیلی کم است؛ با کمی خالی‌شدن، شارژ خودش دوباره شروع می‌شود</t>
         </is>
       </c>
-      <c r="I15" s="61" t="inlineStr">
+      <c r="I15" s="56" t="inlineStr">
         <is>
           <t>رفت‌وبرگشت خودکار پر/شارژ</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="56" t="inlineStr">
         <is>
           <t>باید ببینید: در حالت پر جریان نگهداری خیلی کم است و با کمی خالی‌شدن باتری، شارژ خودش دوباره شروع می‌شود. اگر دوباره شارژ نشد یا بی‌وقفه شارژ کرد، قبول نیست.</t>
         </is>
@@ -1926,13 +1966,13 @@
       </c>
       <c r="M15" s="61" t="n"/>
       <c r="N15" s="61" t="n"/>
-      <c r="O15" s="63" t="inlineStr">
+      <c r="O15" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P15" s="63" t="n"/>
-      <c r="Q15" s="64">
+      <c r="Q15" s="60">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
@@ -1943,49 +1983,49 @@
           <t>CH-014</t>
         </is>
       </c>
-      <c r="B16" s="56" t="inlineStr">
+      <c r="B16" s="87" t="inlineStr">
         <is>
           <t>مود دستی: ددمن لینک</t>
         </is>
       </c>
-      <c r="C16" s="57" t="inlineStr">
+      <c r="C16" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D16" s="56" t="inlineStr">
+      <c r="D16" s="87" t="inlineStr">
         <is>
           <t>شارژر در مود تست دستی و در حال اجرای فرمان دستی است</t>
         </is>
       </c>
-      <c r="E16" s="65" t="inlineStr">
+      <c r="E16" s="91" t="inlineStr">
         <is>
           <t>گام ۱: کابل ارتباطی پنل (ESP) را بکش تا فرمان تازه‌ای نرسد.
 گام ۲: کرنومتر بگیر و شارژر را نگاه کن.
 گام ۳: کابل را وصل کن.</t>
         </is>
       </c>
-      <c r="F16" s="58" t="inlineStr">
+      <c r="F16" s="89" t="inlineStr">
         <is>
           <t>قطع ارتباط پنل حین مود دستی</t>
         </is>
       </c>
-      <c r="G16" s="58" t="inlineStr">
+      <c r="G16" s="89" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="56" t="inlineStr">
+      <c r="H16" s="87" t="inlineStr">
         <is>
           <t>بعد از چند ثانیه بی‌ارتباطی، شارژ دستی خودش متوقف می‌شود؛ نباید بی‌صاحب ادامه دهد</t>
         </is>
       </c>
-      <c r="I16" s="56" t="inlineStr">
+      <c r="I16" s="87" t="inlineStr">
         <is>
           <t>توقف خودکار با قطع ارتباط</t>
         </is>
       </c>
-      <c r="J16" s="56" t="inlineStr">
+      <c r="J16" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از چند ثانیه قطع ارتباط، شارژ دستی خودش متوقف می‌شود و بی‌صاحب ادامه نمی‌دهد. اگر بی‌ارتباط هم ادامه داد، قبول نیست.</t>
         </is>
@@ -1998,13 +2038,13 @@
       </c>
       <c r="M16" s="56" t="n"/>
       <c r="N16" s="56" t="n"/>
-      <c r="O16" s="58" t="inlineStr">
+      <c r="O16" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P16" s="58" t="n"/>
-      <c r="Q16" s="60">
+      <c r="Q16" s="90">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -2087,49 +2127,49 @@
           <t>CH-017</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="87" t="inlineStr">
         <is>
           <t>مود دستی: قطع کانال</t>
         </is>
       </c>
-      <c r="C18" s="63" t="inlineStr">
+      <c r="C18" s="89" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="87" t="inlineStr">
         <is>
           <t>هر دو کانال شارژر در مود دستی در حال کارند (دو باتری وصل)</t>
         </is>
       </c>
-      <c r="E18" s="66" t="inlineStr">
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>گام ۱: از پنل فقط یک کانال را خاموش کن.
 گام ۲: هر دو کانال را نگاه کن.
 گام ۳: کانال خاموش را دوباره روشن کن.</t>
         </is>
       </c>
-      <c r="F18" s="63" t="inlineStr">
+      <c r="F18" s="89" t="inlineStr">
         <is>
           <t>خاموش/روشن کردن یک کانال از پنل</t>
         </is>
       </c>
-      <c r="G18" s="63" t="inlineStr">
+      <c r="G18" s="89" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="61" t="inlineStr">
+      <c r="H18" s="87" t="inlineStr">
         <is>
           <t>فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد</t>
         </is>
       </c>
-      <c r="I18" s="61" t="inlineStr">
+      <c r="I18" s="87" t="inlineStr">
         <is>
           <t>استقلال دو کانال</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: فقط همان کانال می‌ایستد و کانال دیگر بی‌تغییر ادامه می‌دهد. اگر روی کانال دیگر اثر گذاشت، قبول نیست.</t>
         </is>
@@ -2142,13 +2182,13 @@
       </c>
       <c r="M18" s="61" t="n"/>
       <c r="N18" s="61" t="n"/>
-      <c r="O18" s="63" t="inlineStr">
+      <c r="O18" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P18" s="63" t="n"/>
-      <c r="Q18" s="64">
+      <c r="Q18" s="90">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -2159,49 +2199,49 @@
           <t>CH-019</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>سقف duty زنده</t>
         </is>
       </c>
-      <c r="C19" s="63" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="56" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ یک باتری نیمه‌خالی است</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E19" s="56" t="inlineStr">
         <is>
           <t>گام ۱: از پنل سقف توان شارژ را کمتر کن.
 گام ۲: جریان شارژ را در پنل یا آمپرمتر ببین.
 گام ۳: سقف را به حالت اول برگردان.</t>
         </is>
       </c>
-      <c r="F19" s="63" t="inlineStr">
+      <c r="F19" s="58" t="inlineStr">
         <is>
           <t>کم و زیاد کردن سقف توان از پنل</t>
         </is>
       </c>
-      <c r="G19" s="63" t="inlineStr">
+      <c r="G19" s="58" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="61" t="inlineStr">
+      <c r="H19" s="56" t="inlineStr">
         <is>
           <t>جریان شارژ به همان نسبت کم و زیاد می‌شود، بدون اینکه دستگاه خاموش یا خطادار شود</t>
         </is>
       </c>
-      <c r="I19" s="61" t="inlineStr">
+      <c r="I19" s="56" t="inlineStr">
         <is>
           <t>بدون قفل</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="56" t="inlineStr">
         <is>
           <t>باید ببینید: جریان شارژ به همان نسبت سقف کم و زیاد می‌شود و دستگاه خاموش یا خطادار نمی‌شود. اگر سقف بی‌اثر بود، قبول نیست.</t>
         </is>
@@ -2214,13 +2254,13 @@
       </c>
       <c r="M19" s="61" t="n"/>
       <c r="N19" s="61" t="n"/>
-      <c r="O19" s="63" t="inlineStr">
+      <c r="O19" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P19" s="63" t="n"/>
-      <c r="Q19" s="64">
+      <c r="Q19" s="60">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
@@ -2231,22 +2271,22 @@
           <t>CH-036</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="87" t="inlineStr">
         <is>
           <t>استراحت حرارتی 1h-&gt;10min</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="87" t="inlineStr">
         <is>
           <t>دو باتری خالی واقعی وصل و هر دو کانال آمادهٔ شارژ سنگین‌اند</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="87" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را با باتری خالی به شارژ بزن.
 گام ۲: حدود یک ساعت شارژ سنگین را زیر نظر بگیر (هر از چندی سر بزن).
@@ -2254,27 +2294,27 @@
 گام ۴: بعد از استراحت، شارژ باید خودش ادامه پیدا کند.</t>
         </is>
       </c>
-      <c r="F20" s="63" t="inlineStr">
+      <c r="F20" s="89" t="inlineStr">
         <is>
           <t>یک ساعت شارژ سنگین هر دو کانال</t>
         </is>
       </c>
-      <c r="G20" s="63" t="inlineStr">
+      <c r="G20" s="89" t="inlineStr">
         <is>
           <t>حدود یک ساعت و نیم</t>
         </is>
       </c>
-      <c r="H20" s="61" t="inlineStr">
+      <c r="H20" s="87" t="inlineStr">
         <is>
           <t>بعد از یک ساعت شارژ سنگین، هر کانال ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد</t>
         </is>
       </c>
-      <c r="I20" s="61" t="inlineStr">
+      <c r="I20" s="87" t="inlineStr">
         <is>
           <t>استراحت و ادامهٔ خودکار</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J20" s="87" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از حدود یک ساعت شارژ سنگین، کانال حدود ده دقیقه استراحت می‌کند و بعد خودش به شارژ برمی‌گردد. اگر بی‌وقفه چند ساعت شارژ کرد یا برای همیشه ایستاد، قبول نیست.</t>
         </is>
@@ -2287,13 +2327,13 @@
       </c>
       <c r="M20" s="61" t="n"/>
       <c r="N20" s="61" t="n"/>
-      <c r="O20" s="63" t="inlineStr">
+      <c r="O20" s="89" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
       <c r="P20" s="63" t="n"/>
-      <c r="Q20" s="64">
+      <c r="Q20" s="90">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
@@ -3051,7 +3091,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="92" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -3116,87 +3156,87 @@
       <c r="Q3" s="54" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="51" t="inlineStr">
+      <c r="D4" s="86" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" s="86" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr">
+      <c r="F4" s="86" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="G4" s="86" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="51" t="inlineStr">
+      <c r="H4" s="86" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="51" t="inlineStr">
+      <c r="I4" s="86" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="86" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="51" t="inlineStr">
+      <c r="K4" s="86" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="51" t="inlineStr">
+      <c r="L4" s="86" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="51" t="inlineStr">
+      <c r="M4" s="86" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="51" t="inlineStr">
+      <c r="N4" s="86" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="51" t="inlineStr">
+      <c r="O4" s="86" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="51" t="inlineStr">
+      <c r="P4" s="86" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="51" t="inlineStr">
+      <c r="Q4" s="86" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3282,22 +3322,22 @@
           <t>CH-003</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>شروع BULK با رمپ</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="66" t="inlineStr">
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>CH-002 پاس</t>
         </is>
       </c>
-      <c r="E6" s="66" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>گام ۱: اول تست CH-002 را انجام بده و همان اتصال‌ها را نگه دار.
 گام ۲: اسیلوسکوپ را روی گیت یک کانال بگذار.
@@ -3305,27 +3345,27 @@
 گام ۴: duty باید با رمپ نرم از 1 درصد (10 پرمیل) شروع شود و پله‌پله بالا برود، نه اینکه یک‌باره بپرد.</t>
         </is>
       </c>
-      <c r="F6" s="71" t="inlineStr">
+      <c r="F6" s="93" t="inlineStr">
         <is>
           <t>همان CH-002</t>
         </is>
       </c>
-      <c r="G6" s="63" t="inlineStr">
+      <c r="G6" s="89" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="H6" s="61" t="inlineStr">
+      <c r="H6" s="87" t="inlineStr">
         <is>
           <t>ورود BULK با رمپ نرم از ۱٪ (10‰)</t>
         </is>
       </c>
-      <c r="I6" s="61" t="inlineStr">
+      <c r="I6" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="87" t="inlineStr">
         <is>
           <t>پله‌های duty از 10‰ صعودی</t>
         </is>
@@ -3338,13 +3378,13 @@
       </c>
       <c r="M6" s="61" t="n"/>
       <c r="N6" s="61" t="n"/>
-      <c r="O6" s="63" t="inlineStr">
+      <c r="O6" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="63" t="n"/>
-      <c r="Q6" s="64" t="inlineStr">
+      <c r="Q6" s="90" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3430,22 +3470,22 @@
           <t>CH-039</t>
         </is>
       </c>
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>تعلیق شارژر هنگام ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="87" t="inlineStr">
         <is>
           <t>شارژ فعال (BULK)</t>
         </is>
       </c>
-      <c r="E8" s="56" t="inlineStr">
+      <c r="E8" s="87" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK فعال کن و اسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: یکی از این ذخیره‌های فلش را اتفاق بینداز: ذخیرهٔ NVM یا CalLut از پنل. یا صبر کن تا ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
@@ -3454,32 +3494,32 @@
 گام ۵: رکورد و تنظیم هم باید سالم ذخیره شده باشد. هیچ پالس PWM هنگام پاک‌کردن صفحه قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="F8" s="89" t="inlineStr">
         <is>
           <t>شارژ فعال + ذخیرهٔ فلش</t>
         </is>
       </c>
-      <c r="G8" s="58" t="inlineStr">
+      <c r="G8" s="89" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H8" s="56" t="inlineStr">
+      <c r="H8" s="87" t="inlineStr">
         <is>
           <t>دور پاک/نوشتن فلش هر دو گیت PWM متوقف و خروجی صفر شود؛ بلافاصله بعد از ذخیره شارژ بدون پرش ادامه یابد</t>
         </is>
       </c>
-      <c r="I8" s="56" t="inlineStr">
+      <c r="I8" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="56" t="inlineStr">
+      <c r="J8" s="87" t="inlineStr">
         <is>
           <t>هیچ پالس PWM حین پاک‌کردن صفحه دیده نشود و رکورد/تنظیم سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="K8" s="56" t="inlineStr">
+      <c r="K8" s="87" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز (مسیر Diag با 2da0ed1 اضافه شد، NVM/CalLut از قبل بود)؛ تست برد: در انتظار</t>
         </is>
@@ -3491,13 +3531,13 @@
       </c>
       <c r="M8" s="56" t="n"/>
       <c r="N8" s="56" t="n"/>
-      <c r="O8" s="58" t="inlineStr">
+      <c r="O8" s="89" t="inlineStr">
         <is>
           <t>2da0ed1</t>
         </is>
       </c>
       <c r="P8" s="58" t="n"/>
-      <c r="Q8" s="60" t="inlineStr">
+      <c r="Q8" s="90" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
@@ -3509,22 +3549,22 @@
           <t>CH-009</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>تریپ JIT اول</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد و اسکوپ روی گیت کانال باشد.
 گام ۲: ورودی JIT همان کانال (PB2 یا PB6) را یک لبهٔ falling بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) تریپ شود.
@@ -3532,27 +3572,27 @@
 گام ۴: بعد از 3000 میلی‌ثانیه lockout، ریتری باید با نصف duty قبلی شروع شود و وضعیت 5 (state=5) دیده شود.</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>JIT falling (PB2/PB6)</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H9" s="61" t="inlineStr">
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>PWM همان کانال صفر؛ بعد از lockout 3000ms ریتری با نصف duty</t>
         </is>
       </c>
-      <c r="I9" s="61" t="inlineStr">
+      <c r="I9" s="56" t="inlineStr">
         <is>
           <t>retry خودکار</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="56" t="inlineStr">
         <is>
           <t>state=5 → ریتری 50٪ duty قبل</t>
         </is>
@@ -3565,13 +3605,13 @@
       </c>
       <c r="M9" s="61" t="n"/>
       <c r="N9" s="61" t="n"/>
-      <c r="O9" s="63" t="inlineStr">
+      <c r="O9" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="63" t="n"/>
-      <c r="Q9" s="64">
+      <c r="Q9" s="60">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -3582,22 +3622,22 @@
           <t>CH-010</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="87" t="inlineStr">
         <is>
           <t>ریتری دوم</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="89" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="D10" s="87" t="inlineStr">
         <is>
           <t>تریپ دوم همان کانال</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="91" t="inlineStr">
         <is>
           <t>گام ۱: تست CH-009 را انجام بده تا یک تریپ ثبت شده باشد و کانال در ریتری باشد.
 گام ۲: در همان ریتری، JIT را دوباره تریپ کن.
@@ -3605,27 +3645,27 @@
 گام ۴: ریتری دوم نباید بیشتر از 10 درصد (100 پرمیل) duty داشته باشد.</t>
         </is>
       </c>
-      <c r="F10" s="58" t="inlineStr">
+      <c r="F10" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="58" t="inlineStr">
+      <c r="G10" s="89" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H10" s="56" t="inlineStr">
+      <c r="H10" s="87" t="inlineStr">
         <is>
           <t>ریتری دوم حداکثر 10٪ (100‰)</t>
         </is>
       </c>
-      <c r="I10" s="56" t="inlineStr">
+      <c r="I10" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="56" t="inlineStr">
+      <c r="J10" s="87" t="inlineStr">
         <is>
           <t>duty≤100‰</t>
         </is>
@@ -3638,13 +3678,13 @@
       </c>
       <c r="M10" s="56" t="n"/>
       <c r="N10" s="56" t="n"/>
-      <c r="O10" s="58" t="inlineStr">
+      <c r="O10" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="58" t="n"/>
-      <c r="Q10" s="60">
+      <c r="Q10" s="90">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -3655,22 +3695,22 @@
           <t>CH-011</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>تریپ سوم FINAL</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>دو تریپ ثبت‌شده</t>
         </is>
       </c>
-      <c r="E11" s="66" t="inlineStr">
+      <c r="E11" s="65" t="inlineStr">
         <is>
           <t>گام ۱: دو تریپ قبلی همان کانال (CH-009 و CH-010) ثبت شده باشد.
 گام ۲: JIT را برای بار سوم تریپ کن.
@@ -3678,27 +3718,27 @@
 گام ۴: صبر کن و دست نزن؛ بدون ریبوت نباید برگردد. فقط ریبوت برد آن را پاک می‌کند.</t>
         </is>
       </c>
-      <c r="F11" s="63" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="63" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="61" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr">
         <is>
           <t>FINAL_FAULT: هر دو PWM صفر + رله باز؛ فقط ریبوت پاک می‌کند</t>
         </is>
       </c>
-      <c r="I11" s="61" t="inlineStr">
+      <c r="I11" s="56" t="inlineStr">
         <is>
           <t>latch دائمی تا ریبوت</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="56" t="inlineStr">
         <is>
           <t>state=7؛ رله باز؛ بدون ریبوت برنمی‌گردد</t>
         </is>
@@ -3711,13 +3751,13 @@
       </c>
       <c r="M11" s="61" t="n"/>
       <c r="N11" s="61" t="n"/>
-      <c r="O11" s="63" t="inlineStr">
+      <c r="O11" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="63" t="n"/>
-      <c r="Q11" s="64">
+      <c r="Q11" s="60">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
@@ -3728,22 +3768,22 @@
           <t>CH-015</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>مود دستی: JIT و re-arm</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D12" s="87" t="inlineStr">
         <is>
           <t>در مود دستی</t>
         </is>
       </c>
-      <c r="E12" s="66" t="inlineStr">
+      <c r="E12" s="91" t="inlineStr">
         <is>
           <t>گام ۱: در مود دستی (CH-013) JIT را تریپ کن تا کانال پارک شود.
 گام ۲: 15 ثانیه نگاه کن: duty صفر و وضعیت 5 (state=5) می‌ماند و ریتری خودکار نباید اتفاق بیفتد.
@@ -3751,27 +3791,27 @@
 گام ۴: این چرخه را تا تریپ سوم ادامه بده؛ تریپ سوم باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F12" s="63" t="inlineStr">
+      <c r="F12" s="89" t="inlineStr">
         <is>
           <t>JIT trip در مود دستی</t>
         </is>
       </c>
-      <c r="G12" s="63" t="inlineStr">
+      <c r="G12" s="89" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H12" s="61" t="inlineStr">
+      <c r="H12" s="87" t="inlineStr">
         <is>
           <t>پارک با duty صفر و state=5 بدون ریتری خودکار؛ ارسال مجدد duty کانال را مسلح می‌کند؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I12" s="61" t="inlineStr">
+      <c r="I12" s="87" t="inlineStr">
         <is>
           <t>پارک تا re-arm انسانی</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="87" t="inlineStr">
         <is>
           <t>state=5 → بعد از ارسال duty، درایو برگردد</t>
         </is>
@@ -3784,13 +3824,13 @@
       </c>
       <c r="M12" s="61" t="n"/>
       <c r="N12" s="61" t="n"/>
-      <c r="O12" s="63" t="inlineStr">
+      <c r="O12" s="89" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="63" t="n"/>
-      <c r="Q12" s="64">
+      <c r="Q12" s="90">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -4170,7 +4210,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4197,7 +4237,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="92" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -4262,87 +4302,87 @@
       <c r="Q3" s="54" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="51" t="inlineStr">
+      <c r="D4" s="86" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" s="86" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr">
+      <c r="F4" s="86" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="G4" s="86" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="51" t="inlineStr">
+      <c r="H4" s="86" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="51" t="inlineStr">
+      <c r="I4" s="86" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="86" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="51" t="inlineStr">
+      <c r="K4" s="86" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="51" t="inlineStr">
+      <c r="L4" s="86" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="51" t="inlineStr">
+      <c r="M4" s="86" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="51" t="inlineStr">
+      <c r="N4" s="86" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="51" t="inlineStr">
+      <c r="O4" s="86" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="51" t="inlineStr">
+      <c r="P4" s="86" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="51" t="inlineStr">
+      <c r="Q4" s="86" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4354,22 +4394,22 @@
           <t>CH-001</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>نگاشت سخت‌افزار</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E5" s="65" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: تک‌تک این نگاشت‌ها را با کد مقایسه کن:
@@ -4378,27 +4418,27 @@
 گام ۴: هر اختلافی بین شماتیک و کد دیدی، یادداشت کن. قبولی فقط با تطابق کامل است.</t>
         </is>
       </c>
-      <c r="F5" s="63" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
         <is>
           <t>PA0=TIM2_CH1، PA6=TIM3_CH1، PA1/PA7 سنس، PB2/PB6 JIT، رله NC</t>
         </is>
       </c>
-      <c r="G5" s="63" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="61" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>نگاشت مطابق شماتیک؛ رله با coil خاموش وصل (NC)</t>
         </is>
       </c>
-      <c r="I5" s="61" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>نگاشت ثابت</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="56" t="inlineStr">
         <is>
           <t>PASS: تطابق کامل</t>
         </is>
@@ -4411,13 +4451,13 @@
       </c>
       <c r="M5" s="61" t="n"/>
       <c r="N5" s="61" t="n"/>
-      <c r="O5" s="63" t="inlineStr">
+      <c r="O5" s="58" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="63" t="n"/>
-      <c r="Q5" s="64" t="inlineStr">
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -4429,22 +4469,22 @@
           <t>CH-035</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="87" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="E6" s="56" t="inlineStr">
+      <c r="E6" s="87" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر (همان الگوی task_control/task_protection).
 گام ۲: آن را 5 ثانیه پیوسته به Charger_Evaluate بده.
@@ -4452,27 +4492,27 @@
 گام ۴: نباید هیچ تصمیمی بر اساس ولتاژ/جریان زباله گرفته شود و overcurrent کاذب هم نباید بیاید.</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="89" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="89" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="56" t="inlineStr">
+      <c r="H6" s="87" t="inlineStr">
         <is>
           <t>شارژر باید safe-idle بماند؛ duty صفر؛ بدون تصمیم بر اساس v_in/v_bat زباله؛ مانند task_protection هر 9 فیلد صفر</t>
         </is>
       </c>
-      <c r="I6" s="56" t="inlineStr">
+      <c r="I6" s="87" t="inlineStr">
         <is>
           <t>safe-idle</t>
         </is>
       </c>
-      <c r="J6" s="56" t="inlineStr">
+      <c r="J6" s="87" t="inlineStr">
         <is>
           <t>duty=0 بدون overcurrent کاذب</t>
         </is>
@@ -4485,13 +4525,13 @@
       </c>
       <c r="M6" s="56" t="n"/>
       <c r="N6" s="56" t="n"/>
-      <c r="O6" s="58" t="inlineStr">
+      <c r="O6" s="89" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P6" s="58" t="n"/>
-      <c r="Q6" s="60" t="inlineStr">
+      <c r="Q6" s="90" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -4503,22 +4543,22 @@
           <t>CH-038</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>حفظ THERMAL_REST در SafeIdle</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>کانال در استراحت حرارتی</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را به استراحت حرارتی ببر (مثل تست CH-036) تا در THERMAL_REST باشد.
 گام ۲: هنگام استراحت، دادهٔ نامعتبر بده (valid=false).
@@ -4527,27 +4567,27 @@
 گام ۵: قبولی وقتی است که SafeIdle قفل حرارتی را پاک نکرده باشد.</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>valid=false حین rest</t>
         </is>
       </c>
-      <c r="G7" s="63" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H7" s="61" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>THERMAL_REST حفظ نه OFF</t>
         </is>
       </c>
-      <c r="I7" s="61" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="56" t="inlineStr">
         <is>
           <t>PASS: SafeIdle لچ حرارتی را پاک نکند</t>
         </is>
@@ -4559,18 +4599,18 @@
         </is>
       </c>
       <c r="M7" s="61" t="n"/>
-      <c r="N7" s="61" t="inlineStr">
+      <c r="N7" s="56" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O7" s="63" t="inlineStr">
+      <c r="O7" s="58" t="inlineStr">
         <is>
           <t>thermal</t>
         </is>
       </c>
       <c r="P7" s="63" t="n"/>
-      <c r="Q7" s="64" t="inlineStr">
+      <c r="Q7" s="60" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -5049,7 +5089,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Charger</t>
         </is>
@@ -5292,14 +5332,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Charger</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="86" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
@@ -5409,7 +5449,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Charger</t>
         </is>
@@ -5644,7 +5684,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5656,7 +5696,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="95" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -5712,7 +5752,7 @@
       <c r="B7" s="54" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="80" t="inlineStr">
+      <c r="A8" s="95" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -5748,7 +5788,7 @@
       <c r="B12" s="54" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="95" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -5799,7 +5839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5813,11 +5853,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="54" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="54" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -5829,7 +5865,6 @@
           <t>Charger_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="54" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5842,7 +5877,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -5855,7 +5889,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="54" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -5863,13 +5896,13 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="54" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -5877,7 +5910,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,8 +192,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -248,6 +264,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -336,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -573,6 +594,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -939,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1022,7 +1064,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
@@ -1032,6 +1073,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="96" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B14" s="97" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1082,12 +1135,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="85" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Charger</t>
+        </is>
+      </c>
+      <c r="T1" s="98" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1097,6 +1158,14 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="T2" s="99" t="inlineStr">
+        <is>
+          <t>ولتاژ باتری کانال (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U2" s="100" t="n">
+        <v>12900</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
@@ -1104,6 +1173,14 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="T3" s="99" t="inlineStr">
+        <is>
+          <t>ورودی حاضر است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U3" s="100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="86" t="inlineStr">
@@ -1190,6 +1267,19 @@
         <is>
           <t>تاریخ</t>
         </is>
+      </c>
+      <c r="R4" s="86" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="99" t="inlineStr">
+        <is>
+          <t>ولتاژ ورودی (ولت)</t>
+        </is>
+      </c>
+      <c r="U4" s="100" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
@@ -1263,6 +1353,18 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="97">
+        <f>IF($U$3=1,"با وصل ورودی شارژ شروع می‌شود: جریان بالا می‌رود و زرد چشمک می‌زند","با قطع ورودی شارژ صفر می‌شود")</f>
+        <v/>
+      </c>
+      <c r="T5" s="99" t="inlineStr">
+        <is>
+          <t>مود دستی؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U5" s="100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="55" t="inlineStr">
@@ -1335,6 +1437,18 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="97">
+        <f>IF($U$3=0,"ورودی نیست: شارژ متوقف و جریان صفر",IF($U$2&gt;=14600,"بالای جذب: جریان کم و کنترل سقفی (۱۴٫۶ ولت)",IF($U$2&gt;=14300,"جذب (ABSORB): نگه‌داشتن روی ۱۴٫۴ ولت با جریان کاهشی",IF($U$2&gt;13500,"شارژ (بالک): جریان کامل تا رسیدن به ۱۴٫۳ ولت",IF($U$2&gt;=12800,"اگر کامل شده باشد شناور ۱۳٫۵ ولت؛ وگرنه شارژ ادامه دارد","شارژ (بالک) با جریان کامل")))))</f>
+        <v/>
+      </c>
+      <c r="T6" s="99" t="inlineStr">
+        <is>
+          <t>جریان کانال (میلی‌آمپر)</t>
+        </is>
+      </c>
+      <c r="U6" s="100" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
@@ -1406,6 +1520,18 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="97">
+        <f>IF($U$3=0,"ورودی نیست: شارژ متوقف و جریان صفر",IF($U$2&gt;=14600,"بالای جذب: جریان کم و کنترل سقفی (۱۴٫۶ ولت)",IF($U$2&gt;=14300,"جذب (ABSORB): نگه‌داشتن روی ۱۴٫۴ ولت با جریان کاهشی",IF($U$2&gt;13500,"شارژ (بالک): جریان کامل تا رسیدن به ۱۴٫۳ ولت",IF($U$2&gt;=12800,"اگر کامل شده باشد شناور ۱۳٫۵ ولت؛ وگرنه شارژ ادامه دارد","شارژ (بالک) با جریان کامل")))))</f>
+        <v/>
+      </c>
+      <c r="T7" s="99" t="inlineStr">
+        <is>
+          <t>دیوتی کانال (درصد)</t>
+        </is>
+      </c>
+      <c r="U7" s="100" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="55" t="inlineStr">
@@ -1478,6 +1604,16 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="102" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="55" t="inlineStr">
@@ -1550,6 +1686,10 @@
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
+      <c r="R9" s="97">
+        <f>IF($U$5=1,"مود دستی فعال: کانال فقط با دستور پنل کار می‌کند و تشخیص خطا فریز است","مود عادی شارژ است")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="55" t="inlineStr">
@@ -1620,6 +1760,11 @@
       <c r="Q10" s="90">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
+      </c>
+      <c r="R10" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
@@ -1692,6 +1837,10 @@
       <c r="P11" s="58" t="n"/>
       <c r="Q11" s="60">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+      <c r="R11" s="97">
+        <f>IF(OR($U$4&lt;22,$U$4&gt;30),"بیرون از بازهٔ ۲۲ تا ۳۰ ولت: کانال شارژ نمی‌کند","داخل بازهٔ ۲۲ تا ۳۰ ولت: شارژ مجاز است")</f>
         <v/>
       </c>
     </row>
@@ -1764,6 +1913,11 @@
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
+      <c r="R12" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="55" t="inlineStr">
@@ -1833,6 +1987,10 @@
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
+      <c r="R13" s="97">
+        <f>IF(AND($U$7&gt;20,$U$6=0,$U$2&gt;=6000),"امضای خطای فنی کامل است: کانال قفل و خطای ۷","خطای فنی نیست: دست‌کم یکی از شرط‌ها نیست (دیوتی بالای ۲۰٪، جریان صفر، ولتاژ بالای ۶ ولت)")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="55" t="inlineStr">
@@ -1904,6 +2062,10 @@
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
+      <c r="R14" s="97">
+        <f>IF($U$3=0,"ورودی نیست: شارژ متوقف و جریان صفر",IF($U$2&gt;=14600,"بالای جذب: جریان کم و کنترل سقفی (۱۴٫۶ ولت)",IF($U$2&gt;=14300,"جذب (ABSORB): نگه‌داشتن روی ۱۴٫۴ ولت با جریان کاهشی",IF($U$2&gt;13500,"شارژ (بالک): جریان کامل تا رسیدن به ۱۴٫۳ ولت",IF($U$2&gt;=12800,"اگر کامل شده باشد شناور ۱۳٫۵ ولت؛ وگرنه شارژ ادامه دارد","شارژ (بالک) با جریان کامل")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
@@ -1976,6 +2138,10 @@
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
+      <c r="R15" s="97">
+        <f>IF($U$2&lt;=12800,"زیر ۱۲٫۸ ولت: شارژ دوباره شروع می‌شود (برگشت به شارژ)",IF($U$2&lt;13500,"بین ۱۲٫۸ و ۱۳٫۵ ولت: شناور می‌ماند و شارژ تازه شروع نمی‌شود","بالای ۱۳٫۵ ولت: در جذب/شناور کامل است"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="55" t="inlineStr">
@@ -2048,6 +2214,11 @@
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
+      <c r="R16" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="55" t="inlineStr">
@@ -2120,6 +2291,11 @@
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
+      <c r="R17" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="55" t="inlineStr">
@@ -2192,6 +2368,11 @@
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
+      <c r="R18" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="55" t="inlineStr">
@@ -2262,6 +2443,10 @@
       <c r="P19" s="63" t="n"/>
       <c r="Q19" s="60">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+      <c r="R19" s="97">
+        <f>"دیوتی از سقف زندهٔ پنل رد نمی‌شود؛ سقف فعلی که گذاشته‌ای: "&amp;$U$7&amp;" درصد"</f>
         <v/>
       </c>
     </row>
@@ -2336,6 +2521,11 @@
       <c r="Q20" s="90">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
+      </c>
+      <c r="R20" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3043,9 +3233,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q61"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="T8:U8"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
@@ -5839,7 +6031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5853,7 +6045,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -5902,7 +6093,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -2528,24 +2528,82 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="83" t="n"/>
-      <c r="B21" s="83" t="n"/>
-      <c r="C21" s="83" t="n"/>
-      <c r="D21" s="83" t="n"/>
-      <c r="E21" s="83" t="n"/>
-      <c r="F21" s="83" t="n"/>
-      <c r="G21" s="83" t="n"/>
-      <c r="H21" s="83" t="n"/>
-      <c r="I21" s="83" t="n"/>
-      <c r="J21" s="83" t="n"/>
-      <c r="K21" s="83" t="n"/>
-      <c r="L21" s="83" t="n"/>
-      <c r="M21" s="83" t="n"/>
-      <c r="N21" s="83" t="n"/>
-      <c r="O21" s="83" t="n"/>
-      <c r="P21" s="83" t="n"/>
-      <c r="Q21" s="84" t="n"/>
+    <row r="21" ht="108" customHeight="1">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>CH-043</t>
+        </is>
+      </c>
+      <c r="B21" s="87" t="inlineStr">
+        <is>
+          <t>مکث ورودی و شمارندهٔ باتری خراب</t>
+        </is>
+      </c>
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D21" s="87" t="inlineStr">
+        <is>
+          <t>باتری نیمه‌خالی در حال شارژ است؛ منبع ورودی قابل تنظیم است؛ پنل وصل است.</t>
+        </is>
+      </c>
+      <c r="E21" s="87" t="inlineStr">
+        <is>
+          <t>گام ۱: زمان مکث تشخیص باتری خراب را از پنل موقتاً روی ۵ ثانیه بگذار.
+گام ۲: صبر کن شمارندهٔ زمان شارژ از ۱۰ ثانیه بیشتر شود.
+گام ۳: ولتاژ ورودی را به زیر ۲۲ ولت ببر.
+گام ۴: پس از ۳ ثانیه، ورودی را به ۲۴ ولت برگردان و شمارنده را ببین.
+گام ۵: ورودی را دوباره به زیر ۲۲ ولت ببر.
+گام ۶: پس از ۷ ثانیه، ورودی را به ۲۴ ولت برگردان و شمارنده را ببین.
+گام ۷: زمان مکث را به مقدار عادی یک دقیقه برگردان.</t>
+        </is>
+      </c>
+      <c r="F21" s="89" t="inlineStr">
+        <is>
+          <t>ورودی زیر ۲۲ ولت؛ مکث ۳ ثانیه و ۷ ثانیه؛ بازگشت به ۲۴ ولت</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="inlineStr">
+        <is>
+          <t>حدود پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H21" s="87" t="inlineStr">
+        <is>
+          <t>مکث کوتاه شمارنده را نگه می‌دارد؛ مکث ۵ ثانیه یا بیشتر آن را صفر می‌کند؛ پس از برگشت ورودی شارژ امن از سر گرفته می‌شود.</t>
+        </is>
+      </c>
+      <c r="I21" s="87" t="inlineStr">
+        <is>
+          <t>کمتر از ۵ ثانیه: حفظ؛ ۵ ثانیه یا بیشتر: صفر</t>
+        </is>
+      </c>
+      <c r="J21" s="87" t="inlineStr">
+        <is>
+          <t>باید ببینی: پس از مکث ۳ ثانیه‌ای شمارنده ادامه دارد؛ پس از مکث ۷ ثانیه‌ای صفر می‌شود؛ با برگشت ورودی شارژ دوباره و آرام شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="K21" s="61" t="n"/>
+      <c r="L21" s="67" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M21" s="61" t="n"/>
+      <c r="N21" s="61" t="n"/>
+      <c r="O21" s="89" t="n"/>
+      <c r="P21" s="63" t="n"/>
+      <c r="Q21" s="90">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+      <c r="R21" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="83" t="n"/>
@@ -3241,10 +3299,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20 C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L20 L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -4808,24 +4866,77 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="54" t="n"/>
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="54" t="n"/>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
-      <c r="G8" s="54" t="n"/>
-      <c r="H8" s="54" t="n"/>
-      <c r="I8" s="54" t="n"/>
-      <c r="J8" s="54" t="n"/>
-      <c r="K8" s="54" t="n"/>
-      <c r="L8" s="54" t="n"/>
-      <c r="M8" s="54" t="n"/>
-      <c r="N8" s="54" t="n"/>
-      <c r="O8" s="54" t="n"/>
-      <c r="P8" s="54" t="n"/>
-      <c r="Q8" s="68">
+    <row r="8" ht="82" customHeight="1">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>CH-044</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>تست میزبان شمارندهٔ مکث سناریوی ۶</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>سورس Charger و شبیه‌ساز پیش‌نمایش در دسترس است؛ برد لازم نیست.</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>گام ۱: تست‌های میزبان Charger را اجرا کن: `python3 Firmware/Modules/Charger/Tester/host_test_charger.py`.
+گام ۲: تست سناریوی ۶ شبیه‌ساز را اجرا کن: `node tools/panel_preview_server.js --self-test`.</t>
+        </is>
+      </c>
+      <c r="F8" s="58" t="inlineStr">
+        <is>
+          <t>ورودی نامعتبر ۱۵۰۰۰ و ۲۹۵۰۰ میلی‌ولت؛ مکث کوتاه‌تر و بلندتر از حد تنظیم‌شده</t>
+        </is>
+      </c>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>ورودی نامعتبر به INPUT_WAIT می‌رود؛ مکث کوتاه شمارنده را نگه می‌دارد و مکثِ رسیده به حد، آن را صفر می‌کند؛ بازیابی از OFF شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="inlineStr">
+        <is>
+          <t>مکث کوتاه حفظ؛ مکث بلند صفر؛ بازیابی امن</t>
+        </is>
+      </c>
+      <c r="J8" s="56" t="inlineStr">
+        <is>
+          <t>همهٔ بررسی‌های میزبان و شبیه‌ساز سبز شوند؛ تست برد جداگانه در انتظار بماند.</t>
+        </is>
+      </c>
+      <c r="K8" s="61" t="inlineStr">
+        <is>
+          <t>۵۲ تست میزبان Charger و تست رگرسیون شبیه‌ساز موفق؛ تست برد انجام نشده است.</t>
+        </is>
+      </c>
+      <c r="L8" s="72" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M8" s="61" t="n"/>
+      <c r="N8" s="56" t="inlineStr">
+        <is>
+          <t>bash tools/check_firmware_syntax.sh; node tools/panel_preview_server.js --self-test</t>
+        </is>
+      </c>
+      <c r="O8" s="58" t="n"/>
+      <c r="P8" s="63" t="n"/>
+      <c r="Q8" s="60">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -4464,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5357,6 +5357,65 @@
       <c r="Q27" s="68">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CH-045</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>اشمیت مشترک ورودی</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>سورس Charger/Fault و تستر هاست در دسترس است؛ برد لازم نیست.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>گام ۱: host_test_charger.py و host_test_fault.c را اجرا کن.
+گام ۲: در تست Fault، q169/q170 را ۵۰۰/۵۰۰ بگذار و مجوز را دور لبه‌های ۲۱۰۰۰/۲۸۰۰۰ بران.
+گام ۳: در سورس Charger چک کن هر OFF-&gt;BULK (عادی، دیوتی ثابت، دستی، bringup) و INPUT_WAIT-&gt;OFF فقط از bool__inputPermitted می‌گذرد.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>q33=21000, q34=28000, q169=q170=500</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>بیرون پنجره خام مجوز فوراً false؛ برگشت فقط داخل ۲۱۵۰۰..۲۷۵۰۰؛ شارژر بدون مجوز شروع نمی‌کند</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>اشمیت مشترک</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PASS: تست‌ها سبز و همه مسیرهای شروع همان پرچم را می‌خوانند. FAIL: هر مسیر شروع جدا.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Firmware/Modules/Charger/Charger_Validation.xlsx
+++ b/Firmware/Modules/Charger/Charger_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$61</definedName>
